--- a/live-history.xlsx
+++ b/live-history.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E51"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -620,9 +620,655 @@
         <v>17-08-2026 03:55:47 pm</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>6a82fdbdb6cbad57ae425d52</v>
+      </c>
+      <c r="B14" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E14" t="str">
+        <v>17-08-2026 05:55:33 pm</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>6a82e1accd8c3a2ccfb6212e</v>
+      </c>
+      <c r="B15" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E15" t="str">
+        <v>17-08-2026 03:55:48 pm</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>6a83093a730bf22165b047dc</v>
+      </c>
+      <c r="B16" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E16" t="str">
+        <v>17-08-2026 06:44:34 pm</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>6a82fdbdb6cbad57ae425d54</v>
+      </c>
+      <c r="B17" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E17" t="str">
+        <v>17-08-2026 05:55:33 pm</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>6a830941730bf22165b047f5</v>
+      </c>
+      <c r="B18" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E18" t="str">
+        <v>17-08-2026 06:44:41 pm</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>6a83093a730bf22165b047de</v>
+      </c>
+      <c r="B19" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E19" t="str">
+        <v>17-08-2026 06:44:34 pm</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>6a830941730bf22165b047f7</v>
+      </c>
+      <c r="B20" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E20" t="str">
+        <v>17-08-2026 06:44:41 pm</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>6a83094a730bf22165b04816</v>
+      </c>
+      <c r="B21" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Started Playing game and Debited "10" and Balance "90"</v>
+      </c>
+      <c r="E21" t="str">
+        <v>17-08-2026 06:44:50 pm</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>6a83094b730bf22165b0481c</v>
+      </c>
+      <c r="B22" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E22" t="str">
+        <v>17-08-2026 06:44:51 pm</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>6a830a7447673107ea87bbf5</v>
+      </c>
+      <c r="B23" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E23" t="str">
+        <v>17-08-2026 06:49:48 pm</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>6a830a7547673107ea87bbfb</v>
+      </c>
+      <c r="B24" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E24" t="str">
+        <v>17-08-2026 06:49:49 pm</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>6a830a7e47673107ea87bc18</v>
+      </c>
+      <c r="B25" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Started Playing game and Debited "10" and Balance "80"</v>
+      </c>
+      <c r="E25" t="str">
+        <v>17-08-2026 06:49:58 pm</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>6a830acf47673107ea87bc3b</v>
+      </c>
+      <c r="B26" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E26" t="str">
+        <v>17-08-2026 06:51:19 pm</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>6a830ad047673107ea87bc41</v>
+      </c>
+      <c r="B27" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E27" t="str">
+        <v>17-08-2026 06:51:20 pm</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>6a830b2347673107ea87bc87</v>
+      </c>
+      <c r="B28" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E28" t="str">
+        <v>17-08-2026 06:52:43 pm</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>6a830b6a0266c3cf7ac77165</v>
+      </c>
+      <c r="B29" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Started Playing game and Debited "10" and Balance "60"</v>
+      </c>
+      <c r="E29" t="str">
+        <v>17-08-2026 06:53:54 pm</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>6a830c580266c3cf7ac771b2</v>
+      </c>
+      <c r="B30" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D30" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6a830c570266c3cf7ac771a4 , Question : How many letters are misaligned?, Type : letters_missalign </v>
+      </c>
+      <c r="E30" t="str">
+        <v>17-08-2026 06:57:52 pm</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>6a830c1e0266c3cf7ac7718e</v>
+      </c>
+      <c r="B31" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Answerd Correctly to Qst ID : 6a830b6d0266c3cf7ac7716f, Reward : 10, Qst No : 1 ,Question : How many puzzle pieces contain 2 or more MALE connectors (outward tabs)?</v>
+      </c>
+      <c r="E31" t="str">
+        <v>17-08-2026 06:56:54 pm</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>6a830c580266c3cf7ac771b4</v>
+      </c>
+      <c r="B32" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D32" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6a830c570266c3cf7ac771a4 , Question : How many letters are misaligned?, Type : letters_missalign </v>
+      </c>
+      <c r="E32" t="str">
+        <v>17-08-2026 06:57:52 pm</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>6a830c5e0266c3cf7ac771cb</v>
+      </c>
+      <c r="B33" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E33" t="str">
+        <v>17-08-2026 06:57:58 pm</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>6a830c5e0266c3cf7ac771d1</v>
+      </c>
+      <c r="B34" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E34" t="str">
+        <v>17-08-2026 06:57:58 pm</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>6a830c670266c3cf7ac771ee</v>
+      </c>
+      <c r="B35" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Started Playing game and Debited "10" and Balance "50"</v>
+      </c>
+      <c r="E35" t="str">
+        <v>17-08-2026 06:58:07 pm</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>6a8312806bf04dd5800901b3</v>
+      </c>
+      <c r="B36" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E36" t="str">
+        <v>17-08-2026 07:24:08 pm</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>6a8312816bf04dd5800901b9</v>
+      </c>
+      <c r="B37" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E37" t="str">
+        <v>17-08-2026 07:24:09 pm</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>6a8312896bf04dd5800901d6</v>
+      </c>
+      <c r="B38" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Started Playing game and Debited "10" and Balance "40"</v>
+      </c>
+      <c r="E38" t="str">
+        <v>17-08-2026 07:24:17 pm</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>6a8312eeda45678782653e4a</v>
+      </c>
+      <c r="B39" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E39" t="str">
+        <v>17-08-2026 07:25:58 pm</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>6a8312efda45678782653e50</v>
+      </c>
+      <c r="B40" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E40" t="str">
+        <v>17-08-2026 07:25:59 pm</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>6a8312f7da45678782653e6d</v>
+      </c>
+      <c r="B41" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Started Playing game and Debited "10" and Balance "30"</v>
+      </c>
+      <c r="E41" t="str">
+        <v>17-08-2026 07:26:07 pm</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>6a83134ada45678782653e92</v>
+      </c>
+      <c r="B42" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E42" t="str">
+        <v>17-08-2026 07:27:30 pm</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>6a83134bda45678782653e98</v>
+      </c>
+      <c r="B43" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E43" t="str">
+        <v>17-08-2026 07:27:31 pm</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>6a831355da45678782653eb5</v>
+      </c>
+      <c r="B44" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Started Playing game and Debited "10" and Balance "20"</v>
+      </c>
+      <c r="E44" t="str">
+        <v>17-08-2026 07:27:41 pm</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>6a8313acb503e39ab6cff906</v>
+      </c>
+      <c r="B45" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E45" t="str">
+        <v>17-08-2026 07:29:08 pm</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>6a8313adb503e39ab6cff90c</v>
+      </c>
+      <c r="B46" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E46" t="str">
+        <v>17-08-2026 07:29:09 pm</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>6a8313b6b503e39ab6cff929</v>
+      </c>
+      <c r="B47" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Started Playing game and Debited "10" and Balance "10"</v>
+      </c>
+      <c r="E47" t="str">
+        <v>17-08-2026 07:29:18 pm</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>6a8313d3b503e39ab6cff94c</v>
+      </c>
+      <c r="B48" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E48" t="str">
+        <v>17-08-2026 07:29:47 pm</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>6a8313d3b503e39ab6cff952</v>
+      </c>
+      <c r="B49" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E49" t="str">
+        <v>17-08-2026 07:29:47 pm</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>6a8313dcb503e39ab6cff96f</v>
+      </c>
+      <c r="B50" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Started Playing game and Debited "10" and Balance "0"</v>
+      </c>
+      <c r="E50" t="str">
+        <v>17-08-2026 07:29:56 pm</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>6a831456b503e39ab6cff992</v>
+      </c>
+      <c r="B51" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E51" t="str">
+        <v>17-08-2026 07:31:58 pm</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E51"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/live-history.xlsx
+++ b/live-history.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E77"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1266,9 +1266,451 @@
         <v>17-08-2026 07:31:58 pm</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>6a831456b503e39ab6cff998</v>
+      </c>
+      <c r="B52" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D52" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E52" t="str">
+        <v>17-08-2026 07:31:58 pm</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>6a8324878dbf33c823e939e2</v>
+      </c>
+      <c r="B53" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D53" t="str">
+        <v>Refunded: ₹10</v>
+      </c>
+      <c r="E53" t="str">
+        <v>17-08-2026 08:41:03 pm</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>6a8324988dbf33c823e939f7</v>
+      </c>
+      <c r="B54" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D54" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E54" t="str">
+        <v>17-08-2026 08:41:20 pm</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>6a8324988dbf33c823e939fd</v>
+      </c>
+      <c r="B55" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D55" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E55" t="str">
+        <v>17-08-2026 08:41:20 pm</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>6a8325178fabb8b0977b48af</v>
+      </c>
+      <c r="B56" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D56" t="str">
+        <v>Refunded: ₹10</v>
+      </c>
+      <c r="E56" t="str">
+        <v>17-08-2026 08:43:27 pm</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>6a8325208fabb8b0977b48e4</v>
+      </c>
+      <c r="B57" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C57" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D57" t="str">
+        <v>Refunded: ₹10</v>
+      </c>
+      <c r="E57" t="str">
+        <v>17-08-2026 08:43:36 pm</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>6a8325288fabb8b0977b48f7</v>
+      </c>
+      <c r="B58" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C58" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D58" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E58" t="str">
+        <v>17-08-2026 08:43:44 pm</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>6a8325298fabb8b0977b48fd</v>
+      </c>
+      <c r="B59" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C59" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D59" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E59" t="str">
+        <v>17-08-2026 08:43:45 pm</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>6a8325c3b3cc9650dbf20eec</v>
+      </c>
+      <c r="B60" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C60" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D60" t="str">
+        <v>Started Playing game and Debited "10" and Balance "40"</v>
+      </c>
+      <c r="E60" t="str">
+        <v>17-08-2026 08:46:19 pm</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>6a8325c4b3cc9650dbf20ef2</v>
+      </c>
+      <c r="B61" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C61" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D61" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E61" t="str">
+        <v>17-08-2026 08:46:20 pm</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>6a832767a464073910201bb4</v>
+      </c>
+      <c r="B62" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C62" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D62" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E62" t="str">
+        <v>17-08-2026 08:53:19 pm</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>6a832768a464073910201bba</v>
+      </c>
+      <c r="B63" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C63" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D63" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E63" t="str">
+        <v>17-08-2026 08:53:20 pm</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>6a83276fa464073910201bd9</v>
+      </c>
+      <c r="B64" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C64" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D64" t="str">
+        <v>Started Playing game and Debited "10" and Balance "30"</v>
+      </c>
+      <c r="E64" t="str">
+        <v>17-08-2026 08:53:27 pm</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>6a8327afa464073910201c0b</v>
+      </c>
+      <c r="B65" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C65" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D65" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E65" t="str">
+        <v>17-08-2026 08:54:31 pm</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>6a8327b0a464073910201c11</v>
+      </c>
+      <c r="B66" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C66" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D66" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E66" t="str">
+        <v>17-08-2026 08:54:32 pm</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>6a832907a464073910201c97</v>
+      </c>
+      <c r="B67" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C67" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D67" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E67" t="str">
+        <v>17-08-2026 09:00:15 pm</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>6a832d10f3f803e696ea8cdd</v>
+      </c>
+      <c r="B68" t="str">
+        <v>6878c1edcdcb91aacab49c6b</v>
+      </c>
+      <c r="C68" t="str">
+        <v>Naveen. G</v>
+      </c>
+      <c r="D68" t="str">
+        <v>Refunded to User: 6878c1edcdcb91aacab49c6b, Amount: ₹20₹</v>
+      </c>
+      <c r="E68" t="str">
+        <v>17-08-2026 09:17:28 pm</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>6a832e8b79205742ed5c83e5</v>
+      </c>
+      <c r="B69" t="str">
+        <v>6878c1edcdcb91aacab49c6b</v>
+      </c>
+      <c r="C69" t="str">
+        <v>Naveen. G</v>
+      </c>
+      <c r="D69" t="str">
+        <v>Refunded to User: 6878c1edcdcb91aacab49c6b, Amount: ₹20₹</v>
+      </c>
+      <c r="E69" t="str">
+        <v>17-08-2026 09:23:47 pm</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>6a832ec379205742ed5c840b</v>
+      </c>
+      <c r="B70" t="str">
+        <v>6878c1edcdcb91aacab49c6b</v>
+      </c>
+      <c r="C70" t="str">
+        <v>Naveen. G</v>
+      </c>
+      <c r="D70" t="str">
+        <v>Refunded to User: 6878c1edcdcb91aacab49c6b, Amount: ₹20₹</v>
+      </c>
+      <c r="E70" t="str">
+        <v>17-08-2026 09:24:43 pm</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>6a832ecb79205742ed5c8428</v>
+      </c>
+      <c r="B71" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C71" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D71" t="str">
+        <v>Refunded to User: 686e24d32f21c9417882f777, Amount: ₹50₹</v>
+      </c>
+      <c r="E71" t="str">
+        <v>17-08-2026 09:24:51 pm</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>6a832f7b25b4d6e4ce137147</v>
+      </c>
+      <c r="B72" t="str">
+        <v>6878c1edcdcb91aacab49c6b</v>
+      </c>
+      <c r="C72" t="str">
+        <v>Naveen. G</v>
+      </c>
+      <c r="D72" t="str">
+        <v>Refunded to User: 6878c1edcdcb91aacab49c6b, Amount: ₹20₹</v>
+      </c>
+      <c r="E72" t="str">
+        <v>17-08-2026 09:27:47 pm</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>6a832f7e25b4d6e4ce137160</v>
+      </c>
+      <c r="B73" t="str">
+        <v>6878c1edcdcb91aacab49c6b</v>
+      </c>
+      <c r="C73" t="str">
+        <v>Naveen. G</v>
+      </c>
+      <c r="D73" t="str">
+        <v>Refunded to User: 6878c1edcdcb91aacab49c6b, Amount: ₹20₹</v>
+      </c>
+      <c r="E73" t="str">
+        <v>17-08-2026 09:27:50 pm</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>6a832f8225b4d6e4ce137179</v>
+      </c>
+      <c r="B74" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C74" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D74" t="str">
+        <v>Refunded to User: 686e24d32f21c9417882f777, Amount: ₹50₹</v>
+      </c>
+      <c r="E74" t="str">
+        <v>17-08-2026 09:27:54 pm</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>6a832f8625b4d6e4ce137191</v>
+      </c>
+      <c r="B75" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C75" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D75" t="str">
+        <v>Refunded to User: 686e24d32f21c9417882f777, Amount: ₹20₹</v>
+      </c>
+      <c r="E75" t="str">
+        <v>17-08-2026 09:27:58 pm</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>6a83b399e0f705b66fff6214</v>
+      </c>
+      <c r="B76" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C76" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D76" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E76" t="str">
+        <v>18-08-2026 06:51:29 am</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>6a83b39ae0f705b66fff621a</v>
+      </c>
+      <c r="B77" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C77" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D77" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E77" t="str">
+        <v>18-08-2026 06:51:30 am</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E77"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/live-history.xlsx
+++ b/live-history.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E77"/>
+  <dimension ref="A1:E92"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1708,9 +1708,264 @@
         <v>18-08-2026 06:51:30 am</v>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>6a83b3c7e0f705b66fff623b</v>
+      </c>
+      <c r="B78" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C78" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D78" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E78" t="str">
+        <v>18-08-2026 06:52:15 am</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>6a83b3a2e0f705b66fff6223</v>
+      </c>
+      <c r="B79" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C79" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D79" t="str">
+        <v>Selected Language Document Deleted</v>
+      </c>
+      <c r="E79" t="str">
+        <v>18-08-2026 06:51:38 am</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>6a83b3c7e0f705b66fff623d</v>
+      </c>
+      <c r="B80" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C80" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D80" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E80" t="str">
+        <v>18-08-2026 06:52:15 am</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>6a840cd6ea31465bafbb2274</v>
+      </c>
+      <c r="B81" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C81" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D81" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E81" t="str">
+        <v>18-08-2026 01:12:14 pm</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>6a840cd6ea31465bafbb227a</v>
+      </c>
+      <c r="B82" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C82" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D82" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E82" t="str">
+        <v>18-08-2026 01:12:14 pm</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>6a840cdeea31465bafbb22a7</v>
+      </c>
+      <c r="B83" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C83" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D83" t="str">
+        <v>Started Playing game and Debited "10" and Balance "10"</v>
+      </c>
+      <c r="E83" t="str">
+        <v>18-08-2026 01:12:22 pm</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>6a840cdfea31465bafbb22ad</v>
+      </c>
+      <c r="B84" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C84" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D84" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E84" t="str">
+        <v>18-08-2026 01:12:23 pm</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>6a840cf0ea31465bafbb231a</v>
+      </c>
+      <c r="B85" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C85" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D85" t="str">
+        <v>Answered incorrectly for Qst ID: 6a840ce1ea31465bafbb22cf, Qst: How many puzzle pieces contain 2 or more MALE connectors (outward tabs)?, Submitted Answer: 1</v>
+      </c>
+      <c r="E85" t="str">
+        <v>18-08-2026 01:12:40 pm</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>6a840cf3ea31465bafbb2330</v>
+      </c>
+      <c r="B86" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C86" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D86" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E86" t="str">
+        <v>18-08-2026 01:12:43 pm</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>6a840cf3ea31465bafbb2336</v>
+      </c>
+      <c r="B87" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C87" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D87" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E87" t="str">
+        <v>18-08-2026 01:12:43 pm</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>6a840d8aea31465bafbb252a</v>
+      </c>
+      <c r="B88" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C88" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D88" t="str">
+        <v>Started Playing game and Debited "10" and Balance "0"</v>
+      </c>
+      <c r="E88" t="str">
+        <v>18-08-2026 01:15:14 pm</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>6a840d9cea31465bafbb258c</v>
+      </c>
+      <c r="B89" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C89" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D89" t="str">
+        <v>Answerd Correctly to Qst ID : 6a840d8cea31465bafbb253c, Reward : 10, Qst No : 1 ,Question : How many letters are colored with the WRONG color?</v>
+      </c>
+      <c r="E89" t="str">
+        <v>18-08-2026 01:15:32 pm</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>6a840da1ea31465bafbb25ba</v>
+      </c>
+      <c r="B90" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C90" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D90" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6a840da0ea31465bafbb25b1 , Question : What is the alphabetical arrangement of these random letters: "lou"?, Type : re_arrange_letters </v>
+      </c>
+      <c r="E90" t="str">
+        <v>18-08-2026 01:15:37 pm</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>6a840da3ea31465bafbb25d8</v>
+      </c>
+      <c r="B91" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C91" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D91" t="str">
+        <v>Answered incorrectly for Qst ID: 6a840da0ea31465bafbb25b1, Qst: What is the alphabetical arrangement of these random letters: "lou"?, Submitted Answer: 118</v>
+      </c>
+      <c r="E91" t="str">
+        <v>18-08-2026 01:15:39 pm</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>6a840da5ea31465bafbb25ed</v>
+      </c>
+      <c r="B92" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C92" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D92" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E92" t="str">
+        <v>18-08-2026 01:15:41 pm</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E77"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E92"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/live-history.xlsx
+++ b/live-history.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E92"/>
+  <dimension ref="A1:E285"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1963,9 +1963,3290 @@
         <v>18-08-2026 01:15:41 pm</v>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>6a840da6ea31465bafbb25f4</v>
+      </c>
+      <c r="B93" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C93" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D93" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E93" t="str">
+        <v>18-08-2026 01:15:42 pm</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>6a843ffad0fd4161b5fb51a1</v>
+      </c>
+      <c r="B94" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C94" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D94" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E94" t="str">
+        <v>18-08-2026 04:50:26 pm</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>6a843ffad0fd4161b5fb51a7</v>
+      </c>
+      <c r="B95" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C95" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D95" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E95" t="str">
+        <v>18-08-2026 04:50:26 pm</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>6a8445fcedef81c3e8370fbb</v>
+      </c>
+      <c r="B96" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C96" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D96" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E96" t="str">
+        <v>18-08-2026 05:16:04 pm</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>6a8445fdedef81c3e8370fc1</v>
+      </c>
+      <c r="B97" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C97" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D97" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E97" t="str">
+        <v>18-08-2026 05:16:05 pm</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>6a844d943729962c0e31391b</v>
+      </c>
+      <c r="B98" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C98" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D98" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E98" t="str">
+        <v>18-08-2026 05:48:28 pm</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>6a844d943729962c0e313921</v>
+      </c>
+      <c r="B99" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C99" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D99" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E99" t="str">
+        <v>18-08-2026 05:48:28 pm</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>6a844dc73729962c0e313d08</v>
+      </c>
+      <c r="B100" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C100" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D100" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E100" t="str">
+        <v>18-08-2026 05:49:19 pm</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>6a844dc83729962c0e313d0e</v>
+      </c>
+      <c r="B101" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C101" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D101" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E101" t="str">
+        <v>18-08-2026 05:49:20 pm</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>6a844de13729962c0e313f52</v>
+      </c>
+      <c r="B102" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C102" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D102" t="str">
+        <v>Started Playing game and Debited "10" and Balance "990"</v>
+      </c>
+      <c r="E102" t="str">
+        <v>18-08-2026 05:49:45 pm</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>6a844e023729962c0e3141c2</v>
+      </c>
+      <c r="B103" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C103" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D103" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E103" t="str">
+        <v>18-08-2026 05:50:18 pm</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>6a844e023729962c0e3141c8</v>
+      </c>
+      <c r="B104" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C104" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D104" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E104" t="str">
+        <v>18-08-2026 05:50:18 pm</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>6a8450dc0a29387e9fa4ad6e</v>
+      </c>
+      <c r="B105" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C105" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D105" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E105" t="str">
+        <v>18-08-2026 06:02:28 pm</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>6a844e0d3729962c0e314410</v>
+      </c>
+      <c r="B106" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C106" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D106" t="str">
+        <v>Started Playing game and Debited "10" and Balance "980"</v>
+      </c>
+      <c r="E106" t="str">
+        <v>18-08-2026 05:50:29 pm</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>6a8450dc0a29387e9fa4ad70</v>
+      </c>
+      <c r="B107" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C107" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D107" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E107" t="str">
+        <v>18-08-2026 06:02:28 pm</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>6a845524745521f72510169e</v>
+      </c>
+      <c r="B108" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C108" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D108" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E108" t="str">
+        <v>18-08-2026 06:20:44 pm</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>6a8450ed0a29387e9fa4afbd</v>
+      </c>
+      <c r="B109" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C109" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D109" t="str">
+        <v>Started Playing game and Debited "10" and Balance "970"</v>
+      </c>
+      <c r="E109" t="str">
+        <v>18-08-2026 06:02:45 pm</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>6a845524745521f7251016a0</v>
+      </c>
+      <c r="B110" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C110" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D110" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E110" t="str">
+        <v>18-08-2026 06:20:44 pm</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>6a84552b745521f725101762</v>
+      </c>
+      <c r="B111" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C111" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D111" t="str">
+        <v>Started Playing game and Debited "10" and Balance "960"</v>
+      </c>
+      <c r="E111" t="str">
+        <v>18-08-2026 06:20:51 pm</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>6a8456890a3f148bf897ce42</v>
+      </c>
+      <c r="B112" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C112" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D112" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E112" t="str">
+        <v>18-08-2026 06:26:41 pm</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>6a8456890a3f148bf897ce48</v>
+      </c>
+      <c r="B113" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C113" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D113" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E113" t="str">
+        <v>18-08-2026 06:26:41 pm</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>6a8456990a3f148bf897cfd1</v>
+      </c>
+      <c r="B114" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C114" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D114" t="str">
+        <v>Started Playing game and Debited "10" and Balance "950"</v>
+      </c>
+      <c r="E114" t="str">
+        <v>18-08-2026 06:26:57 pm</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>6a84574fb0ba3ff8dfcfde4a</v>
+      </c>
+      <c r="B115" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C115" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D115" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E115" t="str">
+        <v>18-08-2026 06:29:59 pm</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>6a845750b0ba3ff8dfcfde52</v>
+      </c>
+      <c r="B116" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C116" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D116" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E116" t="str">
+        <v>18-08-2026 06:30:00 pm</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>6a845758b0ba3ff8dfcfdfdb</v>
+      </c>
+      <c r="B117" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C117" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D117" t="str">
+        <v>Started Playing game and Debited "10" and Balance "940"</v>
+      </c>
+      <c r="E117" t="str">
+        <v>18-08-2026 06:30:08 pm</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>6a8457898b7cfe270eb3ec30</v>
+      </c>
+      <c r="B118" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C118" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D118" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E118" t="str">
+        <v>18-08-2026 06:30:57 pm</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>6a84578a8b7cfe270eb3ed00</v>
+      </c>
+      <c r="B119" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C119" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D119" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E119" t="str">
+        <v>18-08-2026 06:30:58 pm</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>6a8457918b7cfe270eb3edc3</v>
+      </c>
+      <c r="B120" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C120" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D120" t="str">
+        <v>Started Playing game and Debited "10" and Balance "930"</v>
+      </c>
+      <c r="E120" t="str">
+        <v>18-08-2026 06:31:05 pm</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>6a84580f62089cb39a7747fd</v>
+      </c>
+      <c r="B121" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C121" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D121" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E121" t="str">
+        <v>18-08-2026 06:33:11 pm</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>6a84581062089cb39a774803</v>
+      </c>
+      <c r="B122" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C122" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D122" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E122" t="str">
+        <v>18-08-2026 06:33:12 pm</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>6a84587062089cb39a7750dc</v>
+      </c>
+      <c r="B123" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C123" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D123" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E123" t="str">
+        <v>18-08-2026 06:34:48 pm</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>6a84583662089cb39a774bf3</v>
+      </c>
+      <c r="B124" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C124" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D124" t="str">
+        <v>Started Playing game and Debited "10" and Balance "920"</v>
+      </c>
+      <c r="E124" t="str">
+        <v>18-08-2026 06:33:50 pm</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>6a84587062089cb39a7750de</v>
+      </c>
+      <c r="B125" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C125" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D125" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E125" t="str">
+        <v>18-08-2026 06:34:48 pm</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>6a8470a562089cb39a777f12</v>
+      </c>
+      <c r="B126" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C126" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D126" t="str">
+        <v>Started Playing game and Debited "10" and Balance "910"</v>
+      </c>
+      <c r="E126" t="str">
+        <v>18-08-2026 08:18:05 pm</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>6a8471f562089cb39a7798de</v>
+      </c>
+      <c r="B127" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C127" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D127" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E127" t="str">
+        <v>18-08-2026 08:23:41 pm</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>6a8471f562089cb39a7798e4</v>
+      </c>
+      <c r="B128" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C128" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D128" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E128" t="str">
+        <v>18-08-2026 08:23:41 pm</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>6a84720362089cb39a779a77</v>
+      </c>
+      <c r="B129" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C129" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D129" t="str">
+        <v>Started Playing game and Debited "10" and Balance "900"</v>
+      </c>
+      <c r="E129" t="str">
+        <v>18-08-2026 08:23:55 pm</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>6a84721c62089cb39a779d0b</v>
+      </c>
+      <c r="B130" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C130" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D130" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E130" t="str">
+        <v>18-08-2026 08:24:20 pm</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>6a84721c62089cb39a779d11</v>
+      </c>
+      <c r="B131" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C131" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D131" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E131" t="str">
+        <v>18-08-2026 08:24:20 pm</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>6a84722662089cb39a779ea7</v>
+      </c>
+      <c r="B132" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C132" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D132" t="str">
+        <v>Started Playing game and Debited "10" and Balance "890"</v>
+      </c>
+      <c r="E132" t="str">
+        <v>18-08-2026 08:24:30 pm</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>6a84723a62089cb39a779fc7</v>
+      </c>
+      <c r="B133" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C133" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D133" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6a84723962089cb39a779fb8 , Question : Decode "I" using cipher key, Type : encode_decode </v>
+      </c>
+      <c r="E133" t="str">
+        <v>18-08-2026 08:24:50 pm</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>6a84723462089cb39a779fa4</v>
+      </c>
+      <c r="B134" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C134" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D134" t="str">
+        <v>Answerd Correctly to Qst ID : 6a84722762089cb39a779eb7, Reward : 10, Qst No : 1 ,Question : What is the alphabetical arrangement of these random letters: "sfx"?</v>
+      </c>
+      <c r="E134" t="str">
+        <v>18-08-2026 08:24:44 pm</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>6a84723a62089cb39a779fc9</v>
+      </c>
+      <c r="B135" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C135" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D135" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6a84723962089cb39a779fb8 , Question : Decode "I" using cipher key, Type : encode_decode </v>
+      </c>
+      <c r="E135" t="str">
+        <v>18-08-2026 08:24:50 pm</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>6a84724862089cb39a77a19e</v>
+      </c>
+      <c r="B136" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C136" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D136" t="str">
+        <v xml:space="preserve">Created Question Number : 2, Rupees : 30, Qst ID : 6a84724762089cb39a77a18e , Question : How many broken boxes are there?, Type : Total Boxes [Broken] </v>
+      </c>
+      <c r="E136" t="str">
+        <v>18-08-2026 08:25:04 pm</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>6a84724262089cb39a77a0ab</v>
+      </c>
+      <c r="B137" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C137" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D137" t="str">
+        <v>Answerd Correctly to Qst ID : 6a84723962089cb39a779fb8, Reward : 40, Qst No : 2 ,Question : Decode "I" using cipher key</v>
+      </c>
+      <c r="E137" t="str">
+        <v>18-08-2026 08:24:58 pm</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>6a84724862089cb39a77a1a0</v>
+      </c>
+      <c r="B138" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C138" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D138" t="str">
+        <v xml:space="preserve">Created Question Number : 2, Rupees : 30, Qst ID : 6a84724762089cb39a77a18e , Question : How many broken boxes are there?, Type : Total Boxes [Broken] </v>
+      </c>
+      <c r="E138" t="str">
+        <v>18-08-2026 08:25:04 pm</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>6a84725b62089cb39a77a375</v>
+      </c>
+      <c r="B139" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C139" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D139" t="str">
+        <v xml:space="preserve">Created Question Number : 3, Rupees : 40, Qst ID : 6a84725b62089cb39a77a365 , Question : How many letters are colored with the WRONG color?, Type : letter_colour_find </v>
+      </c>
+      <c r="E139" t="str">
+        <v>18-08-2026 08:25:23 pm</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>6a84725762089cb39a77a282</v>
+      </c>
+      <c r="B140" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C140" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D140" t="str">
+        <v>Answerd Correctly to Qst ID : 6a84724762089cb39a77a18e, Reward : 30, Qst No : 3 ,Question : How many broken boxes are there?</v>
+      </c>
+      <c r="E140" t="str">
+        <v>18-08-2026 08:25:19 pm</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>6a84725b62089cb39a77a377</v>
+      </c>
+      <c r="B141" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C141" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D141" t="str">
+        <v xml:space="preserve">Created Question Number : 3, Rupees : 40, Qst ID : 6a84725b62089cb39a77a365 , Question : How many letters are colored with the WRONG color?, Type : letter_colour_find </v>
+      </c>
+      <c r="E141" t="str">
+        <v>18-08-2026 08:25:23 pm</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>6a84726e62089cb39a77a47d</v>
+      </c>
+      <c r="B142" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C142" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D142" t="str">
+        <v xml:space="preserve">Created Question Number : 4, Rupees : 50, Qst ID : 6a84726e62089cb39a77a46d , Question : How many letters are misaligned?, Type : letters_missalign </v>
+      </c>
+      <c r="E142" t="str">
+        <v>18-08-2026 08:25:42 pm</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>6a84726662089cb39a77a459</v>
+      </c>
+      <c r="B143" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C143" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D143" t="str">
+        <v>Answerd Correctly to Qst ID : 6a84725b62089cb39a77a365, Reward : 40, Qst No : 4 ,Question : How many letters are colored with the WRONG color?</v>
+      </c>
+      <c r="E143" t="str">
+        <v>18-08-2026 08:25:34 pm</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>6a84726e62089cb39a77a47f</v>
+      </c>
+      <c r="B144" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C144" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D144" t="str">
+        <v xml:space="preserve">Created Question Number : 4, Rupees : 50, Qst ID : 6a84726e62089cb39a77a46d , Question : How many letters are misaligned?, Type : letters_missalign </v>
+      </c>
+      <c r="E144" t="str">
+        <v>18-08-2026 08:25:42 pm</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>6a84727d62089cb39a77a62d</v>
+      </c>
+      <c r="B145" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C145" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D145" t="str">
+        <v>Answered incorrectly for Qst ID: 6a84726e62089cb39a77a46d, Qst: How many letters are misaligned?, Submitted Answer: 7</v>
+      </c>
+      <c r="E145" t="str">
+        <v>18-08-2026 08:25:57 pm</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>6a84727f62089cb39a77a643</v>
+      </c>
+      <c r="B146" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C146" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D146" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E146" t="str">
+        <v>18-08-2026 08:25:59 pm</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>6a84727f62089cb39a77a649</v>
+      </c>
+      <c r="B147" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C147" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D147" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E147" t="str">
+        <v>18-08-2026 08:25:59 pm</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>6a851f1962089cb39a77f7ee</v>
+      </c>
+      <c r="B148" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C148" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D148" t="str">
+        <v>Started Playing game and Debited "10" and Balance "880"</v>
+      </c>
+      <c r="E148" t="str">
+        <v>19-08-2026 08:42:25 am</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>6a851f3562089cb39a77fa86</v>
+      </c>
+      <c r="B149" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C149" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D149" t="str">
+        <v>Answered incorrectly for Qst ID: 6a851f1b62089cb39a77f7f8, Qst: How many boxes are unbroken in total?, Submitted Answer: 21</v>
+      </c>
+      <c r="E149" t="str">
+        <v>19-08-2026 08:42:53 am</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>6a851f3762089cb39a77fa9b</v>
+      </c>
+      <c r="B150" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C150" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D150" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E150" t="str">
+        <v>19-08-2026 08:42:55 am</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>6a851f3862089cb39a77faa1</v>
+      </c>
+      <c r="B151" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C151" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D151" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E151" t="str">
+        <v>19-08-2026 08:42:56 am</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>6a851f5a62089cb39a77fd23</v>
+      </c>
+      <c r="B152" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C152" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D152" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E152" t="str">
+        <v>19-08-2026 08:43:30 am</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>6a851f5b62089cb39a77fd29</v>
+      </c>
+      <c r="B153" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C153" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D153" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E153" t="str">
+        <v>19-08-2026 08:43:31 am</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>6a851f6262089cb39a77fec2</v>
+      </c>
+      <c r="B154" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C154" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D154" t="str">
+        <v>Started Playing game and Debited "10" and Balance "870"</v>
+      </c>
+      <c r="E154" t="str">
+        <v>19-08-2026 08:43:38 am</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>6a851f6362089cb39a77fec8</v>
+      </c>
+      <c r="B155" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C155" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D155" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E155" t="str">
+        <v>19-08-2026 08:43:39 am</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>6a851f7062089cb39a780094</v>
+      </c>
+      <c r="B156" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C156" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D156" t="str">
+        <v>Answerd Correctly to Qst ID : 6a851f6462089cb39a77fed2, Reward : 10, Qst No : 1 ,Question : How many puzzle pieces contain 2 or more MALE connectors (outward tabs)?</v>
+      </c>
+      <c r="E156" t="str">
+        <v>19-08-2026 08:43:52 am</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>6a851f7662089cb39a7800ab</v>
+      </c>
+      <c r="B157" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C157" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D157" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6a851f7562089cb39a7800a3 , Question : How many letters are misaligned?, Type : letters_missalign </v>
+      </c>
+      <c r="E157" t="str">
+        <v>19-08-2026 08:43:58 am</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>6a851f8162089cb39a780191</v>
+      </c>
+      <c r="B158" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C158" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D158" t="str">
+        <v>Answerd Correctly to Qst ID : 6a851f7562089cb39a7800a3, Reward : 40, Qst No : 2 ,Question : How many letters are misaligned?</v>
+      </c>
+      <c r="E158" t="str">
+        <v>19-08-2026 08:44:09 am</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>6a851f8a62089cb39a780279</v>
+      </c>
+      <c r="B159" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C159" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D159" t="str">
+        <v xml:space="preserve">Created Question Number : 2, Rupees : 30, Qst ID : 6a851f8962089cb39a780271 , Question : Decode "B" using cipher key, Type : encode_decode </v>
+      </c>
+      <c r="E159" t="str">
+        <v>19-08-2026 08:44:18 am</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>6a851f9162089cb39a78035f</v>
+      </c>
+      <c r="B160" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C160" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D160" t="str">
+        <v>Answerd Correctly to Qst ID : 6a851f8962089cb39a780271, Reward : 30, Qst No : 3 ,Question : Decode "B" using cipher key</v>
+      </c>
+      <c r="E160" t="str">
+        <v>19-08-2026 08:44:25 am</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>6a851f9662089cb39a780376</v>
+      </c>
+      <c r="B161" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C161" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D161" t="str">
+        <v xml:space="preserve">Created Question Number : 3, Rupees : 40, Qst ID : 6a851f9562089cb39a78036e , Question : What is the alphabetical arrangement of these random letters: "fom"?, Type : re_arrange_letters </v>
+      </c>
+      <c r="E161" t="str">
+        <v>19-08-2026 08:44:30 am</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>6a851fa262089cb39a78052d</v>
+      </c>
+      <c r="B162" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C162" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D162" t="str">
+        <v>Answerd Correctly to Qst ID : 6a851f9562089cb39a78036e, Reward : 40, Qst No : 4 ,Question : What is the alphabetical arrangement of these random letters: "fom"?</v>
+      </c>
+      <c r="E162" t="str">
+        <v>19-08-2026 08:44:42 am</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>6a851fa762089cb39a780544</v>
+      </c>
+      <c r="B163" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C163" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D163" t="str">
+        <v xml:space="preserve">Created Question Number : 4, Rupees : 50, Qst ID : 6a851fa662089cb39a78053c , Question : How many colour names match their text colour out of 12?, Type : [Colours &amp; Name Match] </v>
+      </c>
+      <c r="E163" t="str">
+        <v>19-08-2026 08:44:47 am</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>6a851fb762089cb39a7806fb</v>
+      </c>
+      <c r="B164" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C164" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D164" t="str">
+        <v>Answerd Correctly to Qst ID : 6a851fa662089cb39a78053c, Reward : 50, Qst No : 5 ,Question : How many colour names match their text colour out of 12?</v>
+      </c>
+      <c r="E164" t="str">
+        <v>19-08-2026 08:45:03 am</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>6a85335562089cb39a786030</v>
+      </c>
+      <c r="B165" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C165" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D165" t="str">
+        <v>Game quit at question 6; reward collected: "50"</v>
+      </c>
+      <c r="E165" t="str">
+        <v>19-08-2026 10:08:45 am</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>6a85348f483a080e922e5314</v>
+      </c>
+      <c r="B166" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C166" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D166" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E166" t="str">
+        <v>19-08-2026 10:13:59 am</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>6a85348f483a080e922e531a</v>
+      </c>
+      <c r="B167" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C167" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D167" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E167" t="str">
+        <v>19-08-2026 10:13:59 am</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>6a853a102ad846076af9fa41</v>
+      </c>
+      <c r="B168" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C168" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D168" t="str">
+        <v>Started Playing game and Debited "10" and Balance "860"</v>
+      </c>
+      <c r="E168" t="str">
+        <v>19-08-2026 10:37:28 am</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>6a853da62ad846076afa4361</v>
+      </c>
+      <c r="B169" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C169" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D169" t="str">
+        <v>Started Playing game and Debited "10" and Balance "850"</v>
+      </c>
+      <c r="E169" t="str">
+        <v>19-08-2026 10:52:46 am</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>6a853da72ad846076afa4367</v>
+      </c>
+      <c r="B170" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C170" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D170" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E170" t="str">
+        <v>19-08-2026 10:52:47 am</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>6a853dd02ad846076afa46dd</v>
+      </c>
+      <c r="B171" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C171" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D171" t="str">
+        <v>Answerd Correctly to Qst ID : 6a853da82ad846076afa4371, Reward : 10, Qst No : 1 ,Question : How many words are scrambled?</v>
+      </c>
+      <c r="E171" t="str">
+        <v>19-08-2026 10:53:28 am</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>6a853dd62ad846076afa46f4</v>
+      </c>
+      <c r="B172" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C172" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D172" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6a853dd62ad846076afa46ec , Question : How many letters are colored with the WRONG color?, Type : letter_colour_find </v>
+      </c>
+      <c r="E172" t="str">
+        <v>19-08-2026 10:53:34 am</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>6a853dde2ad846076afa47dc</v>
+      </c>
+      <c r="B173" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C173" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D173" t="str">
+        <v>Answerd Correctly to Qst ID : 6a853dd62ad846076afa46ec, Reward : 40, Qst No : 2 ,Question : How many letters are colored with the WRONG color?</v>
+      </c>
+      <c r="E173" t="str">
+        <v>19-08-2026 10:53:42 am</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>6a853deb2ad846076afa48c8</v>
+      </c>
+      <c r="B174" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C174" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D174" t="str">
+        <v xml:space="preserve">Created Question Number : 2, Rupees : 30, Qst ID : 6a853dea2ad846076afa48c0 , Question : How many words are colored with the WRONG color?, Type : word_colour_find </v>
+      </c>
+      <c r="E174" t="str">
+        <v>19-08-2026 10:53:55 am</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>6a853df32ad846076afa49b0</v>
+      </c>
+      <c r="B175" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C175" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D175" t="str">
+        <v>Answerd Correctly to Qst ID : 6a853dea2ad846076afa48c0, Reward : 30, Qst No : 3 ,Question : How many words are colored with the WRONG color?</v>
+      </c>
+      <c r="E175" t="str">
+        <v>19-08-2026 10:54:03 am</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>6a853df72ad846076afa4a9a</v>
+      </c>
+      <c r="B176" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C176" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D176" t="str">
+        <v xml:space="preserve">Created Question Number : 3, Rupees : 40, Qst ID : 6a853df62ad846076afa49bf , Question : Decode "X" using cipher key, Type : encode_decode </v>
+      </c>
+      <c r="E176" t="str">
+        <v>19-08-2026 10:54:07 am</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>6a853e012ad846076afa4b82</v>
+      </c>
+      <c r="B177" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C177" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D177" t="str">
+        <v>Answerd Correctly to Qst ID : 6a853df62ad846076afa49bf, Reward : 40, Qst No : 4 ,Question : Decode "X" using cipher key</v>
+      </c>
+      <c r="E177" t="str">
+        <v>19-08-2026 10:54:17 am</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>6a853e052ad846076afa4b99</v>
+      </c>
+      <c r="B178" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C178" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D178" t="str">
+        <v xml:space="preserve">Created Question Number : 4, Rupees : 50, Qst ID : 6a853e042ad846076afa4b91 , Question : How many puzzle pieces contain 2 or more MALE connectors (outward tabs)?, Type : puzle_peace_male_female </v>
+      </c>
+      <c r="E178" t="str">
+        <v>19-08-2026 10:54:21 am</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>6a853e112ad846076afa4c81</v>
+      </c>
+      <c r="B179" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C179" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D179" t="str">
+        <v>Answerd Correctly to Qst ID : 6a853e042ad846076afa4b91, Reward : 50, Qst No : 5 ,Question : How many puzzle pieces contain 2 or more MALE connectors (outward tabs)?</v>
+      </c>
+      <c r="E179" t="str">
+        <v>19-08-2026 10:54:33 am</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>6a85471ecb75b33514f7c3cc</v>
+      </c>
+      <c r="B180" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C180" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D180" t="str">
+        <v xml:space="preserve">Created Question Number : 5, Rupees : 80, Qst ID : 6a85471dcb75b33514f7c3c4 , Question : How many broken boxes are there?, Type : Total Boxes [Broken] </v>
+      </c>
+      <c r="E180" t="str">
+        <v>19-08-2026 11:33:10 am</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>6a854730cb75b33514f7c584</v>
+      </c>
+      <c r="B181" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C181" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D181" t="str">
+        <v>Answered incorrectly for Qst ID: 6a85471dcb75b33514f7c3c4, Qst: How many broken boxes are there?, Submitted Answer: 25</v>
+      </c>
+      <c r="E181" t="str">
+        <v>19-08-2026 11:33:28 am</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>6a854732cb75b33514f7c596</v>
+      </c>
+      <c r="B182" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C182" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D182" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E182" t="str">
+        <v>19-08-2026 11:33:30 am</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>6a854733cb75b33514f7c59c</v>
+      </c>
+      <c r="B183" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C183" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D183" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E183" t="str">
+        <v>19-08-2026 11:33:31 am</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>6a8562b4cb75b33514f91bb6</v>
+      </c>
+      <c r="B184" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C184" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D184" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E184" t="str">
+        <v>19-08-2026 01:30:52 pm</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>6a8562b4cb75b33514f91bbd</v>
+      </c>
+      <c r="B185" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C185" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D185" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E185" t="str">
+        <v>19-08-2026 01:30:52 pm</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>6a856326cb75b33514f9259b</v>
+      </c>
+      <c r="B186" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C186" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D186" t="str">
+        <v>Started Playing game and Debited "10" and Balance "840"</v>
+      </c>
+      <c r="E186" t="str">
+        <v>19-08-2026 01:32:46 pm</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>6a856327cb75b33514f925a1</v>
+      </c>
+      <c r="B187" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C187" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D187" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E187" t="str">
+        <v>19-08-2026 01:32:47 pm</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>6a8564d7cb75b33514f947da</v>
+      </c>
+      <c r="B188" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C188" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D188" t="str">
+        <v>Answered incorrectly for Qst ID: 6a856328cb75b33514f925ab, Qst: How many colour names match their text colour out of 12?, Submitted Answer: 5</v>
+      </c>
+      <c r="E188" t="str">
+        <v>19-08-2026 01:39:59 pm</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>6a856636cb75b33514f96421</v>
+      </c>
+      <c r="B189" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C189" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D189" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E189" t="str">
+        <v>19-08-2026 01:45:50 pm</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>6a856637cb75b33514f96428</v>
+      </c>
+      <c r="B190" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C190" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D190" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E190" t="str">
+        <v>19-08-2026 01:45:51 pm</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>6a85663dcb75b33514f965ca</v>
+      </c>
+      <c r="B191" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C191" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D191" t="str">
+        <v>Started Playing game and Debited "10" and Balance "830"</v>
+      </c>
+      <c r="E191" t="str">
+        <v>19-08-2026 01:45:57 pm</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>6a85663dcb75b33514f965d0</v>
+      </c>
+      <c r="B192" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C192" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D192" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E192" t="str">
+        <v>19-08-2026 01:45:57 pm</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>6a856643cb75b33514f965f7</v>
+      </c>
+      <c r="B193" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C193" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D193" t="str">
+        <v>Answered incorrectly for Qst ID: 6a85663ecb75b33514f965da, Qst: What is the alphabetical arrangement of these random letters: "myd"?, Submitted Answer: 307</v>
+      </c>
+      <c r="E193" t="str">
+        <v>19-08-2026 01:46:03 pm</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>6a85666ccb75b33514f96963</v>
+      </c>
+      <c r="B194" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C194" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D194" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E194" t="str">
+        <v>19-08-2026 01:46:44 pm</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>6a85666dcb75b33514f96969</v>
+      </c>
+      <c r="B195" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C195" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D195" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E195" t="str">
+        <v>19-08-2026 01:46:45 pm</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>6a856673cb75b33514f96b0c</v>
+      </c>
+      <c r="B196" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C196" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D196" t="str">
+        <v>Started Playing game and Debited "10" and Balance "820"</v>
+      </c>
+      <c r="E196" t="str">
+        <v>19-08-2026 01:46:51 pm</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>6a856674cb75b33514f96b12</v>
+      </c>
+      <c r="B197" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C197" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D197" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E197" t="str">
+        <v>19-08-2026 01:46:52 pm</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>6a856682cb75b33514f96c0f</v>
+      </c>
+      <c r="B198" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C198" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D198" t="str">
+        <v>Answered incorrectly for Qst ID: 6a856674cb75b33514f96b1c, Qst: What is the alphabetical arrangement of these random letters: "ucv"?, Submitted Answer: 210</v>
+      </c>
+      <c r="E198" t="str">
+        <v>19-08-2026 01:47:06 pm</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>6a856697cb75b33514f96dcc</v>
+      </c>
+      <c r="B199" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C199" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D199" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E199" t="str">
+        <v>19-08-2026 01:47:27 pm</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>6a856698cb75b33514f96dd3</v>
+      </c>
+      <c r="B200" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C200" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D200" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E200" t="str">
+        <v>19-08-2026 01:47:28 pm</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>6a8566a8cb75b33514f9704e</v>
+      </c>
+      <c r="B201" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C201" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D201" t="str">
+        <v>Started Playing game and Debited "10" and Balance "810"</v>
+      </c>
+      <c r="E201" t="str">
+        <v>19-08-2026 01:47:44 pm</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>6a8566a9cb75b33514f97054</v>
+      </c>
+      <c r="B202" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C202" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D202" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E202" t="str">
+        <v>19-08-2026 01:47:45 pm</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>6a8566b1cb75b33514f97152</v>
+      </c>
+      <c r="B203" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C203" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D203" t="str">
+        <v>Answered incorrectly for Qst ID: 6a8566a9cb75b33514f9705e, Qst: How many letters are colored with the WRONG color?, Submitted Answer: 2</v>
+      </c>
+      <c r="E203" t="str">
+        <v>19-08-2026 01:47:53 pm</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>6a8566c7cb75b33514f97311</v>
+      </c>
+      <c r="B204" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C204" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D204" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E204" t="str">
+        <v>19-08-2026 01:48:15 pm</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>6a8566c9cb75b33514f9731a</v>
+      </c>
+      <c r="B205" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C205" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D205" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E205" t="str">
+        <v>19-08-2026 01:48:17 pm</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>6a856725cb75b33514f97b7b</v>
+      </c>
+      <c r="B206" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C206" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D206" t="str">
+        <v>Started Playing game and Debited "10" and Balance "800"</v>
+      </c>
+      <c r="E206" t="str">
+        <v>19-08-2026 01:49:49 pm</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>6a856725cb75b33514f97b81</v>
+      </c>
+      <c r="B207" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C207" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D207" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E207" t="str">
+        <v>19-08-2026 01:49:49 pm</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>6a856831cb75b33514f990c2</v>
+      </c>
+      <c r="B208" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C208" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D208" t="str">
+        <v>Answered incorrectly for Qst ID: 6a856726cb75b33514f97b8b, Qst: How many times do the letters H, P, X, S, W appear in the paragraph?, Submitted Answer: 6</v>
+      </c>
+      <c r="E208" t="str">
+        <v>19-08-2026 01:54:17 pm</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>6a856846cb75b33514f99283</v>
+      </c>
+      <c r="B209" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C209" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D209" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E209" t="str">
+        <v>19-08-2026 01:54:38 pm</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>6a856846cb75b33514f992b2</v>
+      </c>
+      <c r="B210" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C210" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D210" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E210" t="str">
+        <v>19-08-2026 01:54:38 pm</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>6a85686bcb75b33514f996be</v>
+      </c>
+      <c r="B211" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C211" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D211" t="str">
+        <v>Started Playing game and Debited "10" and Balance "790"</v>
+      </c>
+      <c r="E211" t="str">
+        <v>19-08-2026 01:55:15 pm</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>6a85686ccb75b33514f996c4</v>
+      </c>
+      <c r="B212" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C212" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D212" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E212" t="str">
+        <v>19-08-2026 01:55:16 pm</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>6a856871cb75b33514f997c4</v>
+      </c>
+      <c r="B213" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C213" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D213" t="str">
+        <v>Answered incorrectly for Qst ID: 6a85686dcb75b33514f996ce, Qst: How many words are colored with the WRONG color?, Submitted Answer: 1</v>
+      </c>
+      <c r="E213" t="str">
+        <v>19-08-2026 01:55:21 pm</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>6a856a34cb75b33514f9bc4f</v>
+      </c>
+      <c r="B214" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C214" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D214" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E214" t="str">
+        <v>19-08-2026 02:02:52 pm</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>6a856a34cb75b33514f9bc55</v>
+      </c>
+      <c r="B215" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C215" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D215" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E215" t="str">
+        <v>19-08-2026 02:02:52 pm</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>6a856a3acb75b33514f9bd27</v>
+      </c>
+      <c r="B216" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C216" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D216" t="str">
+        <v>Started Playing game and Debited "10" and Balance "780"</v>
+      </c>
+      <c r="E216" t="str">
+        <v>19-08-2026 02:02:58 pm</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>6a856a3bcb75b33514f9bd30</v>
+      </c>
+      <c r="B217" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C217" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D217" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E217" t="str">
+        <v>19-08-2026 02:02:59 pm</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>6a856a5ecb75b33514f9c0bc</v>
+      </c>
+      <c r="B218" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C218" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D218" t="str">
+        <v>Answered incorrectly for Qst ID: 6a856a3bcb75b33514f9be11, Qst: How many times does the letter sequence 'avi' appear in the given words?, Submitted Answer: 2</v>
+      </c>
+      <c r="E218" t="str">
+        <v>19-08-2026 02:03:34 pm</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>6a856d9ccb75b33514fa0520</v>
+      </c>
+      <c r="B219" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C219" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D219" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E219" t="str">
+        <v>19-08-2026 02:17:24 pm</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>6a856d9ccb75b33514fa0526</v>
+      </c>
+      <c r="B220" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C220" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D220" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E220" t="str">
+        <v>19-08-2026 02:17:24 pm</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>6a856da2cb75b33514fa05f9</v>
+      </c>
+      <c r="B221" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C221" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D221" t="str">
+        <v>Started Playing game and Debited "10" and Balance "770"</v>
+      </c>
+      <c r="E221" t="str">
+        <v>19-08-2026 02:17:30 pm</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>6a856da2cb75b33514fa05ff</v>
+      </c>
+      <c r="B222" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C222" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D222" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E222" t="str">
+        <v>19-08-2026 02:17:30 pm</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>6a856da7cb75b33514fa0701</v>
+      </c>
+      <c r="B223" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C223" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D223" t="str">
+        <v>Answered incorrectly for Qst ID: 6a856da3cb75b33514fa0609, Qst: How many times do the letters P, H, G, S, Y appear in the paragraph?, Submitted Answer: 4</v>
+      </c>
+      <c r="E223" t="str">
+        <v>19-08-2026 02:17:35 pm</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>6a856e71cb75b33514fa1757</v>
+      </c>
+      <c r="B224" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C224" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D224" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E224" t="str">
+        <v>19-08-2026 02:20:57 pm</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>6a856e71cb75b33514fa175e</v>
+      </c>
+      <c r="B225" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C225" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D225" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E225" t="str">
+        <v>19-08-2026 02:20:57 pm</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>6a856e7ecb75b33514fa19e9</v>
+      </c>
+      <c r="B226" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C226" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D226" t="str">
+        <v>Started Playing game and Debited "10" and Balance "760"</v>
+      </c>
+      <c r="E226" t="str">
+        <v>19-08-2026 02:21:10 pm</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>6a856e7ecb75b33514fa19ef</v>
+      </c>
+      <c r="B227" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C227" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D227" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E227" t="str">
+        <v>19-08-2026 02:21:10 pm</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>6a856e83cb75b33514fa1a16</v>
+      </c>
+      <c r="B228" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C228" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D228" t="str">
+        <v>Answered incorrectly for Qst ID: 6a856e7fcb75b33514fa19f9, Qst: How many letters are colored with the WRONG color?, Submitted Answer: 2</v>
+      </c>
+      <c r="E228" t="str">
+        <v>19-08-2026 02:21:15 pm</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>6a856e97cb75b33514fa1be0</v>
+      </c>
+      <c r="B229" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C229" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D229" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E229" t="str">
+        <v>19-08-2026 02:21:35 pm</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>6a856e97cb75b33514fa1be6</v>
+      </c>
+      <c r="B230" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C230" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D230" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E230" t="str">
+        <v>19-08-2026 02:21:35 pm</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>6a856fdacb75b33514fa3760</v>
+      </c>
+      <c r="B231" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C231" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D231" t="str">
+        <v>Started Playing game and Debited "10" and Balance "750"</v>
+      </c>
+      <c r="E231" t="str">
+        <v>19-08-2026 02:26:58 pm</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>6a856fdacb75b33514fa3766</v>
+      </c>
+      <c r="B232" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C232" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D232" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E232" t="str">
+        <v>19-08-2026 02:26:58 pm</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>6a856fe4cb75b33514fa386d</v>
+      </c>
+      <c r="B233" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C233" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D233" t="str">
+        <v>Answerd Correctly to Qst ID : 6a856fdccb75b33514fa3770, Reward : 10, Qst No : 2 ,Question : How many words are scrambled?</v>
+      </c>
+      <c r="E233" t="str">
+        <v>19-08-2026 02:27:08 pm</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>6a856feccb75b33514fa3961</v>
+      </c>
+      <c r="B234" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C234" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D234" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6a856febcb75b33514fa3959 , Question : How many letters are colored with the WRONG color?, Type : letter_colour_find </v>
+      </c>
+      <c r="E234" t="str">
+        <v>19-08-2026 02:27:16 pm</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>6a856ff0cb75b33514fa3973</v>
+      </c>
+      <c r="B235" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C235" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D235" t="str">
+        <v>Answered incorrectly for Qst ID: 6a856febcb75b33514fa3959, Qst: How many letters are colored with the WRONG color?, Submitted Answer: 2</v>
+      </c>
+      <c r="E235" t="str">
+        <v>19-08-2026 02:27:20 pm</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="str">
+        <v>6a85729bcb75b33514fa7293</v>
+      </c>
+      <c r="B236" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C236" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D236" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E236" t="str">
+        <v>19-08-2026 02:38:43 pm</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>6a85729bcb75b33514fa7299</v>
+      </c>
+      <c r="B237" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C237" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D237" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E237" t="str">
+        <v>19-08-2026 02:38:43 pm</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>6a8572a2cb75b33514fa736f</v>
+      </c>
+      <c r="B238" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C238" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D238" t="str">
+        <v>Started Playing game and Debited "10" and Balance "740"</v>
+      </c>
+      <c r="E238" t="str">
+        <v>19-08-2026 02:38:50 pm</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>6a8572a3cb75b33514fa7375</v>
+      </c>
+      <c r="B239" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C239" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D239" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E239" t="str">
+        <v>19-08-2026 02:38:51 pm</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>6a8572c9cb75b33514fa7726</v>
+      </c>
+      <c r="B240" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C240" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D240" t="str">
+        <v>Answered incorrectly for Qst ID: 6a8572a3cb75b33514fa737f, Qst: What is the alphabetical arrangement of these random letters: "pkz"?, Submitted Answer: 208</v>
+      </c>
+      <c r="E240" t="str">
+        <v>19-08-2026 02:39:29 pm</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>6a8572d9cb75b33514fa78f8</v>
+      </c>
+      <c r="B241" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C241" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D241" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E241" t="str">
+        <v>19-08-2026 02:39:45 pm</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>6a8572dacb75b33514fa7900</v>
+      </c>
+      <c r="B242" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C242" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D242" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E242" t="str">
+        <v>19-08-2026 02:39:46 pm</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>6a8573ffcb75b33514fa9161</v>
+      </c>
+      <c r="B243" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C243" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D243" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E243" t="str">
+        <v>19-08-2026 02:44:39 pm</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>6a8573ffcb75b33514fa9167</v>
+      </c>
+      <c r="B244" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C244" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D244" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E244" t="str">
+        <v>19-08-2026 02:44:39 pm</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>6a85740bcb75b33514fa931c</v>
+      </c>
+      <c r="B245" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C245" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D245" t="str">
+        <v>Started Playing game and Debited "10" and Balance "730"</v>
+      </c>
+      <c r="E245" t="str">
+        <v>19-08-2026 02:44:51 pm</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>6a857433cb75b33514fa96d8</v>
+      </c>
+      <c r="B246" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C246" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D246" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E246" t="str">
+        <v>19-08-2026 02:45:31 pm</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>6a85740bcb75b33514fa9322</v>
+      </c>
+      <c r="B247" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C247" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D247" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E247" t="str">
+        <v>19-08-2026 02:44:51 pm</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="str">
+        <v>6a857578cb75b33514fab2eb</v>
+      </c>
+      <c r="B248" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C248" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D248" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E248" t="str">
+        <v>19-08-2026 02:50:56 pm</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="str">
+        <v>6a857433cb75b33514fa96da</v>
+      </c>
+      <c r="B249" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C249" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D249" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E249" t="str">
+        <v>19-08-2026 02:45:31 pm</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="str">
+        <v>6a857578cb75b33514fab2f5</v>
+      </c>
+      <c r="B250" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C250" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D250" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E250" t="str">
+        <v>19-08-2026 02:50:56 pm</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="str">
+        <v>6a857578cb75b33514fab2ed</v>
+      </c>
+      <c r="B251" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C251" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D251" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E251" t="str">
+        <v>19-08-2026 02:50:56 pm</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="str">
+        <v>6a857578cb75b33514fab2f8</v>
+      </c>
+      <c r="B252" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C252" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D252" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E252" t="str">
+        <v>19-08-2026 02:50:56 pm</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="str">
+        <v>6a857842cb75b33514fae91a</v>
+      </c>
+      <c r="B253" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C253" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D253" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E253" t="str">
+        <v>19-08-2026 03:02:50 pm</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="str">
+        <v>6a857842cb75b33514fae920</v>
+      </c>
+      <c r="B254" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C254" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D254" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E254" t="str">
+        <v>19-08-2026 03:02:50 pm</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="str">
+        <v>6a857848cb75b33514faead8</v>
+      </c>
+      <c r="B255" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C255" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D255" t="str">
+        <v>Started Playing game and Debited "10" and Balance "720"</v>
+      </c>
+      <c r="E255" t="str">
+        <v>19-08-2026 03:02:56 pm</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="str">
+        <v>6a857849cb75b33514faeade</v>
+      </c>
+      <c r="B256" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C256" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D256" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E256" t="str">
+        <v>19-08-2026 03:02:57 pm</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="str">
+        <v>6a85784fcb75b33514faeb05</v>
+      </c>
+      <c r="B257" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C257" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D257" t="str">
+        <v>Answered incorrectly for Qst ID: 6a857849cb75b33514faeae8, Qst: How many boxes are unbroken in total?, Submitted Answer: 22</v>
+      </c>
+      <c r="E257" t="str">
+        <v>19-08-2026 03:03:03 pm</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="str">
+        <v>6a857ae8cb75b33514fb231a</v>
+      </c>
+      <c r="B258" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C258" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D258" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E258" t="str">
+        <v>19-08-2026 03:14:08 pm</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="str">
+        <v>6a857ae9cb75b33514fb2320</v>
+      </c>
+      <c r="B259" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C259" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D259" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E259" t="str">
+        <v>19-08-2026 03:14:09 pm</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="str">
+        <v>6a857aeecb75b33514fb23f9</v>
+      </c>
+      <c r="B260" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C260" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D260" t="str">
+        <v>Started Playing game and Debited "10" and Balance "710"</v>
+      </c>
+      <c r="E260" t="str">
+        <v>19-08-2026 03:14:14 pm</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="str">
+        <v>6a857aeecb75b33514fb24e0</v>
+      </c>
+      <c r="B261" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C261" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D261" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E261" t="str">
+        <v>19-08-2026 03:14:14 pm</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="str">
+        <v>6a857af3cb75b33514fb2507</v>
+      </c>
+      <c r="B262" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C262" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D262" t="str">
+        <v>Answered incorrectly for Qst ID: 6a857aefcb75b33514fb24ea, Qst: How many letters are colored with the WRONG color?, Submitted Answer: 3</v>
+      </c>
+      <c r="E262" t="str">
+        <v>19-08-2026 03:14:19 pm</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>6a857ca8cb75b33514fb4a05</v>
+      </c>
+      <c r="B263" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C263" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D263" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E263" t="str">
+        <v>19-08-2026 03:21:36 pm</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>6a857ca8cb75b33514fb4a0b</v>
+      </c>
+      <c r="B264" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C264" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D264" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E264" t="str">
+        <v>19-08-2026 03:21:36 pm</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="str">
+        <v>6a857caecb75b33514fb4bc7</v>
+      </c>
+      <c r="B265" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C265" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D265" t="str">
+        <v>Started Playing game and Debited "10" and Balance "700"</v>
+      </c>
+      <c r="E265" t="str">
+        <v>19-08-2026 03:21:42 pm</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="str">
+        <v>6a857cafcb75b33514fb4bcd</v>
+      </c>
+      <c r="B266" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C266" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D266" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E266" t="str">
+        <v>19-08-2026 03:21:43 pm</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="str">
+        <v>6a857cb3cb75b33514fb4bf4</v>
+      </c>
+      <c r="B267" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C267" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D267" t="str">
+        <v>Answered incorrectly for Qst ID: 6a857cafcb75b33514fb4bd7, Qst: How many words are scrambled?, Submitted Answer: 2</v>
+      </c>
+      <c r="E267" t="str">
+        <v>19-08-2026 03:21:47 pm</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="str">
+        <v>6a857fbdcb75b33514fb81e2</v>
+      </c>
+      <c r="B268" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C268" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D268" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E268" t="str">
+        <v>19-08-2026 03:34:45 pm</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>6a857fbecb75b33514fb81e8</v>
+      </c>
+      <c r="B269" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C269" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D269" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E269" t="str">
+        <v>19-08-2026 03:34:46 pm</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="str">
+        <v>6a857fc3cb75b33514fb82db</v>
+      </c>
+      <c r="B270" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C270" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D270" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E270" t="str">
+        <v>19-08-2026 03:34:51 pm</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="str">
+        <v>6a857fc4cb75b33514fb82e1</v>
+      </c>
+      <c r="B271" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C271" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D271" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E271" t="str">
+        <v>19-08-2026 03:34:52 pm</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="str">
+        <v>6a857fcdcb75b33514fb849e</v>
+      </c>
+      <c r="B272" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C272" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D272" t="str">
+        <v>Started Playing game and Debited "10" and Balance "690"</v>
+      </c>
+      <c r="E272" t="str">
+        <v>19-08-2026 03:35:01 pm</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="str">
+        <v>6a857fcdcb75b33514fb84a4</v>
+      </c>
+      <c r="B273" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C273" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D273" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E273" t="str">
+        <v>19-08-2026 03:35:01 pm</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="str">
+        <v>6a857fdacb75b33514fb85b1</v>
+      </c>
+      <c r="B274" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C274" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D274" t="str">
+        <v>Answerd Correctly to Qst ID : 6a857fcecb75b33514fb84ae, Reward : 10, Qst No : 2 ,Question : How many letters are colored with the WRONG color?</v>
+      </c>
+      <c r="E274" t="str">
+        <v>19-08-2026 03:35:14 pm</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="str">
+        <v>6a857fddcb75b33514fb85c8</v>
+      </c>
+      <c r="B275" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C275" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D275" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6a857fddcb75b33514fb85c0 , Question : What is the alphabetical arrangement of these random letters: "dds"?, Type : re_arrange_letters </v>
+      </c>
+      <c r="E275" t="str">
+        <v>19-08-2026 03:35:17 pm</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="str">
+        <v>6a857fedcb75b33514fb87a3</v>
+      </c>
+      <c r="B276" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C276" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D276" t="str">
+        <v>Answerd Correctly to Qst ID : 6a857fddcb75b33514fb85c0, Reward : 40, Qst No : 3 ,Question : What is the alphabetical arrangement of these random letters: "dds"?</v>
+      </c>
+      <c r="E276" t="str">
+        <v>19-08-2026 03:35:33 pm</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="str">
+        <v>6a857ff0cb75b33514fb87ba</v>
+      </c>
+      <c r="B277" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C277" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D277" t="str">
+        <v xml:space="preserve">Created Question Number : 2, Rupees : 30, Qst ID : 6a857ff0cb75b33514fb87b2 , Question : How many times does the letter sequence 'sky' appear in the given words?, Type : count_word_exist </v>
+      </c>
+      <c r="E277" t="str">
+        <v>19-08-2026 03:35:36 pm</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="str">
+        <v>6a858002cb75b33514fb8995</v>
+      </c>
+      <c r="B278" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C278" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D278" t="str">
+        <v>Answerd Correctly to Qst ID : 6a857ff0cb75b33514fb87b2, Reward : 30, Qst No : 4 ,Question : How many times does the letter sequence 'sky' appear in the given words?</v>
+      </c>
+      <c r="E278" t="str">
+        <v>19-08-2026 03:35:54 pm</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="str">
+        <v>6a858006cb75b33514fb89ac</v>
+      </c>
+      <c r="B279" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C279" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D279" t="str">
+        <v xml:space="preserve">Created Question Number : 3, Rupees : 40, Qst ID : 6a858006cb75b33514fb89a4 , Question : How many boxes are unbroken in total?, Type : Total Boxes [Comp] </v>
+      </c>
+      <c r="E279" t="str">
+        <v>19-08-2026 03:35:58 pm</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="str">
+        <v>6a858014cb75b33514fb8b87</v>
+      </c>
+      <c r="B280" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C280" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D280" t="str">
+        <v>Answerd Correctly to Qst ID : 6a858006cb75b33514fb89a4, Reward : 40, Qst No : 5 ,Question : How many boxes are unbroken in total?</v>
+      </c>
+      <c r="E280" t="str">
+        <v>19-08-2026 03:36:12 pm</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="str">
+        <v>6a85801ecb75b33514fb8c81</v>
+      </c>
+      <c r="B281" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C281" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D281" t="str">
+        <v xml:space="preserve">Created Question Number : 4, Rupees : 50, Qst ID : 6a85801ecb75b33514fb8c79 , Question : How many words are colored with the WRONG color?, Type : word_colour_find </v>
+      </c>
+      <c r="E281" t="str">
+        <v>19-08-2026 03:36:22 pm</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="str">
+        <v>6a858025cb75b33514fb8c96</v>
+      </c>
+      <c r="B282" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C282" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D282" t="str">
+        <v>Answerd Correctly to Qst ID : 6a85801ecb75b33514fb8c79, Reward : 50, Qst No : 6 ,Question : How many words are colored with the WRONG color?</v>
+      </c>
+      <c r="E282" t="str">
+        <v>19-08-2026 03:36:29 pm</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="str">
+        <v>6a858030cb75b33514fb8d94</v>
+      </c>
+      <c r="B283" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C283" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D283" t="str">
+        <v xml:space="preserve">Created Question Number : 5, Rupees : 80, Qst ID : 6a858030cb75b33514fb8d8c , Question : How many letters are misaligned?, Type : letters_missalign </v>
+      </c>
+      <c r="E283" t="str">
+        <v>19-08-2026 03:36:40 pm</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="str">
+        <v>6a858040cb75b33514fb8f6c</v>
+      </c>
+      <c r="B284" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C284" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D284" t="str">
+        <v>Answered incorrectly for Qst ID: 6a858030cb75b33514fb8d8c, Qst: How many letters are misaligned?, Submitted Answer: 6</v>
+      </c>
+      <c r="E284" t="str">
+        <v>19-08-2026 03:36:56 pm</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="str">
+        <v>6a8580a7cb75b33514fb9866</v>
+      </c>
+      <c r="B285" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C285" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D285" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E285" t="str">
+        <v>19-08-2026 03:38:39 pm</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E92"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E285"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/live-history.xlsx
+++ b/live-history.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E285"/>
+  <dimension ref="A1:E287"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5244,9 +5244,43 @@
         <v>19-08-2026 03:38:39 pm</v>
       </c>
     </row>
+    <row r="286">
+      <c r="A286" t="str">
+        <v>6a85ca43580bee4b55998ab5</v>
+      </c>
+      <c r="B286" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C286" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D286" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E286" t="str">
+        <v>19-08-2026 08:52:43 pm</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="str">
+        <v>6a8580a8cb75b33514fb986c</v>
+      </c>
+      <c r="B287" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C287" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D287" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E287" t="str">
+        <v>19-08-2026 03:38:40 pm</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E285"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E287"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/live-history.xlsx
+++ b/live-history.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E287"/>
+  <dimension ref="A1:E342"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5278,9 +5278,944 @@
         <v>19-08-2026 03:38:40 pm</v>
       </c>
     </row>
+    <row r="288">
+      <c r="A288" t="str">
+        <v>6a85ca43580bee4b55998ab7</v>
+      </c>
+      <c r="B288" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C288" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D288" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E288" t="str">
+        <v>19-08-2026 08:52:43 pm</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="str">
+        <v>6a88102fcda9a07b795ccdcd</v>
+      </c>
+      <c r="B289" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C289" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D289" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E289" t="str">
+        <v>21-08-2026 02:15:35 pm</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="str">
+        <v>6a881030cda9a07b795ccdd3</v>
+      </c>
+      <c r="B290" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C290" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D290" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E290" t="str">
+        <v>21-08-2026 02:15:36 pm</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="str">
+        <v>6a8810b7cda9a07b795cceb1</v>
+      </c>
+      <c r="B291" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C291" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D291" t="str">
+        <v>Started Playing game and Debited "10" and Balance "680"</v>
+      </c>
+      <c r="E291" t="str">
+        <v>21-08-2026 02:17:51 pm</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="str">
+        <v>6a8810b7cda9a07b795cceb7</v>
+      </c>
+      <c r="B292" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C292" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D292" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E292" t="str">
+        <v>21-08-2026 02:17:51 pm</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="str">
+        <v>6a8810eacda9a07b795ccee2</v>
+      </c>
+      <c r="B293" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C293" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D293" t="str">
+        <v>Answerd Correctly to Qst ID : 6a8810b8cda9a07b795ccec1, Reward : 10, Qst No : 2 ,Question : What is the alphabetical arrangement of these random letters: "xdw"?</v>
+      </c>
+      <c r="E293" t="str">
+        <v>21-08-2026 02:18:42 pm</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="str">
+        <v>6a881185cda9a07b795ccefc</v>
+      </c>
+      <c r="B294" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C294" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D294" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6a881185cda9a07b795ccef4 , Question : How many letters are colored with the WRONG color?, Type : letter_colour_find </v>
+      </c>
+      <c r="E294" t="str">
+        <v>21-08-2026 02:21:17 pm</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="str">
+        <v>6a88118fcda9a07b795ccf11</v>
+      </c>
+      <c r="B295" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C295" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D295" t="str">
+        <v>Answerd Correctly to Qst ID : 6a881185cda9a07b795ccef4, Reward : 40, Qst No : 3 ,Question : How many letters are colored with the WRONG color?</v>
+      </c>
+      <c r="E295" t="str">
+        <v>21-08-2026 02:21:27 pm</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="str">
+        <v>6a8811a6cda9a07b795ccf28</v>
+      </c>
+      <c r="B296" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C296" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D296" t="str">
+        <v xml:space="preserve">Created Question Number : 2, Rupees : 30, Qst ID : 6a8811a6cda9a07b795ccf20 , Question : How many words are colored with the WRONG color?, Type : word_colour_find </v>
+      </c>
+      <c r="E296" t="str">
+        <v>21-08-2026 02:21:50 pm</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="str">
+        <v>6a8811b0cda9a07b795ccf3d</v>
+      </c>
+      <c r="B297" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C297" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D297" t="str">
+        <v>Answerd Correctly to Qst ID : 6a8811a6cda9a07b795ccf20, Reward : 30, Qst No : 4 ,Question : How many words are colored with the WRONG color?</v>
+      </c>
+      <c r="E297" t="str">
+        <v>21-08-2026 02:22:00 pm</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="str">
+        <v>6a8811b5cda9a07b795ccf54</v>
+      </c>
+      <c r="B298" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C298" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D298" t="str">
+        <v xml:space="preserve">Created Question Number : 3, Rupees : 40, Qst ID : 6a8811b4cda9a07b795ccf4c , Question : How many colour names match their text colour out of 12?, Type : [Colours &amp; Name Match] </v>
+      </c>
+      <c r="E298" t="str">
+        <v>21-08-2026 02:22:05 pm</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="str">
+        <v>6a8811c7cda9a07b795ccf6a</v>
+      </c>
+      <c r="B299" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C299" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D299" t="str">
+        <v>Answerd Correctly to Qst ID : 6a8811b4cda9a07b795ccf4c, Reward : 40, Qst No : 5 ,Question : How many colour names match their text colour out of 12?</v>
+      </c>
+      <c r="E299" t="str">
+        <v>21-08-2026 02:22:23 pm</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="str">
+        <v>6a8811cccda9a07b795ccf81</v>
+      </c>
+      <c r="B300" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C300" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D300" t="str">
+        <v xml:space="preserve">Created Question Number : 4, Rupees : 50, Qst ID : 6a8811cbcda9a07b795ccf79 , Question : Decode "Z" using cipher key, Type : encode_decode </v>
+      </c>
+      <c r="E300" t="str">
+        <v>21-08-2026 02:22:28 pm</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="str">
+        <v>6a8811d3cda9a07b795ccf96</v>
+      </c>
+      <c r="B301" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C301" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D301" t="str">
+        <v>Answerd Correctly to Qst ID : 6a8811cbcda9a07b795ccf79, Reward : 50, Qst No : 6 ,Question : Decode "Z" using cipher key</v>
+      </c>
+      <c r="E301" t="str">
+        <v>21-08-2026 02:22:35 pm</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="str">
+        <v>6a881279cda9a07b795ccfb4</v>
+      </c>
+      <c r="B302" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C302" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D302" t="str">
+        <v xml:space="preserve">Created Question Number : 5, Rupees : 80, Qst ID : 6a881279cda9a07b795ccfac , Question : How many boxes are unbroken in total?, Type : Total Boxes [Comp] </v>
+      </c>
+      <c r="E302" t="str">
+        <v>21-08-2026 02:25:21 pm</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="str">
+        <v>6a88128acda9a07b795ccfc6</v>
+      </c>
+      <c r="B303" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C303" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D303" t="str">
+        <v>Answered incorrectly for Qst ID: 6a881279cda9a07b795ccfac, Qst: How many boxes are unbroken in total?, Submitted Answer: 13</v>
+      </c>
+      <c r="E303" t="str">
+        <v>21-08-2026 02:25:38 pm</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="str">
+        <v>6a8812aacda9a07b795ccfd8</v>
+      </c>
+      <c r="B304" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C304" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D304" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E304" t="str">
+        <v>21-08-2026 02:26:10 pm</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="str">
+        <v>6a8812abcda9a07b795ccfde</v>
+      </c>
+      <c r="B305" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C305" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D305" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E305" t="str">
+        <v>21-08-2026 02:26:11 pm</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="str">
+        <v>6a8825becda9a07b795cd0f3</v>
+      </c>
+      <c r="B306" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C306" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D306" t="str">
+        <v>Started Playing game and Debited "10" and Balance "670"</v>
+      </c>
+      <c r="E306" t="str">
+        <v>21-08-2026 03:47:34 pm</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="str">
+        <v>6a8825becda9a07b795cd0f9</v>
+      </c>
+      <c r="B307" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C307" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D307" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E307" t="str">
+        <v>21-08-2026 03:47:34 pm</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="str">
+        <v>6a884231f196f265099f1c9c</v>
+      </c>
+      <c r="B308" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C308" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D308" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E308" t="str">
+        <v>21-08-2026 05:48:57 pm</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="str">
+        <v>6a884232f196f265099f1ca4</v>
+      </c>
+      <c r="B309" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C309" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D309" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E309" t="str">
+        <v>21-08-2026 05:48:58 pm</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="str">
+        <v>6a884239f196f265099f1d80</v>
+      </c>
+      <c r="B310" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C310" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D310" t="str">
+        <v>Started Playing game and Debited "10" and Balance "660"</v>
+      </c>
+      <c r="E310" t="str">
+        <v>21-08-2026 05:49:05 pm</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="str">
+        <v>6a88423af196f265099f1d86</v>
+      </c>
+      <c r="B311" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C311" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D311" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E311" t="str">
+        <v>21-08-2026 05:49:06 pm</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="str">
+        <v>6a884254f196f265099f1dad</v>
+      </c>
+      <c r="B312" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C312" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D312" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E312" t="str">
+        <v>21-08-2026 05:49:32 pm</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="str">
+        <v>6a884254f196f265099f1db5</v>
+      </c>
+      <c r="B313" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C313" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D313" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E313" t="str">
+        <v>21-08-2026 05:49:32 pm</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="str">
+        <v>6a88425bf196f265099f1e92</v>
+      </c>
+      <c r="B314" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C314" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D314" t="str">
+        <v>Started Playing game and Debited "10" and Balance "650"</v>
+      </c>
+      <c r="E314" t="str">
+        <v>21-08-2026 05:49:39 pm</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="str">
+        <v>6a88425cf196f265099f1e98</v>
+      </c>
+      <c r="B315" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C315" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D315" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E315" t="str">
+        <v>21-08-2026 05:49:40 pm</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="str">
+        <v>6a884276f196f265099f1ec2</v>
+      </c>
+      <c r="B316" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C316" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D316" t="str">
+        <v>Answerd Correctly to Qst ID : 6a88425df196f265099f1ea2, Reward : 10, Qst No : 2 ,Question : How many boxes are unbroken in total?</v>
+      </c>
+      <c r="E316" t="str">
+        <v>21-08-2026 05:50:06 pm</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="str">
+        <v>6a88428af196f265099f1ed9</v>
+      </c>
+      <c r="B317" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C317" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D317" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6a884289f196f265099f1ed1 , Question : What is the alphabetical arrangement of these random letters: "kbn"?, Type : re_arrange_letters </v>
+      </c>
+      <c r="E317" t="str">
+        <v>21-08-2026 05:50:26 pm</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="str">
+        <v>6a884295f196f265099f1eef</v>
+      </c>
+      <c r="B318" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C318" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D318" t="str">
+        <v>Answerd Correctly to Qst ID : 6a884289f196f265099f1ed1, Reward : 40, Qst No : 3 ,Question : What is the alphabetical arrangement of these random letters: "kbn"?</v>
+      </c>
+      <c r="E318" t="str">
+        <v>21-08-2026 05:50:37 pm</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="str">
+        <v>6a88429cf196f265099f1f06</v>
+      </c>
+      <c r="B319" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C319" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D319" t="str">
+        <v xml:space="preserve">Created Question Number : 2, Rupees : 30, Qst ID : 6a88429bf196f265099f1efe , Question : Decode "V" using cipher key, Type : encode_decode </v>
+      </c>
+      <c r="E319" t="str">
+        <v>21-08-2026 05:50:44 pm</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="str">
+        <v>6a8842a6f196f265099f1f1b</v>
+      </c>
+      <c r="B320" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C320" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D320" t="str">
+        <v>Answerd Correctly to Qst ID : 6a88429bf196f265099f1efe, Reward : 30, Qst No : 4 ,Question : Decode "V" using cipher key</v>
+      </c>
+      <c r="E320" t="str">
+        <v>21-08-2026 05:50:54 pm</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="str">
+        <v>6a8842aaf196f265099f1f32</v>
+      </c>
+      <c r="B321" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C321" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D321" t="str">
+        <v xml:space="preserve">Created Question Number : 3, Rupees : 40, Qst ID : 6a8842a9f196f265099f1f2a , Question : How many puzzle pieces contain 2 or more MALE connectors (outward tabs)?, Type : puzle_peace_male_female </v>
+      </c>
+      <c r="E321" t="str">
+        <v>21-08-2026 05:50:58 pm</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="str">
+        <v>6a8842b6f196f265099f1f47</v>
+      </c>
+      <c r="B322" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C322" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D322" t="str">
+        <v>Answerd Correctly to Qst ID : 6a8842a9f196f265099f1f2a, Reward : 40, Qst No : 5 ,Question : How many puzzle pieces contain 2 or more MALE connectors (outward tabs)?</v>
+      </c>
+      <c r="E322" t="str">
+        <v>21-08-2026 05:51:10 pm</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="str">
+        <v>6a8842bdf196f265099f1f5e</v>
+      </c>
+      <c r="B323" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C323" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D323" t="str">
+        <v xml:space="preserve">Created Question Number : 4, Rupees : 50, Qst ID : 6a8842bcf196f265099f1f56 , Question : How many words are scrambled?, Type : scramble_words </v>
+      </c>
+      <c r="E323" t="str">
+        <v>21-08-2026 05:51:17 pm</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="str">
+        <v>6a8842d2f196f265099f1f74</v>
+      </c>
+      <c r="B324" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C324" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D324" t="str">
+        <v>Answerd Correctly to Qst ID : 6a8842bcf196f265099f1f56, Reward : 50, Qst No : 6 ,Question : How many words are scrambled?</v>
+      </c>
+      <c r="E324" t="str">
+        <v>21-08-2026 05:51:38 pm</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="str">
+        <v>6a8842dff196f265099f1f86</v>
+      </c>
+      <c r="B325" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C325" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D325" t="str">
+        <v>Game quit at question 6; reward collected: "50"</v>
+      </c>
+      <c r="E325" t="str">
+        <v>21-08-2026 05:51:51 pm</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="str">
+        <v>6a884313f196f265099f1f9b</v>
+      </c>
+      <c r="B326" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C326" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D326" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E326" t="str">
+        <v>21-08-2026 05:52:43 pm</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="str">
+        <v>6a884314f196f265099f1fa2</v>
+      </c>
+      <c r="B327" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C327" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D327" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E327" t="str">
+        <v>21-08-2026 05:52:44 pm</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="str">
+        <v>6a88431ff196f265099f2082</v>
+      </c>
+      <c r="B328" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C328" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D328" t="str">
+        <v>Started Playing game and Debited "10" and Balance "640"</v>
+      </c>
+      <c r="E328" t="str">
+        <v>21-08-2026 05:52:55 pm</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="str">
+        <v>6a884320f196f265099f2088</v>
+      </c>
+      <c r="B329" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C329" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D329" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E329" t="str">
+        <v>21-08-2026 05:52:56 pm</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="str">
+        <v>6a88433ff196f265099f20ad</v>
+      </c>
+      <c r="B330" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C330" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D330" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E330" t="str">
+        <v>21-08-2026 05:53:27 pm</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="str">
+        <v>6a88433ff196f265099f20b3</v>
+      </c>
+      <c r="B331" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C331" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D331" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E331" t="str">
+        <v>21-08-2026 05:53:27 pm</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="str">
+        <v>6a884362f196f265099f2196</v>
+      </c>
+      <c r="B332" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C332" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D332" t="str">
+        <v>Started Playing game and Debited "10" and Balance "630"</v>
+      </c>
+      <c r="E332" t="str">
+        <v>21-08-2026 05:54:02 pm</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="str">
+        <v>6a884362f196f265099f219c</v>
+      </c>
+      <c r="B333" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C333" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D333" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E333" t="str">
+        <v>21-08-2026 05:54:02 pm</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="str">
+        <v>6a884370f196f265099f21c6</v>
+      </c>
+      <c r="B334" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C334" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D334" t="str">
+        <v>Answerd Correctly to Qst ID : 6a884363f196f265099f21a6, Reward : 10, Qst No : 2 ,Question : How many letters are colored with the WRONG color?</v>
+      </c>
+      <c r="E334" t="str">
+        <v>21-08-2026 05:54:16 pm</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="str">
+        <v>6a884373f196f265099f21dd</v>
+      </c>
+      <c r="B335" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C335" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D335" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6a884373f196f265099f21d5 , Question : What is the alphabetical arrangement of these random letters: "fxt"?, Type : re_arrange_letters </v>
+      </c>
+      <c r="E335" t="str">
+        <v>21-08-2026 05:54:19 pm</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="str">
+        <v>6a88437df196f265099f21f3</v>
+      </c>
+      <c r="B336" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C336" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D336" t="str">
+        <v>Answerd Correctly to Qst ID : 6a884373f196f265099f21d5, Reward : 40, Qst No : 3 ,Question : What is the alphabetical arrangement of these random letters: "fxt"?</v>
+      </c>
+      <c r="E336" t="str">
+        <v>21-08-2026 05:54:29 pm</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="str">
+        <v>6a884382f196f265099f220a</v>
+      </c>
+      <c r="B337" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C337" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D337" t="str">
+        <v xml:space="preserve">Created Question Number : 2, Rupees : 30, Qst ID : 6a884381f196f265099f2202 , Question : How many broken boxes are there?, Type : Total Boxes [Broken] </v>
+      </c>
+      <c r="E337" t="str">
+        <v>21-08-2026 05:54:34 pm</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="str">
+        <v>6a884392f196f265099f221c</v>
+      </c>
+      <c r="B338" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C338" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D338" t="str">
+        <v>Answered incorrectly for Qst ID: 6a884381f196f265099f2202, Qst: How many broken boxes are there?, Submitted Answer: 28</v>
+      </c>
+      <c r="E338" t="str">
+        <v>21-08-2026 05:54:50 pm</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="str">
+        <v>6a884529dcde39447acb5af7</v>
+      </c>
+      <c r="B339" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C339" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D339" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E339" t="str">
+        <v>21-08-2026 06:01:37 pm</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="str">
+        <v>6a88452adcde39447acb5afd</v>
+      </c>
+      <c r="B340" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C340" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D340" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E340" t="str">
+        <v>21-08-2026 06:01:38 pm</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="str">
+        <v>6a88464adcde39447acb5b1a</v>
+      </c>
+      <c r="B341" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C341" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D341" t="str">
+        <v>New Coin Purchase :: Title : 20₹; Body : win 20₹; Stars : 20; Type : Stars</v>
+      </c>
+      <c r="E341" t="str">
+        <v>21-08-2026 06:06:26 pm</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="str">
+        <v>6a8848addcde39447acb5b39</v>
+      </c>
+      <c r="B342" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C342" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D342" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E342" t="str">
+        <v>21-08-2026 06:16:37 pm</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E287"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E342"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/live-history.xlsx
+++ b/live-history.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E342"/>
+  <dimension ref="A1:E344"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6213,9 +6213,43 @@
         <v>21-08-2026 06:16:37 pm</v>
       </c>
     </row>
+    <row r="343">
+      <c r="A343" t="str">
+        <v>6a8848aedcde39447acb5b40</v>
+      </c>
+      <c r="B343" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C343" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D343" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E343" t="str">
+        <v>21-08-2026 06:16:38 pm</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="str">
+        <v>6a89c6f1af0a65eb80b69e17</v>
+      </c>
+      <c r="B344" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C344" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D344" t="str">
+        <v xml:space="preserve">Created New Payment Data : User : 686e24d32f21c9417882f777; Account Holder Name : staWro; Type of Payment Method : Bank; </v>
+      </c>
+      <c r="E344" t="str">
+        <v>22-08-2026 09:27:37 pm</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E342"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E344"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/live-history.xlsx
+++ b/live-history.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E344"/>
+  <dimension ref="A1:E515"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6247,9 +6247,2916 @@
         <v>22-08-2026 09:27:37 pm</v>
       </c>
     </row>
+    <row r="345">
+      <c r="A345" t="str">
+        <v>6a89ca75af0a65eb80b69e86</v>
+      </c>
+      <c r="B345" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C345" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D345" t="str">
+        <v xml:space="preserve">Created New Payment Data : User : 686e24d32f21c9417882f777; Account Holder Name : Avi; Type of Payment Method : Bank; </v>
+      </c>
+      <c r="E345" t="str">
+        <v>22-08-2026 09:42:37 pm</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="str">
+        <v>6a8bff3e2969f40a94886225</v>
+      </c>
+      <c r="B346" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C346" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D346" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E346" t="str">
+        <v>24-08-2026 01:52:22 pm</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="str">
+        <v>6a8bff3e2969f40a9488622b</v>
+      </c>
+      <c r="B347" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C347" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D347" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E347" t="str">
+        <v>24-08-2026 01:52:22 pm</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="str">
+        <v>6a8bff792969f40a9488630d</v>
+      </c>
+      <c r="B348" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C348" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D348" t="str">
+        <v>Started Playing game and Debited "10" and Balance "620"</v>
+      </c>
+      <c r="E348" t="str">
+        <v>24-08-2026 01:53:21 pm</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="str">
+        <v>6a8bff792969f40a94886313</v>
+      </c>
+      <c r="B349" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C349" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D349" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E349" t="str">
+        <v>24-08-2026 01:53:21 pm</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="str">
+        <v>6a8bff842969f40a9488633d</v>
+      </c>
+      <c r="B350" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C350" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D350" t="str">
+        <v>Answerd Correctly to Qst ID : 6a8bff7a2969f40a9488631d, Reward : 10, Qst No : 2 ,Question : Decode "X" using cipher key</v>
+      </c>
+      <c r="E350" t="str">
+        <v>24-08-2026 01:53:32 pm</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="str">
+        <v>6a8bff8b2969f40a94886354</v>
+      </c>
+      <c r="B351" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C351" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D351" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6a8bff8a2969f40a9488634c , Question : How many colour names match their text colour out of 8?, Type : [Colours &amp; Name Match] </v>
+      </c>
+      <c r="E351" t="str">
+        <v>24-08-2026 01:53:39 pm</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="str">
+        <v>6a8bff972969f40a94886369</v>
+      </c>
+      <c r="B352" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C352" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D352" t="str">
+        <v>Answerd Correctly to Qst ID : 6a8bff8a2969f40a9488634c, Reward : 40, Qst No : 3 ,Question : How many colour names match their text colour out of 8?</v>
+      </c>
+      <c r="E352" t="str">
+        <v>24-08-2026 01:53:51 pm</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="str">
+        <v>6a8bff9b2969f40a94886380</v>
+      </c>
+      <c r="B353" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C353" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D353" t="str">
+        <v xml:space="preserve">Created Question Number : 2, Rupees : 30, Qst ID : 6a8bff9a2969f40a94886378 , Question : How many puzzle pieces contain 2 or more MALE connectors (outward tabs)?, Type : puzle_peace_male_female </v>
+      </c>
+      <c r="E353" t="str">
+        <v>24-08-2026 01:53:55 pm</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="str">
+        <v>6a8bffa72969f40a94886391</v>
+      </c>
+      <c r="B354" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C354" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D354" t="str">
+        <v>Answerd Correctly to Qst ID : 6a8bff9a2969f40a94886378, Reward : 30, Qst No : 4 ,Question : How many puzzle pieces contain 2 or more MALE connectors (outward tabs)?</v>
+      </c>
+      <c r="E354" t="str">
+        <v>24-08-2026 01:54:07 pm</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="str">
+        <v>6a8bffab2969f40a948863ab</v>
+      </c>
+      <c r="B355" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C355" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D355" t="str">
+        <v xml:space="preserve">Created Question Number : 3, Rupees : 40, Qst ID : 6a8bffab2969f40a948863a3 , Question : How many times does the letter sequence 'fly' appear in the given words?, Type : count_word_exist </v>
+      </c>
+      <c r="E355" t="str">
+        <v>24-08-2026 01:54:11 pm</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="str">
+        <v>6a8bffbc2969f40a948863c0</v>
+      </c>
+      <c r="B356" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C356" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D356" t="str">
+        <v>Answerd Correctly to Qst ID : 6a8bffab2969f40a948863a3, Reward : 40, Qst No : 5 ,Question : How many times does the letter sequence 'fly' appear in the given words?</v>
+      </c>
+      <c r="E356" t="str">
+        <v>24-08-2026 01:54:28 pm</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="str">
+        <v>6a8bffca2969f40a948863d7</v>
+      </c>
+      <c r="B357" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C357" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D357" t="str">
+        <v xml:space="preserve">Created Question Number : 4, Rupees : 50, Qst ID : 6a8bffc92969f40a948863cf , Question : How many words are scrambled?, Type : scramble_words </v>
+      </c>
+      <c r="E357" t="str">
+        <v>24-08-2026 01:54:42 pm</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="str">
+        <v>6a8bffd32969f40a948863ec</v>
+      </c>
+      <c r="B358" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C358" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D358" t="str">
+        <v>Answerd Correctly to Qst ID : 6a8bffc92969f40a948863cf, Reward : 50, Qst No : 6 ,Question : How many words are scrambled?</v>
+      </c>
+      <c r="E358" t="str">
+        <v>24-08-2026 01:54:51 pm</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="str">
+        <v>6a8bffda2969f40a94886407</v>
+      </c>
+      <c r="B359" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C359" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D359" t="str">
+        <v xml:space="preserve">Created Question Number : 5, Rupees : 80, Qst ID : 6a8bffd92969f40a948863ff , Question : How many boxes are unbroken in total?, Type : Total Boxes [Comp] </v>
+      </c>
+      <c r="E359" t="str">
+        <v>24-08-2026 01:54:58 pm</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="str">
+        <v>6a8bffe42969f40a9488641c</v>
+      </c>
+      <c r="B360" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C360" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D360" t="str">
+        <v>Answerd Correctly to Qst ID : 6a8bffd92969f40a948863ff, Reward : 80, Qst No : 7 ,Question : How many boxes are unbroken in total?</v>
+      </c>
+      <c r="E360" t="str">
+        <v>24-08-2026 01:55:08 pm</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="str">
+        <v>6a8bffeb2969f40a94886437</v>
+      </c>
+      <c r="B361" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C361" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D361" t="str">
+        <v xml:space="preserve">Created Question Number : 6, Rupees : 110, Qst ID : 6a8bffeb2969f40a9488642f , Question : How many times do the letters Z, L, S, P, T appear in the paragraph?, Type : count_leters_exist </v>
+      </c>
+      <c r="E361" t="str">
+        <v>24-08-2026 01:55:15 pm</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="str">
+        <v>6a8c00012969f40a9488644a</v>
+      </c>
+      <c r="B362" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C362" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D362" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E362" t="str">
+        <v>24-08-2026 01:55:37 pm</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="str">
+        <v>6a8c00012969f40a94886452</v>
+      </c>
+      <c r="B363" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C363" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D363" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E363" t="str">
+        <v>24-08-2026 01:55:37 pm</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="str">
+        <v>6a8c00062969f40a94886535</v>
+      </c>
+      <c r="B364" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C364" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D364" t="str">
+        <v>Started Playing game and Debited "10" and Balance "610"</v>
+      </c>
+      <c r="E364" t="str">
+        <v>24-08-2026 01:55:42 pm</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="str">
+        <v>6a8c00072969f40a9488653b</v>
+      </c>
+      <c r="B365" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C365" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D365" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E365" t="str">
+        <v>24-08-2026 01:55:43 pm</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="str">
+        <v>6a8c00152969f40a94886565</v>
+      </c>
+      <c r="B366" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C366" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D366" t="str">
+        <v>Answerd Correctly to Qst ID : 6a8c00072969f40a94886545, Reward : 10, Qst No : 2 ,Question : How many words are colored with the WRONG color?</v>
+      </c>
+      <c r="E366" t="str">
+        <v>24-08-2026 01:55:57 pm</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="str">
+        <v>6a8c00182969f40a9488657c</v>
+      </c>
+      <c r="B367" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C367" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D367" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6a8c00172969f40a94886574 , Question : Decode "M" using cipher key, Type : encode_decode </v>
+      </c>
+      <c r="E367" t="str">
+        <v>24-08-2026 01:56:00 pm</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="str">
+        <v>6a8c001f2969f40a94886591</v>
+      </c>
+      <c r="B368" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C368" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D368" t="str">
+        <v>Answerd Correctly to Qst ID : 6a8c00172969f40a94886574, Reward : 40, Qst No : 3 ,Question : Decode "M" using cipher key</v>
+      </c>
+      <c r="E368" t="str">
+        <v>24-08-2026 01:56:07 pm</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="str">
+        <v>6a8c00222969f40a948865a8</v>
+      </c>
+      <c r="B369" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C369" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D369" t="str">
+        <v xml:space="preserve">Created Question Number : 2, Rupees : 30, Qst ID : 6a8c00212969f40a948865a0 , Question : How many colour names match their text colour out of 8?, Type : [Colours &amp; Name Match] </v>
+      </c>
+      <c r="E369" t="str">
+        <v>24-08-2026 01:56:10 pm</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="str">
+        <v>6a8c002d2969f40a948865bd</v>
+      </c>
+      <c r="B370" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C370" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D370" t="str">
+        <v>Answerd Correctly to Qst ID : 6a8c00212969f40a948865a0, Reward : 30, Qst No : 4 ,Question : How many colour names match their text colour out of 8?</v>
+      </c>
+      <c r="E370" t="str">
+        <v>24-08-2026 01:56:21 pm</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="str">
+        <v>6a8c00312969f40a948865d4</v>
+      </c>
+      <c r="B371" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C371" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D371" t="str">
+        <v xml:space="preserve">Created Question Number : 3, Rupees : 40, Qst ID : 6a8c00312969f40a948865cc , Question : How many words are scrambled?, Type : scramble_words </v>
+      </c>
+      <c r="E371" t="str">
+        <v>24-08-2026 01:56:25 pm</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="str">
+        <v>6a8c003a2969f40a948865e9</v>
+      </c>
+      <c r="B372" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C372" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D372" t="str">
+        <v>Answerd Correctly to Qst ID : 6a8c00312969f40a948865cc, Reward : 40, Qst No : 5 ,Question : How many words are scrambled?</v>
+      </c>
+      <c r="E372" t="str">
+        <v>24-08-2026 01:56:34 pm</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="str">
+        <v>6a8c003d2969f40a94886600</v>
+      </c>
+      <c r="B373" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C373" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D373" t="str">
+        <v xml:space="preserve">Created Question Number : 4, Rupees : 50, Qst ID : 6a8c003d2969f40a948865f8 , Question : How many broken boxes are there?, Type : Total Boxes [Broken] </v>
+      </c>
+      <c r="E373" t="str">
+        <v>24-08-2026 01:56:37 pm</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="str">
+        <v>6a8c00472969f40a94886612</v>
+      </c>
+      <c r="B374" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C374" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D374" t="str">
+        <v>Answered incorrectly for Qst ID: 6a8c003d2969f40a948865f8, Qst: How many broken boxes are there?, Submitted Answer: 26, image : iVBORw0KGgoAAAANSUhEUgAAAZAAAAD6CAYAAACPpxFEAAAABmJLR0QA/wD/AP+gvaeTAAADjElEQVR4nO3VwQ3AIBDAsNL9dz5mIB+EZE+QX9bMzAcAh/7bAQC8yUAASAwEgMRAAEgMBIDEQABIDASAxEAASAwEgMRAAEgMBIDEQABIDASAxEAASAwEgMRAAEgMBIDEQABIDASAxEAASAwEgMRAAEgMBIDEQABIDASAxEAASAwEgMRAAEgMBIDEQABIDASAxEAASAwEgMRAAEgMBIDEQABIDASAxEAASAwEgMRAAEgMBIDEQABIDASAxEAASAwEgMRAAEgMBIDEQABIDASAxEAASAwEgMRAAEgMBIDEQABIDASAxEAASAwEgMRAAEgMBIDEQABIDASAxEAASAwEgMRAAEgMBIDEQABIDASAxEAASAwEgMRAAEgMBIDEQABIDASAxEAASAwEgMRAAEgMBIDEQABIDASAxEAASAwEgMRAAEgMBIDEQABIDASAxEAASAwEgMRAAEgMBIDEQABIDASAxEAASAwEgMRAAEgMBIDEQABIDASAxEAASAwEgMRAAEgMBIDEQABIDASAxEAASAwEgMRAAEgMBIDEQABIDASAxEAASAwEgMRAAEgMBIDEQABIDASAxEAASAwEgMRAAEgMBIDEQABIDASAxEAASAwEgMRAAEgMBIDEQABIDASAxEAASAwEgMRAAEgMBIDEQABIDASAxEAASAwEgMRAAEgMBIDEQABIDASAxEAASAwEgMRAAEgMBIDEQABIDASAxEAASAwEgMRAAEgMBIDEQABIDASAxEAASAwEgMRAAEgMBIDEQABIDASAxEAASAwEgMRAAEgMBIDEQABIDASAxEAASAwEgMRAAEgMBIDEQABIDASAxEAASAwEgMRAAEgMBIDEQABIDASAxEAASAwEgMRAAEgMBIDEQABIDASAxEAASAwEgMRAAEgMBIDEQABIDASAxEAASAwEgMRAAEgMBIDEQABIDASAxEAASAwEgMRAAEgMBIDEQABIDASAxEAASAwEgMRAAEgMBIDEQABIDASAxEAASAwEgMRAAEgMBIDEQABIDASAxEAASAwEgMRAAEgMBIDEQABIDASAxEAASAwEgMRAAEgMBIDEQABIDASAxEAASAwEgMRAAEgMBIDEQABIDASAxEAASAwEgMRAAEgMBIDEQABIDASAxEAASAwEgMRAAEgMBIDEQABIDASAxEAASAwEgMRAAEgMBIDEQABIDASAxEAASAwEgGQDJ6wF8MK0Cn8AAAAASUVORK5CYII=</v>
+      </c>
+      <c r="E374" t="str">
+        <v>24-08-2026 01:56:47 pm</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="str">
+        <v>6a8c00762969f40a94886632</v>
+      </c>
+      <c r="B375" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C375" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D375" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E375" t="str">
+        <v>24-08-2026 01:57:34 pm</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="str">
+        <v>6a8c00762969f40a94886638</v>
+      </c>
+      <c r="B376" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C376" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D376" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E376" t="str">
+        <v>24-08-2026 01:57:34 pm</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="str">
+        <v>6a8c007b2969f40a9488671c</v>
+      </c>
+      <c r="B377" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C377" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D377" t="str">
+        <v>Started Playing game and Debited "10" and Balance "600"</v>
+      </c>
+      <c r="E377" t="str">
+        <v>24-08-2026 01:57:39 pm</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="str">
+        <v>6a8c007c2969f40a94886722</v>
+      </c>
+      <c r="B378" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C378" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D378" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E378" t="str">
+        <v>24-08-2026 01:57:40 pm</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="str">
+        <v>6a8c008c2969f40a9488674e</v>
+      </c>
+      <c r="B379" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C379" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D379" t="str">
+        <v>Answerd Correctly to Qst ID : 6a8c007c2969f40a9488672e, Reward : 10, Qst No : 2 ,Question : How many boxes are unbroken in total?</v>
+      </c>
+      <c r="E379" t="str">
+        <v>24-08-2026 01:57:56 pm</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="str">
+        <v>6a8c008f2969f40a94886765</v>
+      </c>
+      <c r="B380" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C380" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D380" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6a8c008e2969f40a9488675d , Question : How many letters are misaligned?, Type : letters_missalign </v>
+      </c>
+      <c r="E380" t="str">
+        <v>24-08-2026 01:57:59 pm</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="str">
+        <v>6a8c00a42969f40a9488677a</v>
+      </c>
+      <c r="B381" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C381" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D381" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E381" t="str">
+        <v>24-08-2026 01:58:20 pm</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="str">
+        <v>6a8c00a42969f40a94886780</v>
+      </c>
+      <c r="B382" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C382" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D382" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E382" t="str">
+        <v>24-08-2026 01:58:20 pm</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="str">
+        <v>6a8c00ae2969f40a94886865</v>
+      </c>
+      <c r="B383" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C383" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D383" t="str">
+        <v>Started Playing game and Debited "10" and Balance "590"</v>
+      </c>
+      <c r="E383" t="str">
+        <v>24-08-2026 01:58:30 pm</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="str">
+        <v>6a8c00ae2969f40a9488686b</v>
+      </c>
+      <c r="B384" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C384" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D384" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E384" t="str">
+        <v>24-08-2026 01:58:30 pm</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="str">
+        <v>6a8c00c22969f40a94886894</v>
+      </c>
+      <c r="B385" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C385" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D385" t="str">
+        <v>Answered incorrectly for Qst ID: 6a8c00af2969f40a94886877, Qst: How many broken boxes are there?, Submitted Answer: 25, image : iVBORw0KGgoAAAANSUhEUgAAAZAAAAD6CAYAAACPpxFEAAAABmJLR0QA/wD/AP+gvaeTAAAgAElEQVR4nO3dbUxT5/sH8O+xlCLEaHSJE2ORuMXAUHxODIox6janVNMYnWTWuBcuZBoTsjdmybIsCjNxJkZ+Lll87AuYBIiLonEsAVHQ8eCa8jCyGBgufx3JGBJFaUM5/xfmnBUt0JbTnqfv5xXGnvYW4Vznuu/7um5BFEURREREEZqm9gCIiEifGECIiCgqDCBERBQVBhAiIooKAwgREUWFAYSIiKLCAEJERFFhACEioqgwgBARUVQYQIiIKCoMIEREFBUGECIiigoDCBERRSVB7QEQESlt9+7dqnxueXm5Kp+rFmYgRGQoagUPtT9bDcxAiMiQ4p0NmC14AMxAiIgoSgwgREQUFQYQIiKKCgMIERFFhYvoRGR6T58+RUdHBwYGBiAIAmbNmoWsrCzMnDlT7aFpGgMIEZlWT08PSktL4fV6IYrimL8TBAHZ2dnYu3cv0tPTVRqhtjGAEJEp3bhxA263G6Ojo7DZbFiyZAnefvttAMDff/+NtrY2eDwetLW1weVyYevWrSqPWHsYQIjIdG7cuIFLly5BEATk5eXB6XQiJSVlzGuGhoZQWVmJ6upqXLx4EQAYRF7DRXQiMpWenh643W4IgoBDhw5h3759bwQPAEhJSYHL5cKhQ4cgCALcbjf+/PPP+A9YwxhAiMhUSktLMTo6iu3bt2P9+vWTvn79+vX46KOPEAgEUFZWFocR6gcDCBGZxtOnT+H1emGz2eB0OsO+bteuXUhMTITH48Hg4GAMR6gvDCBEZBodHR0QRRFLliwJOW01npSUFGRlZUEURXR2dsZwhPrCAEJEpvHvv/8CAObNmxfxtampqQCAf/75R9Ex6RkDCBFRGKQ6EUEQVB6JdjCAEJFpzJkzBwDw+PHjiK998uTJmPcgBhAiMpHMzEwIgoD29nYMDQ2Ffd3z58/R3t4OQRCQmZkZwxHqCwMIEZnGrFmzkJ2dDZ/Ph8rKyrCvq6iogN/vx7Jly9gfKwgr0YnGwXO1jWnv3r1oa2tDdXU10tPTJ60Fqa+vx82bN2GxWJCfnx+nUeqDIL7eQYyIVD+elEEketL/3UTfw5s3b+LixYsQBAEfffQRdu3a9ca23ufPn6OiogI3b96EKIo4cOAAW5m8hhkI0QR4rrYxSYHA7XajuroaNTU1IZsp+v1+WCwW7N+/Hx9++KGaQ9YkBhAiMqWtW7ciIyMDZWVl8Hg8aG1tHfP3giBg+fLlyM/PR1pamkqj1DYGECIyrYULF+Lo0aMYHBxEZ2enXGg4e/ZsZGZmRrRgHs7UmdEwgBCR6c2cORNr165Vexi6wwBiYNxFFD0j/BuIYo0BxKDUXIzdvXu3KW/APFebYmGy3+Xg3zUlf+/D+R1mADG4aG7kL1++BABMnz494mvNuIuI52pTrGj9QZABhN7Q1NQEQRCQm5ur9lBUE+6CKM/VpngI90Ew+HXxeBBkAKE3NDQ0mD6AhIPnamubGbPhYPF4EGQvLBrj2bNnaGtrg9frxbNnz9QejmbxXG3tUnP9TUtrfw0NDWhoaIjpZzADoTHu3buHQCAAALh//z62bNmi8oi0STpXOy8vL+xztbu7u1FdXY2ysjIcPXo0DqPUH+4cVIb0ICh9PWPGjJh8DjMQGiP4ieXu3bsqjkS7eK52bKi9YGwk0oNgIBDA/fv3Y/Y5zEBI1t/fj66uLiQmJgIAurq60N/fzwN0XjPVc7UfPHiAzs5OFq6Ng/3Hpu71B8FYzSQwAyFZY2MjRFHEypUrsXLlSoiiiMbGRrWHpTk8V5u0LPhBMDExUX4QjAUGEJJJU1br1q1DTk4OAMR8Ec5seK42xVo8HwQ5hWUCjx8/xvDwMHw+H0ZGRgAAIyMjGB4ell/T39+Pnp4eJCcnY9myZQCA5ORkdHd34/r162OmsZKSkpCQ8OpHJyEhATabDUlJSfLTtdHxXG3SsuAHQVEUce/ePTQ0NCAvL0/xz2IAMYmzZ8/i0aNHk75uzZo1sFqt8td1dXVwu90TXmO321FYWKjIOPXg9XO1w10H4bnasdPX1wcAmDt3rsojiR0tPggygJhAamoqjh8/jgsXLqC2thbAf2cd2Gw2AJBvgps2bZKv++CDD+QfsKGhIQCAz+fDb7/9Jk/FbNy4EZ9++qn8PmYgnavt8XhQWVkJl8sV1nXSudrLly9nfyyFVVVVAQAKCgpUHklsae1BkAHEJGw2GwoKCpCZmYlz587B5/Ohr68PhYWFWLBgQchrFi1ahEWLFsl/fvLkCU6dOgVRFGG1WnHgwAFs3rw5Xv8ETeG52trR19eH+vp6AIDT6TRsFqLFB0EGEJPZsGED3nnnHZw6dQp//fUXvvzyS3z22Wfyovl4mpqacPbsWbx48QLz5s1DYWGhqU9pS09Ph8vlwsWLF1FSUoLu7u6wztV2uVym/r7FQlVVlVz8WlVVZegsRGsPggwgJjR//nwcO3YMP/zwAxoaGnD69Gl0dXVh//798pOKZGRkBJcvX8atW7cAADk5OTh48OC4DdqMVtE7EZ6rrT4p+7BYLABeZXpGzkIkWnkQZAAxqenTp+PIkSNIS0tDaWkp6urqQs7li6KIuro6AEB+fj527twZ55FqG8/VVpeUfWzcuBEAUFtba/gsRBLLB8FwMYCYnDTlsnTpUnnRLZjVasXSpUvR3NwcUdW1mSh5rjaFT8o+pk2bhp07d2LatGmor6/H7du3sXPnzqgKPfVG7QdBFhKaXEtLCwBg1apVAF4tsp05cwbfffed3I1X+rvXn65D2b17tyFbQ4RDOld727Zt2LZtG9auXcvgEUNS9rFhwwbMmzcPc+fORW5uLkZHR3H16lW1hxdX4T4IBr9WCQwgJubz+dDR0QFBELBixQp4PB4UFhbizp07+PXXX/HFF1/A4/FgxYoVct2Dz+dTe9hEb2QfEqfTCYvFgtu3b8tFm2ag9INguBhATMzr9cLv98Nut6OiogLFxcUYGBhARkYGMjIyMDAwgOLiYlRUVMBut8Pv98Pr9ao9bKI3sg+JGbMQNR8EuQZiYtKTSG9vL3p7e2G1WrFnzx655cG1a9dw5coVeeFNumb16tWqjJcIGD/7kDidTlOthUgPgmlpaaioqMDPP/8MURSRkZEBAPj9999RXFyM999/H3a7Hb29vfB6vYr8HjMDMSlRFMeksna7HUVFRXA4HBAEAYIgwOFwoKioCHa7XX5da2urXHxEpIbxsg+J2bKQ4AfBW7duISEhAZ988gm+/vprfP311/jkk0+QkJCAW7duobe3d8w1U8UMxKQePnyIwcFBCIKA7du34+OPPw65+JaWlobi4mL8+OOPuH79OgYHB/Hw4UO8++67Kow6/sy6IUCrJss+JGbJQkI9CB4+fHjMlnGHw4Hs7GycOXNGboMiPQhOtSs0A4hJtbS04K233sLnn3+O9957b8LXWq1W7Nu3D2vWrEFJSQlaWlriFkDGu4EHFyzG4iZfXl7O41U1KLjuY6KgIGUhtbW1uHr1qmHrQtR+EGQAMamUlBScPHkSycnJYV+zePFinDhxAr/88ksMR/YftY845Y1cW8LNPiRmyELUfhBkADEph8MR1XXJyclRXxutyW7kSt/oOW2lTeFmHxIzZCFqPwgygBCR5gV33E1ISMBPP/0U1nVSSw+j9shS+0GQAYSINC+4425NTU3E1wcCAdP0yIonBhCD43QM6V0gEMDs2bOxY8eOKb1PQkICAoGA3LmXpo4BxKDU3EUEvBm4uCBN0bJYLNizZ4/aw1CVVh8EGUAM7PWbtlI/hNFsoY3XrqanT5+io6MDAwMDEAQBs2bNQlZWFpsaki5pfTs5A4gJKXkjD+e94vEL0NPTg9LSUni93jcq5QVBQHZ2Nvbu3Yv09PSYj4VISVrO3hlASPdu3LgBt9uN0dFR2Gy2kKcCejwetLW1weVyyScJEilNy9lCLDCAkK7duHEDly5dgiAIyMvLg9PpfOO8g6GhIVRWVqK6uhoXL14EAAYRUpzaa45qBBEGENKtnp4euN1uCIKAQ4cOYf369SFfl5KSApfLhfT0dJSUlMDtdiMjIwMLFy6M74ApLBNtwNDqYnKweN/I1fyesBsv6VZpaSlGR0exffv2cYNHsPXr1+Ojjz5CIBBAWVlZHEZIkVBzrl/L6wxaxgyEJqTVXU1Pnz6F1+uFzWaD0+kM+7pdu3ahpqYGHo8Hg4ODqv87aKx4t62hqWEAoZC0vqupo6MDoihiyZIlEZ3xnJKSgqysLDx48ACdnZ1Yu3ZtDEdJZGwMIPQGPexq+vfffwEgqg6rqampePDgAf755x+lh2VoZtthFE99fX0AoLteXQwgNIYZdjVJGdVUD9MxEzPuMIqnqqoqANBdry4GEJLpaVfTnDlzAACPHz+O+NonT56MeQ8Kn5l2GMVLcKdhvXUM5i4skulpV1NmZiYEQUB7ezuGhobCvu758+dob2+HIAjIzMyM4QiJwiN1GpY6BusJAwgBmNqupsTERHlXU7zMmjUL2dnZ8Pl8qKysDPu6iooK+P1+LFu2jDuwSHVS9mGxWGCxWFBfXy+vh+gBAwgBmPquJlEU0dnZGcMRvmnv3r2wWCyorq7GnTt3Jn19fX09bt68CYvFgvz8/DiMkGhiUvaRm5uL3Nxc3WUhDCAEYOq7mgDEfVdTeno6XC4XRFFESUkJLl++HHI66/nz57h06RL+97//QRRFuFwupKWlxXWsZtbX16erp+p4ef2Md6fTCYvFgtu3b8vrdFrHRXSaMjV3NUm7v9xuN6qrq1FTUxNy27Hf74fFYsH+/fvx4Ycfxn2cZqbXHUaxFuqMd72d4c4AQgD0vatp69atyMjIQFlZGTweD1pbW8f8vSAIWL58OfLz85l5xJmedxjF0uvZh8TpdKK+vh63b9/Gzp07o5oRiCcGEALw5q6mcNdBtLKraeHChTh69CgGBwfR2dkpT8nNnj0bmZmZXDBXSfBZ5jyT/D+hsg/gVSGhnrIQroEQAOPsapo5cybWrl2Lbdu2Ydu2bVi7dq0mxmVGet9hFCvjZR8SPa2FMICQjLuaSElK7DAqLy83XBW69H3ZsGFDyCkqKQsZHR3F1atXVRhh+BhASMZdTaQUI+wwioXJsg+JXr5fXAOhMbiriZRghB1GsTDe2sfr9LIWwgASAbN0I+WuJpoKJXcYSb9zRpjGCjf7kOhhRxYDSJjM1o1US7uazNBQz0iMssNIaeFmHxI9fL8YQCJktm6k0q4mNZSXl5sm6zOKcHYYaf2pOhaC62ESEhLw008/hXVdQsKrW3R9fb0m62gYQEjTeCPXl8mesvXwVB0LwfUwNTU1EV8v7WDT2veLAYSIFBHJDiMzZSGBQACzZ8/Gjh07pvQ+CQkJCAQCsFgsCo1s6hhAiEgRRtthpBSLxYI9e/aoPYyYYB0IEU1ZNDuM9FDnQBNjBhKmaObinz59io6ODgwMDEAQBMyaNQtZWVmqt9ZQe2GejMeIO4xocuMGEO5+iV5PTw9KS0vh9XrlVucSQRCQnZ2NvXv3Ij09Pa7j4q4migWj7jCiyYUMIGareVDSjRs34Ha7MTo6CpvNFrKK2+PxoK2tDS6XS678jhc9f29Jm4y6w4gmN+EUVjQ3m5cvXwIApk+fHvG1Wp5aCaci9saNG7h06RIEQUBeXh6cTucbbdGHhoZQWVmJ6upqXLx4EQDiHkSIlGLkHUbRUuo+Fnyv0eq9UfE1kKamJgiCgNzcXKXfWtN6enrgdrshCAIOHTqE9evXh3xdSkoKXC4X0tPTUVJSArfbjYyMDCxcuDC+AyZSgJF3GEXKjFPEigeQhoYGUwaQ0tJSjI6OIi8vb9zgEWz9+vXo7u5GdXU1ysrKcPTo0TiMkohiKVY3cq1OPSu6jffZs2doa2uD1+vFs2fPlHxrTXv69Cm8Xi9sNhucTmfY1+3atQuJiYnweDwYHByM4QiJiJSnaAC5d+8eAoEAAoEA7t+/r+Rba1pHRwdEUcSSJUvCPgoWeDWdlZWVBVEU0dnZGcMREhEpT9EA0tDQIH999+5dJd9a06ROtdG0ZEhNTQUA/PPPP4qOiYgo1hRbA+nv70dXVxcSExMBAF1dXejv78ecOXOU+ghDkupEBEFQeSREk9PqbiBSh2IZSGNjI0RRxMqVK7Fy5UqIoojGxkal3l7TpCD5+PHjiK+V2jgw0JKWqbmIq9UFZFIwA5GmrNatWwdRFHHv3j00NDQgLy9PqY/QrMzMTAiCgPb2dgwNDYW9DvL8+XO0t7dDEARkZmbGeJREU8Mb+ZuUzMgiqfvQyv/FpAHk8ePHGB4ehs/nw8jICABgZGQEw8PD8mv6+/vR09OD5ORkLFu2DACQnJyM7u5uXL9+fczTdVJSktzCICEhATabDUlJSfJagB7NmjUL2dnZ8Hg8qKyshMvlCuu6iooK+P1+LF++XPX+WEQUGXbsCDMDOXv2LB49ejTp69asWQOr1Sp/XVdXB7fbPeE1drsdhYWF4QxD0/bu3Yu2tjZUV1cjPT190lqQ+vp63Lx5ExaLBfn5+XEaJREpLRY38oneU0vrUJMGkNTUVBw/fhwXLlxAbW0tgFcLvsuXL4fNZgMAecpm06ZN8nUffPCBnGkMDQ0BAHw+H3777Td54Xjjxo349NNP5ffRs/T0dLhcLly8eBElJSXo7u7Grl273pjOev78OSoqKnDz5k2IogiXy4W0tDSVRk1EFL2wMhCbzYaCggJkZmbi3Llz8Pl86OvrQ2FhIRYsWBDymkWLFmHRokXyn588eYJTp05BFEVYrVYcOHAAmzdvVuZfoRFSTyu3243q6mrU1NSEbKbo9/thsViwf/9+fPjhh2oOmabIbK0riIJFtIi+YcMGvPPOOzh16hT++usvfPnll/jss8+Qk5Mz4XVNTU04e/YsXrx4gXnz5qGwsNCwT91bt25FRkYGysrK4PF40NraOubvpewtPz/fsN8Ds+AcOJldxLuw5s+fj2PHjuGHH35AQ0MDTp8+ja6uLuzfv1+espKMjIzg8uXLuHXrFgAgJycHBw8ejKpTr54sXLgQR48exeDgIDo7O+VCw9mzZyMzM5ML5gbDrtVkVlFt450+fTqOHDmCtLQ0lJaWoq6uLuTOI1EUUVdXBwDIz88P66hLI5k5cybWrl2r9jBIg8zatdrstHpKabSmVAciLRAvXbpU3n0VzGq1YunSpWhubo6oRxTpA+f/o2fWrtVmpdVTSqdqSgGkpaUFALBq1SoAr3ZbXbhwAX6/HwcPHsSMGTOwatUqNDc3o7W1FVu2bJn6iEkTOP8fPalrtfT1jBkzVB4RxZLWTymdiqgDiM/nQ0dHBwRBwIoVK+DxePD9999jYGAAAPDHH3+goKAAK1askKu0fT6fIbbs0n84/x85qWs1ANy/f58PVgZm9FNKo+6F5fV64ff7YbfbUVFRgeLiYgwMDCAjIwMZGRkYGBhAcXExKioqYLfb4ff74fV6lRw76VRTUxOam5vVHoZqzNq12mxeP6V03759IafypVNKDx06BEEQ4Ha78eeff8Z/wFGIOgORtqf29vait7cXVqsVe/bskXtfXbt2DVeuXJF3YEnXrF69eopDVpcRnoDVZub5f3atNg8znFIaVQYiiuKY+ga73Y6ioiI4HA4IggBBEOBwOFBUVAS73S6/rrW19Y0FJL1gN1JlmPXUSomZu1abiVlOKY0qA3n48CEGBwchCAK2b9+Ojz/+OOQurLS0NBQXF+PHH3/E9evXMTg4iIcPH+Ldd9+d8sDVYKQbuVrMPv9v5q7VZjLVU0ofPHiAzs5OzZcBRBVAWlpa8NZbb+Hzzz/He++9N+FrrVYr9u3bhzVr1qCkpAQtLS26DSA0da/P/xslgLBrNQWb6imlDx480MUppVEFkJSUFJw8eRLJyclhX7N48WKcOHECv/zySzQfaRpGrq0w+vw/u1aTEvR0SmlUAcThcET1YcnJyVFfawZGr60Inv8HXk1nNTY2GmL6hl2rKZhZTilV7ERCUo5RayuMPv/PrtUkMcsppQwgBqFmbyXO/4/FrtVkllNKJwwg4z2ZRnJ2L8WH2rUVnP8fK5Zdq7kbUB/McEppyABSXl5u6MVco1G7txLn/0Nj12pzM8MppeNmIOHeyHnDV58WaiviNf+vx583dq02L6OfUso1EAPQUm0F5//fpHTXaml2QI/B1IyMfEopA4jOabG2gqdW/oddqwkw7imlDCA6p9XailjN/+vt6VvqWp2WloaKigr8/PPPEEURGRkZAIDff/8dxcXFeP/992G329Hb2wuv16v7pqMUmtFOKWUA0Tmt11aYff7frF2ryRwYQDTKKLUVZj61MlTX6sOHD4+Z53Y4HMjOzsaZM2fkbdBS12o9tLIgc2MA0TC911aYff7frF2ryTwYQDTKCLUVZp//Z9dqMjoGEA3Te28ls8//s2u1OZi5G4diAYSV67Gjx9oKzv+za7XRsWOHQgHE6G3ItUBvtRWc/yczMMO9ZyKKTmHF+5tpttRRT72VOP9PZHxcA9EhPdRWmGn+32wPMkSSaWoPgCIXqrbizJkz+O677/Ds2bMxf/d63514cTgcEQUPiZ7m/9WcvjD71AlpAzMQnTF7bYXW8EZOZqZ6AOnr6wMAzJ07V+WR6IPZayuISDtUDyBVVVUAgIKCApVHog9aq63g/D+Ream6BtLX14f6+nrU19fLmQiNL1RtRVFRERwOBwRBgCAIcDgcKCoqgt1ul18n1VYoifP/RKRqBlJVVSWfpFdVVcUsZBJaq63gjZzI3FQLIFL2YbFYALw6UN7pdHItZAKsrSAzM3vVtxapNoUlZR+5ubnIzc1FIBCQ10PCVV5ebqr/XKm2YrLgEUyqrTDiWRtkHmp3u6DQVMlApOxj2rRp2LlzJ6ZNm4b6+nrcvn0bO3fuxLx589QYluaxtxKZXTQPjC9fvgSAqFr5MHhMTJUMRMo+NmzYgHnz5mHu3LnIzc3F6Ogorl69qsaQiMigmpqa0NzcrPYwDCnuAeT17EPidDphsVhw+/ZtPHnyJKz32r17N58QiGhCDQ0NaGhoUHsYhhT3KSwp+9i4ceOYqSopC6mtrcXVq1dNvSPr9aAYnLbHO2By4ZL07NmzZ2hra5O/njFjRlw/f7zfn1j/Tsfr9yeuAWS87EPidDpNvRaitfMF1F64ZBDRHr1l/Pfu3ZNLBe7fv48tW7bE7bPN8PsT1wAyXvYhYRYy+ZODGjdVtuknQJ//L8FTV3fv3o1rAJFE8zutl4X/uAWQybIPidmzECKt08sDRX9/P7q6upCYmAgA6OrqQn9/P+bMmaPk8GKiqakJgiAgNzdX7aFMKG6L6K/vvBoPd2QRkRIaGxshiiJWrlyJlStXQhRFNDY2qj2ssOhl4T8uASTc7EMSzY4sIqJgd+/eBQCsW7cOOTk5AKCLm7K08O/1euXzfbQqLlNYk619vI5rIUQ0nsePH2N4eBg+nw8jIyMAgJGREQwPD8uv6e/vR09PD5KTk7Fs2TIArwpqu7u7cf369THTWElJSUhIeHUrTEhIgM1mQ1JSElJTU+P4r/qPmgv/kYp5AJGyD+DVf85PP/0U1nXSfyh7ZOnL06dP0dHRgYGBAQiCgFmzZiErKwszZ85Ue2ikIqXP/Tl79iwePXo06evWrFkjNxxds2YN6urq4Ha7J7zGbrejsLBQkXFGQwsL/+GKeQAJ7rhbU1MT8fVSjyxmIdrW09OD0tJSeL3eN1rHC4KA7Oxs7N27F+np6SqNkNSk5Lk/qampOH78OC5cuIDa2loAr37Gli9fLp+8KfV+27Rpk3zdBx98ID+YDg0NAXh1wudvv/0m/8xu3LgRn376qWoneOpt4T+mASQQCGD27NnYsWPHlN4nISEBgUBA7txL2nLjxg243W6Mjo7CZrNhyZIlePvttwEAf//9N9ra2uDxeNDW1gaXy4WtW7eqPGKKp+BZCKVmE2w2GwoKCpCZmYlz587B5/Ohr68PhYWFWLBgQchrFi1ahEWLFsl/fvLkCU6dOgVRFGG1WnHgwAFs3rx5ymObiuCFf+DVdFZjY6N8YJzWxDSAWCwW7NmzJ5YfQSq7ceMGLl26BEEQkJeXB6fT+Ubn36GhIVRWVqK6uhoXL14EAAYRE4nluT8bNmzAO++8g1OnTuGvv/7Cl19+ic8++0xeNB9PU1MTzp49ixcvXmDevHkoLCxEWlqaYuOKVvDCvyiKuHfvHhoaGswZQMxG6QKecNsdqFWx3dPTA7fbDUEQcOjQIaxfvz7k61JSUuByuZCeno6SkhK43W5kZGRg4cKF8R0wxV08zv2ZP38+jh07hh9++AENDQ04ffo0urq6sH//fnnKSjIyMoLLly/LRz7n5OTg4MGDURXsRcKoC/8MIAoxQ9uC15WWlmJ0dBR5eXnjBo9g69evR3d3N6qrq1FWVoajR4/GYZSkpuAdmABQW1sbkzXN6dOn48iRI0hLS0NpaSnq6urgcrneeJ0oiqirqwMA5Ofnh1VWoBQjLvwzgCgsVjfy8d5XrcD19OlTeL1e2Gw2OJ3OsK/btWsXampq4PF4MDg4yN1ZBqbGuT/S9OnSpUtDHvdstVqxdOlSNDc3x/WQNaMu/DOAUFQ6OjogiiKWLFkS0S9iSkoKsrKy8ODBA3R2dmLt2rUxHCWpKVT9V6zru1paWgAAq1atAvDqpnvhwgX4/X4cPHgQM2bMwKpVq9Dc3IzW1ta4bpE14sK/ogFEj83WKDr//vsvAET1FJmamooHDx7gn3/+UXpYpBETnfsTqyzE5/Oho6MDgiBgxYoV8Hg8+P777zEwMAAA+OOPP1BQUIAVK1ZAEAS0t7fD5/PF/cndSAv/irQyUbPtNlt+64+UeguCoPJIKFbG630Xy153Xq8Xfr8fdrsdFRUVKC4uxsDAADIyMpCRkYGBgQEUFxejou9KxwsAAArtSURBVKICdrsdfr8fXq9X0TGES1r4z8nJwfDwME6fPo3z58/LC+zBRkZGcP78eZw8eRIvXrxATk4Ovv32W9WDB6BgBsIbefSUrtKNB2lHyOPHjyO+VupvptXiKJoatc79aW1tBQD09vait7cXVqsVe/bskbfAXrt2DVeuXJF3YEnXrF69WpHPj5QeFv4no8qZ6DRWVVWVXKmrF5mZmfI0gLS4F47nz5+jvb0dgiAgMzMzhiMktUzWeTsWWYgoinIAAV7tSioqKoLD4YAgCBAEAQ6HA0VFRbDb7fLrWltb3+icEG/hLvwHv1YrGEBUJj2t1dfXy5mIHsyaNQvZ2dnw+XyorKwM+7qKigr4/X4sW7aMO7AMKJJzf5TsuP3w4UMMDg7KBa3FxcUhp3jS0tJQXFyMvLw8CIKAwcFBPHz4cMqfPxWhFv7PnDmD7777Tu7GK/1dcJDUAgYQlUlPa1LPLz3Zu3cvLBYLqqurcefOnUlfX19fj5s3b8JisSA/Pz8OI6R4U+vcn5aWFrz11lv46quvsG/fvpBP8hKr1Yp9+/bhm2++wdy5c+UbuBpCLfwXFhbizp07+PXXX/HFF1/A4/G8sfCvFQwgKgqu0rVYLLrLQtLT0+FyuSCKIkpKSnD58uWQ01nPnz/HpUuX8L///Q+iKMLlcmliAZCUpea5PykpKTh58iTee++9sK9ZvHgxTpw4oeq0kJ4W/kNhHYiK4lWlG0tSTyu3243q6mrU1NSEbKbo9/thsViwf/9+fPjhh2oOmWJEzXN/HA5HVNclJydHfa0S9Lbw/zoGEJWoUaUbK1u3bkVGRgbKysrg8XjemKeVKm7z8/OZeRgUz/2JXKiF/8OHD4/5HXE4HMjOzsaZM2fkNijSwr8WtsEzgKhEjSrdWFq4cCGOHj2KwcFBdHZ2yoWGs2fPRmZmJhfMDY7n/kQueOF/+/bt+Pjjj0Ou3UgL/z/++COuX78uL/y/++67Kox6LAYQFahRpRsvM2fOZHsSk4nnuT+vd7sIt2O1FkkL/59//vmkazfSwv+aNWtQUlKClpYWBhCzGm+umGfBkx4Z/dyfWBVJSwv/ycnJYV8jLfz/8ssvMRlTpBhA4kytKl0ivZvsRq63bhh6XfgPxm28caZGlS4RUSwwgMSRWlW6RESxwCmsOAp3n7zW1kLCPU5Xb4uYRPFg5N8LBpA4iaZKV+21kPLyctV++PU2n20m4f5MmP3hwgy/PwwgcaJmle5URPKDyJu+sZnhhqg0vY47XAwgccAqXTKKaG+IRr+RmhUDSBywSpeiodTTfqRTSbzZU7gYQGIsnlW6ZBxqrhns3r2bQYTConoAMfqcqtGrdCm2lP45nez9zLjYTdFTtQ5E7acsIiKKnuoZCBDdU9bLly8BvDqYPlIMHkREU6fbSvSmpiY0NzerPQwiItPSbQBpaGhAQ0OD2sMg0py+vj5dHY1M+qWJKaxIPXv2DG1tbfLXM2bMUHlE/+H0GKmtqqoKALjtm2JOlxnIvXv3EAgEEAgEcP/+fbWHA0DdvfPcckkSqWi1vr6eWQjFnC4zkOCpq7t372LLli0qjuY/vJGT2oKLVll8SrGmuwykv78fXV1dSExMRGJiIrq6utDf36/2sIhUJ2UfFosFFouFWQjFnO4CSGNjI0RRxMqVK7Fy5UqIoojGxka1h0WkOin7yM3NRW5urtwChyhWdDeFdffuXQDAunXrIIoi7t27h4aGBuTl5ak8MiL1vH5cwLRp02J+HIDRu0jQ5DQTQB4/fozh4WH4fD6MjIwAAEZGRjA8PCy/pr+/Hz09PUhOTsayZcsAvDofuLu7G9evX8ecOXPk1yYlJcndbBMSEmCz2ZCUlITU1NQ4/quI4iPUcQGxPA5A7S4SDCLaoJkAAgBnz57Fo0ePJn3dmjVrYLVa5a/r6urgdrsnvMZut6OwsFCRcRJpyXiHlcXjULJ438i5TV5bNBNAUlNTcfz4cVy4cAG1tbUAAEEQsHz5cthsNgBASkoKAGDTpk3ydR988IGcaQwNDQEAfD4ffvvtN4iiCADYuHEjPv30U/l9iIxkvMPKtHIoGRmXZgIIANhsNhQUFCAzMxPnzp2Dz+dDX18fCgsLsWDBgpDXLFq0CIsWLZL//OTJE5w6dQqiKMJqteLAgQPYvHlzvP4JRHE12VHJWjgamYxL1V1Y5eXlIVPgDRs24Ntvv8WCBQvwf//3f/jyyy/DalvS1NSEo0ePore3F/PmzUNRURGDBxmalH1s2LAhZHCQspDR0VFcvXpVhRGSkWl2G+/8+fNx7Ngx5OTkYHh4GKdPn8b58+flBfZgIyMjOH/+PE6ePIkXL14gJycH3377LdLS0lQYOVF8TJZ9SJxOJywWC27fvo0nT57EcYShsVeXcWg2gACvWrUfOXIE+fn5AIC6ujp5XSOYKIqoq6sDAOTn5+PIkSNRtXkn0pPJsg+J1rKQqqoq1qcYhOoHSoWzq0JaPF+6dKm8+yqY1WrF0qVLx7yWyMjCzT4kWslC2KvLWDS1iD6elpYWAMCqVasAvNptdeHCBfj9fhw8eBAzZszAqlWr0NzcjNbWVs30xjIqFpCpb7ydV+PRyo4s9uoyFs0HEJ/Ph46ODgiCgBUrVsDj8eD777/HwMAAAOCPP/5AQUEBVqxYAUEQ0N7eDp/Pxy27McICMvVJT/HAqyLZn376KazrpO3u9fX1cDqdmDt3bszGGEpwry41x0HK0XwA8Xq98Pv9SEtLQ0VFBX7++WeIooiMjAwAwO+//47i4mK8//77sNvt6O3thdfrxerVq1UeubGxgEw9wU/xNTU1EV8v9ciK99N/cNYEALW1tcxCdE7zAaS1tRUA0Nvbi97eXlitVuzZs0fufXXt2jVcuXIFt27dGnMNAwgZUSAQwOzZs7Fjx44pvU9CQgICgYCcDcSaGr26KPY0HUBEUZQDCPCqHcnhw4fHbM91OBzIzs7GmTNn5DYora2tEEURgiDEfcxEsWSxWLBnzx61hxGxePfqovjQ9Dbehw8fYnBwEIIgIC8vD8XFxSFrO9LS0lBcXIy8vDwIgoDBwUE8fPhQhRET0esm6tWlhZ1hFD1NB5CWlha89dZb+Oqrr7Bv376QW3glVqsV+/btwzfffIO5c+fKO7dIO1hAZk7j1atorT6FIqfpAJKSkoKTJ0/ivffeC/uaxYsX48SJE6wH0SAWkJlPOL26mIXol6YDiMPhQHJycsTXJScnw+FwxGBEFC0WkJkTe3UZm6YX0ck4WEAWHT1vX46kVxd3ZOmTpjMQMobgAjKLxcIsJAxqFkwq9dl67dVF4dNEBqLnpyyaHAvIoqPnqvtoenUxC9Ef1c8DMeNnm8nrNxIumppDuNmHhFmIPqmegfBGbmwsIDMfvfbqosipHkDIuCYqION0hXHptVcXRY4BhGJmvJbjWmktTsrTa68uig4DCMVEOAVkzEKMR6+9uig63MZLMcECMiLjYwAhxUVSQMYdWUT6xQBCimMBGZE5MICQoqIpIGMWQqRPXEQnRY2382o83JGlb6G6SATXdrHLhLExgJBiWEBmHuXl5aoFBxYfawcDCCmGBWTmEs6NnDd7Y2MAIUWwgIzIfBhASBEsICMyH+7CIiKiqDCAEBFRVBhAiIgoKgwgREQUFS6iU1RiUQPAAjQifWEGQhHhMcREJBFEURTVHgQREekPMxAiIooKAwgREUWFAYSIiKLCAEJERFH5fw5fcVSqW1W9AAAAAElFTkSuQmCC</v>
+      </c>
+      <c r="E385" t="str">
+        <v>24-08-2026 01:58:50 pm</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="str">
+        <v>6a8c026d2969f40a948868aa</v>
+      </c>
+      <c r="B386" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C386" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D386" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E386" t="str">
+        <v>24-08-2026 02:05:57 pm</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="str">
+        <v>6a8c026d2969f40a948868b0</v>
+      </c>
+      <c r="B387" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C387" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D387" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E387" t="str">
+        <v>24-08-2026 02:05:57 pm</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="str">
+        <v>6a8c02722969f40a94886996</v>
+      </c>
+      <c r="B388" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C388" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D388" t="str">
+        <v>Started Playing game and Debited "10" and Balance "580"</v>
+      </c>
+      <c r="E388" t="str">
+        <v>24-08-2026 02:06:02 pm</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="str">
+        <v>6a8c02732969f40a9488699c</v>
+      </c>
+      <c r="B389" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C389" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D389" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E389" t="str">
+        <v>24-08-2026 02:06:03 pm</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="str">
+        <v>6a8c02e32969f40a948869c3</v>
+      </c>
+      <c r="B390" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C390" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D390" t="str">
+        <v>Answered incorrectly for Qst ID: 6a8c02732969f40a948869a6, Qst: What is the alphabetical arrangement of these random letters: "ike"?, Submitted Answer: None of the above, image : iVBORw0KGgoAAAANSUhEUgAAAZAAAAD6CAYAAACPpxFEAAAABmJLR0QA/wD/AP+gvaeTAAAPc0lEQVR4nO3df1TU9Z7H8ReC/FBBBK5WamrI9UdQaeJFc20xK243WsOulquV0lrX7bid6qS76h+cs3Xy7tHdyt0DbeHKbimmncrOmpDmRetEkmih5C+KlERIGJOAcRhm/+heVsOZ4K3OCDwf5/iHM5/5zvvMQZ98v9+Z7wRVV1d7wsLCBABARzmdToWEhYUpOjo60LMAALoQh8OhXoEeAgDQNREQAIAJAQEAmBAQAIAJAQEAmBAQAIAJAQEAmBAQAIAJAQEAmBAQAIAJAQEAmBAQAIAJAQEAmBAQAIAJAQEAmBAQAIAJAQEAmBAQAIAJAQEAmBAQAIAJAQEAmBAQAIAJAQEAmBAQAIAJAQEAmBAQAIAJAQEAmBAQAIAJAQEAmBAQAIAJAQEAmBAQAIAJAQEAmBAQAIAJAQEAmBAQAIAJAQEAmBAQAIAJAQEAmBAQAIAJAQEAmBAQAIAJAQEAmBAQAIAJAQEAmBAQAIAJAQEAmBAQAIAJAQEAmBAQAIAJAQEAmBAQAIAJAQEAmBAQAIAJAQEAmBAQAIAJAQEAmBAQAIAJAQEAmBAQAIAJAQEAmBAQAIAJAQEAmBAQAIAJAQEAmBAQAIAJAQEAmBAQAIAJAQEAmBAQAIAJAQEAmBAQAIAJAQEAmBAQAIAJAQEAmBAQAIAJAQEAmBAQAIAJAQEAmBAQAIAJAQEAmBAQAIAJAQEAmBAQAIAJAQEAmBAQAIAJAQEAmBAQAIAJAQEAmBAQAIAJAQEAmBAQAIAJAQEAmBAQAIAJAQEAmBAQAIAJAQEAmBAQAIAJAQEAmBAQAIAJAQEAmBAQAIAJAQEAmBAQAIAJAQEAmIQEegBcOa6y/5CrPPei94WOX6KQ+N/7eaLAObr7O32+6chF7xs7/Xol3TuiU9trOefW9pdK5aj60ee6m++7QaOnDe3Utq8mK0rXqrj2qyv6HDdGD9e/TvzDFX0OXBkEpBvzNNep9YevL36f8wc/TxNY55padLam8aL3OX90dWpbnlaPdv77fh0vrfW5LjFteJeOhyTVNDv07Y81V/Q5YsOiruj2ceVwCAvoDI+0+7UyfbPnlM9lo/56iFLmjfHTUEBgEBCgE4rXf6VDO0/4XPPrqYM15e8SpSA/DQUECAEBOmj/exX68v2LHxL8ixG/uUZ/tTBJQUHUA90f50CADjiyq0p78g/5XDM8eZBSn7xFQb16RjzCg0MVdBl2syJCQi/DNAgEAgL8gsrPa7Tr1S8lj/c1Q27+lVKfvEW9gntGPCQp97ZnNT42IdBjIIA4hAX4cPJgnXa8XKpWt/d6DE6K051Pj1dwb/45oWfhJx7wou7bsypcvVduV6vXNYN+PYB4oMfipx64iB9ONWrri3t0rtH7Z0QGJkQrbekEhYQF+3Ey4OpBQICfaax3ausLn6nJ4fS6JnZYlO5+boJ6h3MaET0XAQHOc66xRR/8cY/O1jZ5XRNzfaTuWTZRYX17+3Ey4OpDQIA/aznnVsG/lKiu8qzXNf2v7avfLk1WWD/iAbD/DUhqdXu0/d9KVX2o3uuaoKAg3f3cBEVEh/lxsqvXtu9KdMDxzSVtY1xMghIHDL8s88D/CAh6PI+k3f/5pY7v831xRI/Ho4PbKpXyMNe4kqR1RwsueRtPjc0gIF0Yh7DQ4321/VsdLqrq0NoD2ypVc8RxhScCugYCgh7P2dDxy7l7PB79KfsLn58NAXoKAgJ00pmTP2rfO0cDPQYQcAQEuIi+MeGKG+H9i472v1fh891aQE/ASXTgZyL6h+m3/5gst6tV7yz/RJ7W9tfBanV7tDN7v2b882096gKK5/v70X+jYf0GXdI2xvS//jJNg0AgIMB5IqJC9bvlExU9uJ+kn75Z8Ksdxy+6tq7yrL783691c/oN/hzxqnHbwBu5Gm8PxyEs4M/Co0J1z7L/j4ckJT84yueHBvduOiJHVYM/xgOuOgQEkBTap7fSliRrwNDIC24P69db4zJGen2c29Wqole/lMfj48tCgG6KgKDHC+0Tonv+KdnrSfOxdw5TzM/Ccr6aIw6VF357pcYDrloEBD3emOnXK+6G/l7v7xUcpN/M8/3p8z0bDqvhe+8XYAS6IwKCHi8o6JffRTU4MVbDk72/48jV3KKiX/jaW6C7ISBAB6XMG+Pzy6O+KzutI7s7dkkUoDsgIEAH9YuLUNLvRvhc8+l/l6vpjPcvogK6Ez4HAnTCzffdoKO7qrx+4ZSzwaVP/uug7viHcX6ezP/21x3TWdflOe+TEDVY1/WJvSzbgv8QEKATQkKDlfzQKO14eZ/XNV8XV+ubPad8njPpDlaW5V+2bS2/6W81N376Zdse/INDWEAn3ZByra4d6/u35Y/XHpDzx45f5RfoiggIYDD50bE+r4HV5HCq+H++8uNEgP8REMBgwJB+Gn2H7wsBHv7TCZ344ns/TQT4HwEBjG79fYLCI0N9rtn9WplczS1+mgjwL06id2PB192u0F4XvxBg8K/G+3mawIobEeX1qrnXjIkxbTOsb2/d/oebVF1e53Nd/fEGDUyINj1HoKUPmaSkaN9vXb4cborpmVc07uqC6uvrPdHRXfOHGwAQGA6Hg0NYAAAbAgIAMCEgAAATAgIAMCEgAAATAgIAMCEgAAATAgIAMCEgAAATAgIAMCEgAAATAgIAMCEgAAATAgIAMCEgAAATAgIAMCEgAAATAgIAMCEgAAATAgIAMCEgAAATAgIAMCEgAAATAgIAMCEgAAATAgIAMCEgAAATAgIAMCEgAAATAgIAMCEgAAATAgIAMCEgAAATAgIAMCEgAAATAgIAMCEgAAATAgIAMCEgAAATAgIAMCEgAAATAgIAMCEgAAATAgIAMCEgAAATAgIAMCEgAAATAgIAMCEgAAATAgIAMCEgAAATAgIAMCEgAAATAgIAMCEgAAATAgIAMCEgAAATAgIAMCEgAAATAgIAMCEgAAATAgIAMCEgAAATAgIAMCEgAAATAgIAMCEgAAATAgIAMCEgAAATAgIAMCEgAAATAgIAMCEgAAATAgIAMCEgAAATAgIAMCEgAAATAgIAMCEgAAATAgIAMCEgAAATAgIAMCEgAAATAgIAMCEgAAATAgIAMCEgAAATAgIAMCEgALqtiooKxcfHt/1JTExUZmam6urqAj1am/fff19Llixpd3t6erqOHTtm3u6SJUs0ffr0tr/Pnz9fGzZsuGBNa2urUlJSVFlZqaysLOXk5HTqOQgIgG7L5XKpublZJSUlKikpUUFBgRobG/X0008HerQ2DQ0Nqq2tbXd7VVWVzp07Z9pmU1OTNm/erKCgIO3evVuSNH36dOXm5l6wbufOnQoODtawYcN0+vRpORyOTj0PAQHQrfXq1UsDBgzQgAEDdN1112nBggX64osvJEmHDx/Wgw8+qJSUFD3zzDM6e/astmzZojVr1kiSjh8/rrS0tLb/yJcuXapDhw7p1KlTWrBggSZPnqwnn3xSZ86ckSQ99dRTeuWVVzRt2jQdO3ZM+/bt04wZMzRlyhStXLlSbrdbklRcXKy7775bd911l4qLi73Onp+fr6lTp2ru3LmqqqrS999/r5kzZ6q1tVWSVFdXp4cffrjd4zZv3qxJkyZpzpw5ys7OliRlZGRo7969OnnyZNu6devWKTMz0/7amh8JAF1AS0uLKioqVFFRoc8//1wvvfSSpk6dKqfTqfT0dM2dO1dFRUXq3bu3Fi1apFGjRum1116TJG3btk1FRUX67LPP1NzcrA0bNig+Pl4zZ85UamqqioqKNHLkSD3xxBOSpJKSEn388cdasWKF+vbtq4yMDC1fvlwffvihysrKtGbNGjU2NiojI0NZWVnauHGj9uzZ43X2yspKFRYWKjU1VQ899JDi4uJUXV2tXbt2SZI2btyoQYMGtXtcbm6u5s2bpwceeEBbt25VbW2tIiIiNHv2bK1fv17ST3s+hYWFmj17tvm1JSAAurW6ujrNmjVLs2bN0rJlyzRx4kS98MILOnDggGJiYnTvvfcqNDRUK1as0LvvvquEhAS5XC5VV1ersLBQjz/+uHbs2KGdO3cqNTVVNTU12r9/v5qampSbm6vQ0FBt2bJFHo9HkpSZmanU1FR98sknioyM1N69e5WXl6drrrlG77zzjj799FONHj1aKSkpio6O1qJFi7zO/txzzyksLEyZmZk6ePCgzpw5o0cffVRvvPGGJCkvL0+PPPLIBY+pqKhQSUmJPB6PiouLNWbMGK1du7Zttr88dtOmTUpPT1ffvn3Nr22I+ZEA0AUMHDhQJSUl7W5vaGhQnz592v4eFhYmp9Mpt9ut9PR0bdu2TeXl5Xr++ef12GOPqba2VjNmzGj3uJCQEK1evVoul0uSFBsb27b9iIiItnUJCQmaOHGimpqaFB4e3nZ7ZGSk19nPvy88PFwul0uzZ89WVlaWDh48KJfLpcTExAses3btWiUlJentt9+WJA0dOlSvvvqqnn32WY0fP14ej0fl5eXKy8vTypUrO/QaesMeCIAe6cYbb1R5ebmqq6slSVu3blViYqJCQkJ03333adWqVbrllls0cuRInTx5UgUFBbrzzjs1fPhwhYSEaMqUKVq4cKEmT56sDz74QKGhoRdsf8KECaqpqdGcOXO0cOFCRUZGqqysTBMmTFBpaWnbO8G2b9/udcbCwkJJUmlpqfr166e4uDhFRUVp2rRpWrx4cbu9D7fbrXXr1ik7O1s5OTnKycnRm2++KY/Ho4KCAkk/7YW8/PLLcjgcSk5OvqTXkD0QAD1SbGysVq9erdtvv10jRozQiRMnlJeXJ0lKSUnRqVOndMcdd0iSpk6dqtOnT7fteeTm5ur+++9XQkKCjh49qlWrVrXb/tixY7V48WLdeuutio+P14kTJ7Rp0yYNGjRIWVlZmjRpkoYOHarg4GANHjz4ojO+9957Wr9+vY4fP67XX3+97fb58+crLS1N+fn5F6wvLCxUTEyMkpKS2m4LCgrS/PnzlZ2drbS0NM2ZM0dDhgzRiy++eGkvoKSg+vp6T3R09CVvCAC6IrfbrdraWg0cOFC9enX8oIzH41FNTY1iY2MVEuL9d/GWlhadPn263cnuxsZGud1un4ewJKm+vl79+/e/YLaPPvpIOTk57T7X4U8Oh4OAAEBXsmzZMuXn5+utt97SuHHjAjYHAQGALqa0tFRRUVGKj48P6BwOh4NzIADQlQRyr+PneBcWAMCEgAAATAgIAMCEgAAATAgIAMCEgAAATEKcTmenv0QEANCzOZ1O/R8umuIqliWMqQAAAABJRU5ErkJggg==</v>
+      </c>
+      <c r="E390" t="str">
+        <v>24-08-2026 02:07:55 pm</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="str">
+        <v>6a8c02f12969f40a948869d9</v>
+      </c>
+      <c r="B391" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C391" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D391" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E391" t="str">
+        <v>24-08-2026 02:08:09 pm</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="str">
+        <v>6a8c02f12969f40a948869df</v>
+      </c>
+      <c r="B392" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C392" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D392" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E392" t="str">
+        <v>24-08-2026 02:08:09 pm</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="str">
+        <v>6a8c02f82969f40a94886ac6</v>
+      </c>
+      <c r="B393" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C393" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D393" t="str">
+        <v>Started Playing game and Debited "10" and Balance "570"</v>
+      </c>
+      <c r="E393" t="str">
+        <v>24-08-2026 02:08:16 pm</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="str">
+        <v>6a8c02f82969f40a94886acc</v>
+      </c>
+      <c r="B394" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C394" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D394" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E394" t="str">
+        <v>24-08-2026 02:08:16 pm</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="str">
+        <v>6a8c03052969f40a94886af6</v>
+      </c>
+      <c r="B395" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C395" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D395" t="str">
+        <v>Answerd Correctly to Qst ID : 6a8c02f92969f40a94886ad6, Reward : 10, Qst No : 2 ,Question : How many words are scrambled?</v>
+      </c>
+      <c r="E395" t="str">
+        <v>24-08-2026 02:08:29 pm</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="str">
+        <v>6a8c03082969f40a94886b0d</v>
+      </c>
+      <c r="B396" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C396" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D396" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6a8c03082969f40a94886b05 , Question : How many words are colored with the WRONG color?, Type : word_colour_find </v>
+      </c>
+      <c r="E396" t="str">
+        <v>24-08-2026 02:08:32 pm</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="str">
+        <v>6a8c03102969f40a94886b22</v>
+      </c>
+      <c r="B397" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C397" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D397" t="str">
+        <v>Answerd Correctly to Qst ID : 6a8c03082969f40a94886b05, Reward : 40, Qst No : 3 ,Question : How many words are colored with the WRONG color?</v>
+      </c>
+      <c r="E397" t="str">
+        <v>24-08-2026 02:08:40 pm</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="str">
+        <v>6a8c03142969f40a94886b39</v>
+      </c>
+      <c r="B398" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C398" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D398" t="str">
+        <v xml:space="preserve">Created Question Number : 2, Rupees : 30, Qst ID : 6a8c03132969f40a94886b31 , Question : Decode "Y" using cipher key, Type : encode_decode </v>
+      </c>
+      <c r="E398" t="str">
+        <v>24-08-2026 02:08:44 pm</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="str">
+        <v>6a8c031a2969f40a94886b4e</v>
+      </c>
+      <c r="B399" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C399" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D399" t="str">
+        <v>Answerd Correctly to Qst ID : 6a8c03132969f40a94886b31, Reward : 30, Qst No : 4 ,Question : Decode "Y" using cipher key</v>
+      </c>
+      <c r="E399" t="str">
+        <v>24-08-2026 02:08:50 pm</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="str">
+        <v>6a8c03252969f40a94886b65</v>
+      </c>
+      <c r="B400" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C400" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D400" t="str">
+        <v xml:space="preserve">Created Question Number : 3, Rupees : 40, Qst ID : 6a8c03242969f40a94886b5d , Question : How many puzzle pieces contain 2 or more MALE connectors (outward tabs)?, Type : puzle_peace_male_female </v>
+      </c>
+      <c r="E400" t="str">
+        <v>24-08-2026 02:09:01 pm</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="str">
+        <v>6a8c03302969f40a94886b7a</v>
+      </c>
+      <c r="B401" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C401" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D401" t="str">
+        <v>Answerd Correctly to Qst ID : 6a8c03242969f40a94886b5d, Reward : 40, Qst No : 5 ,Question : How many puzzle pieces contain 2 or more MALE connectors (outward tabs)?</v>
+      </c>
+      <c r="E401" t="str">
+        <v>24-08-2026 02:09:12 pm</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="str">
+        <v>6a8c03332969f40a94886b91</v>
+      </c>
+      <c r="B402" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C402" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D402" t="str">
+        <v xml:space="preserve">Created Question Number : 4, Rupees : 50, Qst ID : 6a8c03322969f40a94886b89 , Question : How many times does the letter sequence 'the' appear in the given words?, Type : count_word_exist </v>
+      </c>
+      <c r="E402" t="str">
+        <v>24-08-2026 02:09:15 pm</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="str">
+        <v>6a8c03422969f40a94886ba6</v>
+      </c>
+      <c r="B403" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C403" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D403" t="str">
+        <v>Answerd Correctly to Qst ID : 6a8c03322969f40a94886b89, Reward : 50, Qst No : 6 ,Question : How many times does the letter sequence 'the' appear in the given words?</v>
+      </c>
+      <c r="E403" t="str">
+        <v>24-08-2026 02:09:30 pm</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="str">
+        <v>6a8c03672969f40a94886bc1</v>
+      </c>
+      <c r="B404" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C404" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D404" t="str">
+        <v xml:space="preserve">Created Question Number : 5, Rupees : 80, Qst ID : 6a8c03672969f40a94886bb9 , Question : How many broken boxes are there?, Type : Total Boxes [Broken] </v>
+      </c>
+      <c r="E404" t="str">
+        <v>24-08-2026 02:10:07 pm</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="str">
+        <v>6a8c03752969f40a94886bd6</v>
+      </c>
+      <c r="B405" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C405" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D405" t="str">
+        <v>Answerd Correctly to Qst ID : 6a8c03672969f40a94886bb9, Reward : 80, Qst No : 7 ,Question : How many broken boxes are there?</v>
+      </c>
+      <c r="E405" t="str">
+        <v>24-08-2026 02:10:21 pm</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="str">
+        <v>6a8c037a2969f40a94886bf1</v>
+      </c>
+      <c r="B406" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C406" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D406" t="str">
+        <v xml:space="preserve">Created Question Number : 6, Rupees : 110, Qst ID : 6a8c037a2969f40a94886be9 , Question : How many letters are misaligned?, Type : letters_missalign </v>
+      </c>
+      <c r="E406" t="str">
+        <v>24-08-2026 02:10:26 pm</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="str">
+        <v>6a8c03c42969f40a94886c17</v>
+      </c>
+      <c r="B407" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C407" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D407" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E407" t="str">
+        <v>24-08-2026 02:11:40 pm</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="str">
+        <v>6a8c03c42969f40a94886c1f</v>
+      </c>
+      <c r="B408" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C408" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D408" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E408" t="str">
+        <v>24-08-2026 02:11:40 pm</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="str">
+        <v>6a8c03cc2969f40a94886d07</v>
+      </c>
+      <c r="B409" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C409" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D409" t="str">
+        <v>Started Playing game and Debited "10" and Balance "560"</v>
+      </c>
+      <c r="E409" t="str">
+        <v>24-08-2026 02:11:48 pm</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="str">
+        <v>6a8c03cc2969f40a94886d0d</v>
+      </c>
+      <c r="B410" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C410" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D410" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E410" t="str">
+        <v>24-08-2026 02:11:48 pm</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="str">
+        <v>6a8c03d92969f40a94886d37</v>
+      </c>
+      <c r="B411" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C411" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D411" t="str">
+        <v>Answerd Correctly to Qst ID : 6a8c03cd2969f40a94886d17, Reward : 10, Qst No : 2 ,Question : What is the alphabetical arrangement of these random letters: "dok"?</v>
+      </c>
+      <c r="E411" t="str">
+        <v>24-08-2026 02:12:01 pm</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="str">
+        <v>6a8c03dc2969f40a94886d4e</v>
+      </c>
+      <c r="B412" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C412" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D412" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6a8c03dc2969f40a94886d46 , Question : How many words are colored with the WRONG color?, Type : word_colour_find </v>
+      </c>
+      <c r="E412" t="str">
+        <v>24-08-2026 02:12:04 pm</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="str">
+        <v>6a8c03e32969f40a94886d63</v>
+      </c>
+      <c r="B413" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C413" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D413" t="str">
+        <v>Answerd Correctly to Qst ID : 6a8c03dc2969f40a94886d46, Reward : 40, Qst No : 3 ,Question : How many words are colored with the WRONG color?</v>
+      </c>
+      <c r="E413" t="str">
+        <v>24-08-2026 02:12:11 pm</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="str">
+        <v>6a8c03e72969f40a94886d7a</v>
+      </c>
+      <c r="B414" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C414" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D414" t="str">
+        <v xml:space="preserve">Created Question Number : 2, Rupees : 30, Qst ID : 6a8c03e62969f40a94886d72 , Question : How many colour names match their text colour out of 8?, Type : [Colours &amp; Name Match] </v>
+      </c>
+      <c r="E414" t="str">
+        <v>24-08-2026 02:12:15 pm</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="str">
+        <v>6a8c03f32969f40a94886d8f</v>
+      </c>
+      <c r="B415" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C415" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D415" t="str">
+        <v>Answerd Correctly to Qst ID : 6a8c03e62969f40a94886d72, Reward : 30, Qst No : 4 ,Question : How many colour names match their text colour out of 8?</v>
+      </c>
+      <c r="E415" t="str">
+        <v>24-08-2026 02:12:27 pm</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="str">
+        <v>6a8c03f72969f40a94886da6</v>
+      </c>
+      <c r="B416" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C416" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D416" t="str">
+        <v xml:space="preserve">Created Question Number : 3, Rupees : 40, Qst ID : 6a8c03f62969f40a94886d9e , Question : How many times does the letter sequence 'avi' appear in the given words?, Type : count_word_exist </v>
+      </c>
+      <c r="E416" t="str">
+        <v>24-08-2026 02:12:31 pm</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="str">
+        <v>6a8c040a2969f40a94886dbb</v>
+      </c>
+      <c r="B417" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C417" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D417" t="str">
+        <v>Answerd Correctly to Qst ID : 6a8c03f62969f40a94886d9e, Reward : 40, Qst No : 5 ,Question : How many times does the letter sequence 'avi' appear in the given words?</v>
+      </c>
+      <c r="E417" t="str">
+        <v>24-08-2026 02:12:50 pm</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="str">
+        <v>6a8c040d2969f40a94886dd2</v>
+      </c>
+      <c r="B418" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C418" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D418" t="str">
+        <v xml:space="preserve">Created Question Number : 4, Rupees : 50, Qst ID : 6a8c040c2969f40a94886dca , Question : How many broken boxes are there?, Type : Total Boxes [Broken] </v>
+      </c>
+      <c r="E418" t="str">
+        <v>24-08-2026 02:12:53 pm</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="str">
+        <v>6a8c041b2969f40a94886de7</v>
+      </c>
+      <c r="B419" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C419" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D419" t="str">
+        <v>Answerd Correctly to Qst ID : 6a8c040c2969f40a94886dca, Reward : 50, Qst No : 6 ,Question : How many broken boxes are there?</v>
+      </c>
+      <c r="E419" t="str">
+        <v>24-08-2026 02:13:07 pm</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="str">
+        <v>6a8c04c32969f40a94886e02</v>
+      </c>
+      <c r="B420" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C420" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D420" t="str">
+        <v xml:space="preserve">Created Question Number : 5, Rupees : 80, Qst ID : 6a8c04c22969f40a94886dfa , Question : How many puzzle pieces contain 2 or more MALE connectors (outward tabs)?, Type : puzle_peace_male_female </v>
+      </c>
+      <c r="E420" t="str">
+        <v>24-08-2026 02:15:55 pm</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="str">
+        <v>6a8c04cd2969f40a94886e17</v>
+      </c>
+      <c r="B421" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C421" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D421" t="str">
+        <v>Answerd Correctly to Qst ID : 6a8c04c22969f40a94886dfa, Reward : 80, Qst No : 7 ,Question : How many puzzle pieces contain 2 or more MALE connectors (outward tabs)?</v>
+      </c>
+      <c r="E421" t="str">
+        <v>24-08-2026 02:16:05 pm</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="str">
+        <v>6a8c04e32969f40a94886e32</v>
+      </c>
+      <c r="B422" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C422" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D422" t="str">
+        <v xml:space="preserve">Created Question Number : 6, Rupees : 110, Qst ID : 6a8c04e32969f40a94886e2a , Question : How many times do the letters B, C, D, G, J appear in the paragraph?, Type : count_leters_exist </v>
+      </c>
+      <c r="E422" t="str">
+        <v>24-08-2026 02:16:27 pm</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="str">
+        <v>6a8c04f92969f40a94886e46</v>
+      </c>
+      <c r="B423" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C423" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D423" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E423" t="str">
+        <v>24-08-2026 02:16:49 pm</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="str">
+        <v>6a8c04f92969f40a94886e4d</v>
+      </c>
+      <c r="B424" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C424" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D424" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E424" t="str">
+        <v>24-08-2026 02:16:49 pm</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="str">
+        <v>6a8c052e2969f40a94886f36</v>
+      </c>
+      <c r="B425" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C425" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D425" t="str">
+        <v>Started Playing game and Debited "10" and Balance "550"</v>
+      </c>
+      <c r="E425" t="str">
+        <v>24-08-2026 02:17:42 pm</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="str">
+        <v>6a8c052e2969f40a94886f3c</v>
+      </c>
+      <c r="B426" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C426" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D426" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E426" t="str">
+        <v>24-08-2026 02:17:42 pm</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="str">
+        <v>6a8c05422969f40a94886f63</v>
+      </c>
+      <c r="B427" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C427" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D427" t="str">
+        <v>Answered incorrectly for Qst ID: 6a8c052f2969f40a94886f46, Qst: How many boxes are unbroken in total?, Submitted Answer: 12, image : iVBORw0KGgoAAAANSUhEUgAAAZAAAAD6CAYAAACPpxFEAAAABmJLR0QA/wD/AP+gvaeTAAAgAElEQVR4nO3deXxU5fX48c+dNclkQQIm7ARBJWVVEBTZlIogVAwUhUrcF1r6srXqt9h+sfJVq9VqW6ntr1SWWKGlgKgEhCBLwr5IWAKymAgIIUJC9swkmbm/P4YZEghkMpmZOzM577+GeJ+5Jwbm5Nznec6jqKqqIoQQQjSRTusAhBBChCZJIEIIIbwiCUQIIYRXDFoHIIQIPgP/33FN7rvrme6a3Fd4RyoQIUQ9WiUPre8tmk4qECFEg7ypBiprHABEGZv+u6kkj9AjFYgQwmc25FWwMa9C6zBEgEgCEUL4zJrjZaw5XqZ1GCJAvH6ENXnyZF/GAcCSJUsaff+61wghgkex1c6u01Xu160i9BpHJPzNqwrEH8kjFO4thLi6dbnl1DpUah0qX+aWax2OCIBmTaL7sxpo6L0leQgRvNYev5Q01hwvZ2JynIbRiECQORAhRLN9X1HLvrNVmA0KZoPCvrNVfF9Rq3VYws8kgQghmm3t8XIcKgztYmFoZwsOFdZ+I4+xwp3sAwkC+a/coMl92736jSb3FeHHtfJqdPcYUJ3zIWuPl/Fwn1aaxKPV4+6Wtsgn4AmkoKAAgISEhEDfOihplTxc95YkIq7lRHE1lTUq1loHNQ7nyQ81dqiqdW4YRIWCilq+Pm8j2qTjjk5RAESbdBw+Z+Pj/cUkWAygOC+PNOgwXlycZdQpRBh0RBkVurQy+SxmrRf5tKQkEvAEsnz5cgCmT58e6FsHNW8+yFWbc8OWYrY0eayWiUuEltkbCzheVN3odSOSojHpFffrlUdK+dO289cc0721iTd/mOiTOC8X6A/ylrjIJ6AJpKCggMzMTABSUlKkCmkm6+G1oEBk3we0DkWEqS6tTMx/oBN/2HyOz4+UAs5iYkhnCxEGBRSIMTmnUif0vLTq6sc/iMPVzaSs2gEqWGtVtpyswHWC3fibYnnpzrbO9xEhKaAJZPny5djtdvdrqUKap+rAZ6AokkCEX0UYFGaNuJ5b20fyVtY5qmodnC6r4c0fJtLtuoYfPSW3NZPc9nr3n0+W1PDrjHxUwKRXeGFIWx7oGRug70D4S8BWYbmqD71ej16vJzMz0z0fIprOUXkBW95WbLlbcFRe0Doc0QLcd2MMC1M60u06E3kXqnnsk+88aluyMa+CR5af4lhhNZ3jjCx4oJMkjzARsATiqj6GDRvGsGHDsNvt7vkQ0XTWnFVgrwV7Ldac1VqHI1qIpOtMzH+gI6O7x1BZ4+C3Xxbw1uZz7gn2umocKm9tPseLa/Mpr3YwunsMH03sRI94302Y+1pBQYH8YtsEAXmE5ao+dDodEyZMQKfTkZmZyaZNm5gwYQLt2rULRBhhperA5/VeRw2cqmE0LVeHLz/U5L6n735Ck/uCs1X7a3cn0D3exF93FJJ+pIxf3t7miutUFdKPOCuUnw2K59F+1wU61CaTRT5NE5AKxFV9DB8+nHbt2pGQkMCwYcNwOBysWLEiECGEFXvpWapP7kExRqAYI6g+uRt76Vmtw2pxtEoeWt/bJfbi5PmgjpHu1Vd1mfQKgzpG1rs2mLl+0ZXH657zewVyefXhkpKSIlWIl6wHPgfVgfmmu0FVseaswnpwJZY7ntQ6tBYp0NVAMCQPgMwTzmXkw7o6l5GXVTv4w+ZzVNtVZg5tS6sIPUO7WNj4bQVZJypJCfLeWLLIp+n8/mvB5dWHi1Qh3nM9vorsPZ7I3uPrfU2IQKiqdbD7TBU6xbmkd9upSib/5yRfHCtjfW45U/57im2nKrmziwWdArvOVF7afBiEZJGPd/xagVyt+nCRKqS+2vO5qNWVqDWVqPYa5xftNajVlc7Xqoq99Cw1+TkoETGYuw8DQImIoebMQSq2fog+NhEU5+MExRQFeqPztd6IYoxCMUVhaNMt4N+bCC87v6vCVqvSI97M3D1FLMspQQX6t3M+stqbX8Vzq84w8Qdx3NDazLFCGzu/q2J416Zveg0E1y+6I0eOBGDDhg1ShXjArwmk7g+loeTgqkI2bNjAihUr5IcFFK94idqCI41eF9HzHhSD2f26au8ySte8cc0xhoSbuG7yHJ/EKVq2rIuPr44V2jhWaMOkV3h2YGt+0sc5Uf7x/gv8fVcRS3NK6o0JxgQii3y857dHWI1VHy4pKSno9Xo2bdpEfn6+v8IJCYY23Wjz1DKi+k+69EVFwXzjSCJ+MJaIXvcRNeAhogY8hGXgw+5LLAMfdn89otd9RPxgLOYbR7orEYCo/pNo89QyqT5EsznUSwkEnO1IFjzQiWl9r0OngE6BaX2vY8EDneje+tKS3awTFTSw2ldzssjHe36rQBqrPlykCqlPMUYSN+EtTF0HU5I+C7W6EvuFU1w3eQ6G63s0OMbYoQ9xHfq4/1xbmEfxf2aAqqIYzMSOmUXUgIcC9S2Ia/i+uoptF/IpsFWiANebo7jjuna0NUVqHZrHcr63UlRlR6fA1N6tmH5bfIOrsHrEm1iY0om/7Sxk0YFiiqrs5HxvpXdChAZRN0wW+TSPXyoQT6sPF6lCrhTZ7wHaPP0Jhut7UHvuOOfnpng0UW49vJbz/3iAmoKvMcQnEf/0ckkeQeBAWSFT937BrZsX89ODG3j12A5+d2wHPz24gVs2L+bh7DUcLCvUOkyPZJ6oIDHawF/HdeC529s0mDxcTHqF525vw9z7O9Ix1livcgkGssinefySQK72Q7ka+WE1zNC2O22eXEZk7/Go1ZUUL/0FJemvXJpgr0O111CS/goX/j0d1VpGZO/xtHnmU4wJN2sQuajrn6dyuG/Xp2wqOo1Zp+eeNp15unMvnu7ci3vadMas07Oh8Dvu2/UZH57K0TrcRsWadSz+cWcGtPe8auqTEMFHEzsRYw6e/SCeLPKRX2yvzeePsOp23DUYDHz66aeeBWJwhpKZmSmdeutQzBZaTfoThoSbKVv3NlXZy4kd/fKVF6oOqrKdu2hjRr1I9NBnAxyp98J5N/c/T+XwytHtKMAznXvzi6R+xBrqt/Iora3mvby9zD15kFlHtwPwRKcf+D02b03r692O8miTzuux/iCLfJrP5wmk7macjIyMJo939chqyg+rJZzop4t0bsIydxviXn1Vl2IwY+42BOvXGe5rQ4HWu7n9mUQOlBUy+9gOFOAvPxhBSmLDf09jDSZe6TGIXjHxPJezidnHdjK4VSI/iIn3W2wtXVMW+chcyNX5NIHY7XZat27N/fff36z3MRgM2O129Hp9o9e2lBP9rF+vA8B88ygAHNZSStN/h1prI278a+iirsN8091Yv87AeuRLogZMCUhcvhKOu7nf/GY3dlXlmc69r5o86pqY2J0DZYXMPXmQN7/ZzUf9Rvs9xpZKFvn4hk8TiF6v58EHH/TlW3os0EezBjJxqdWVVH+7HRQdET1GYDueSfGK/8FR9j0A1ae+otWEt4i4cSQlio7qvG2o1ZXOjYRCE99XV5FZdJpIvYFfJPXzeNwvk/rx0XeH2Vh0mnPVVZquzhr4/45rdm9/8maRj1QhDQueGS1xVbbcrag1VowJN1G26X2K/vU4jrLvMXW5DVOX23CUfU/Rvx6nbNP7GBNuQq2xYsvdqnXYLdq2C/k4VJWh17W/Ys7jWuIMZoa0bo9DVdl+QZsGmbue6a7JfQN1b1nk4zsBPxNdNJ3tyJcA1Jw9TM3ZwygGEzF3PY/lDudjn4qtH1K2/l0qd/6r3piIi4+7RODlXzyvvltU0+ejboiK40tOccZW7uuwPKZlEvEnWeTjW5JAgp3qwHp0vfuPhoSbaDXx3XrLcy1DnsLUfSjFy553t0GxHl1PnOoARYpMLbh2Rniz8do1RkHOCvc1LRb5hDNJIEGu5vQ+HOXnQdFhuf1xYu7+FUoDj0SMCTfT5ukVlH35Ryq2zcNRfp6a0/swduyvQdT+FQq7uduZnT2fcitLGrnySq4xrvcQvqHFIp9w16wEMnnyZF/FEVCO8nPY8nbgKCsARUEXfT3mpMHooq88VU1r1q+/RB/XnlYPvI0pafA1r1UMJmJHzyQieTTFy3+F9cj6sEogB8oK+f3xXWRdOINDrf+7vU5RGN66A7++YQC9gmD56+Dr2qFTFDZfOENpbbXH8yDFNTa2FJ1Bpyjcfl2in6NsWbRc5BOuvEogS5Ys0Sx5LFmyxOuxNfk5lGW8jS13C6iXnU2g6DDfcCcxo17E2C65mVH6ji4yjrY/XYUSEePxGFOnW2j7zGdU7vm3HyMLrH+eymH2sR3YVZVIvYGh17Wna1QsAN9WlpJ14QwbCr8jq+gMs3rcpvlGvOtNkQxv3YENhd/xXt5eXukxyKNx7+Xtxeqwc1d8J9oEUUUlREO8rkCa80GuhYrtC5ztzh12FGMk5m5D0Md3AcBeeAJb7hZsxzOx5W4hdvRvsAx+ROOInSxDnvJqnBIR4/XYYBOqu7l/fcMAsorOMPfkQXrFxDMx8doT00vPHufDUzkYFB0zuw8IUJRCeK9FzIFUbF9A6er/A0XBcseTRA//GbqI2HrXOKyllG+aQ8W2eZSung0QNEmkJQvl3dy9YuKZ1eM2Zh3dznM5mzhQVsgvk/oRd1kngeIaG+/l7eXDUzmowCs9BpEc3VqboIVogrBPIDX5Oc7KQ1FolfJHIvs0PIGmi4gldvTLGBOTKf7kBUrXvI6p60CMicHzOKslCvXd3E90+gEKCq8e28Hckwf56LvD3Nm6A0kXH7/lVZayueg0Vocdg6LjdzcO4rGO8ndOhIawTyBl694Bhx3LHU9eNXnUFdl3AjX5OVRsm0fZundo/fC8AESpbUuWYBUOu7kBHu+UzKBWCbz5zW42Fp1m3fmT9f67TlG4K74TM7sPkMrDhxqbp637GD5UFwRpLawTiKP8HLZvNqMYI4ke/jOPx0UPn0Hl7kXYjmfhKD/v19VZ7V79pkU0g/RGc3dzf3n+FNsvnGV8QpIfo/TMD2Li+ajfaM5XV7HtwlnOXtxomGi2cPt1iTJh7kOhusgnFIV1ArHl7QDVgbnbkCvmPK5FFxmHKel2bEc3UP3tDiJ63efHKIP/g1wrob6buyFtTJFBkdDCXVM/yFvaB7+vhPU2ZUep8xAYfZum/4N1nR1uL5WDZLQiu7mFCG5hnUBQLn54qF58BKmXPoKENmQ3txDBLawTiC7W2WnTXpjX5LG1F8foY2U3sFYu383tKdnNLURghHUCMXe9DRQdttytOKylHo9zVBVTnbcNFF2j7UOE/7h2c1fZa3kvb6/H41y7uUe07iiT00L4UVhPouui22K+4U5sxzMp3zSn4bPEG1C+8X3UGivmHiPQWbTvq9SShcJubi2P5RVCS2FdgQDEjHoRdHoqts2jal/jh8FU7fuEih0LQacnZtQLAYhQXItrN7cKPJezid8d20FJre2K64prbLxydDu/yNkUsN3cgT6GN1juLYRLWFcgAMZ2ycSO/g2lq2dT/MkL1OTnED18BrrI+ktDHVXFlG9835k8VJXYMb/FmNhTo6hFXcG8m1s+yEVLFvYJBC72tFIUSr94jYpt86jcvQhT0h0Y4rsCUFv4LdV5zmNj0emJHfNbLINStQ1a1CO7uYUIPi0igQBYBqVi6jKAsnXvYDuehe3oeuo9CFF0mHuMIGbUC1J5BCnZzS1EcGkxCQTAmJhM64fn4agopDpvO/ayAgD0MQmYkgbLhHmIkN3cQgSHFpVAXHSWeL+3J2mI9OcRQoSTFplAtKBlt8/JkydLEhHCTwaO1ebcoF2rFmpy37okgQRYoD/IpU21EP6jVfJw3VvrJCIJRAghmsmbD/LKKisAUZERTR6rZeKqSxKICAqym1u0NBu27kFRYOxdQ7QOxWthk0DkRL/QdPruJzRLHrIJUGhpzcZtKIoiCURLLeFEv4IC53LjhISEgNwv0OSDXLQ0xaVl7Np3yP26VWyMxhF5J+QTCIT/iX7Lly8HYPr06RpHIoTwhXVZu6ittQPw5eZdTBx7l8YReSfsmymGuoKCAjIzM8nMzHRXIk2xZMkSWcIrRJBZu2m7+/WajduvcWVwC5oKRDbZNWz58uXY7Xb3a6lChAht358vYl/OUcwmEwD7co7y/fkirm8Tej3cgqIC0XqTXbByVR96vR69Xu91FSKECB5rN+3AoaoMHdSPoYP64VBV1mbu0DosrwRNBQKyye5yrupj5MiRAGzYsKHJVYjrewz2SkuIlmLNxcdXo0cMBhXWZe1k7cbtPJwyRuPImi6oEoi4xFV96HQ6JkyYgE6nIzMzk02bNjFhwgTatWundYhCiDpOfJdPpdWG1WqjpqYWgJraWqqsl/p+F5wv4uvj3xJtieSOW/sAEG2J5PDxb/n4ky9IqPMYKzLCjNHg/Ig2Gg1ERJiJijDTpWPw/NuXBBKk6lYfrmQxbNgwNmzYwIoVK2QuRIggNPvduRz/9rtGrxtxxwBMJqP79cqMLP40d/E1x3Tv2pE3X57hkzh9RRJIELq8+nBJSUmRKkSIINWlYzvmv/cKf/ggjc8zsgBQFIUhA/sQYTYDEBMdBcCE0SPc4358390YDXoAysorAbDabGzZtR9VVQEY/8OhvPTTVCLMpkB9Ox6RBBKEGqo+wLmRUKoQIYJXhNnErF8+ya19evLWXxdSZbVxOv8cb748g25dOjQ4JvnGJJJvvHS+zcnTZ/n1G3NQVRWTycgLzzzMA2NGBOg7aJqgWIXljeLiYrZs2cLKlStJT09ny5YtlJSUaB1Ws12t+nBJSUlBr9ezadMm8vPzNYhQCNGY++4ewsI//45uXTqQd+oMjz0/26P9Hhu37uGRX/yOY3mn6NwhkQXvvRK0yQNCsALJy8tj0aJF7N9/qbxzURSFvn37MmXKFJKSQvPEuqtVHy5ShQgRGpI6tWf+u7N44/35rNm4nd/+4W9kHzrK809PdU+Ou9TU1vLuPxaxdOWXgHOF1ss/f8yrTr2BFFIVyKpVq5g5cyb79u3DZDIxYMAAxo0bx7hx4xgwYAAmk4ns7GxefvllVq9erXW4TdZY9eEiVYgQoSEqMoLXXprOzx79MQDp6zajOtQrrlMdKunrNgPws0d/zGsvTQ/65AEhVIGsWrWKBQsWoCgK48ePJyUlBYvFUu+aiooKli1bRnp6OvPnzwdgzJjQWVvdWPXhIlWIEKElNtr5WTWofy/36qu6TCYjg/r3YuO2Pe5rQ0FIVCB5eXmkpaWhKAozZsxg2rRpVyQPAIvFQmpqKjNmzEBRFNLS0vj2228DH7AXPK0+XKQKESJ0ZO7YC8Cwwf0BKKuo5H/f/jv/8/r7FJeWATB0UD8Asnbu1SZIL4REAlm0aBEOh4Nx48YxdOjQRq8fOnQoY8eOxW63s3jxtddWBwtX9TF8+HCPlue6qhCHw8GKFSsCEKEQwhtVVhu79x1Gd3FJ77Y9B5j8zEy+2LCN9Vt2M+Wnv2XbngPceVtfdIrCruzD9TYfBrOgf4RVXFzM/v37MZvNpKSkeDxu0qRJZGRkkJ2dTUlJCXFxcX6Msnlc1QeAwWDg008/9Wic4eJEXGZmJikpKWF7XogQoWxndg626mp6dOvM3EWfsix9Paqq0r/XTQDsPXiE52b9kYn33cUNSZ04lnuSndk5DB98i8aRNy7oE0hOTg6qqtK7d+8GH1tdjcVioVevXnz11VccOnSI22+/3Y9RNk/djrsZGRlNHm+326VTrxBBKmtHNgDHck9yLPckJqOBZ6dN5CcTnfOzHy9bzd8/WuZegeUaIwnEB4qKigC82nXdvn17vvrqK86fP+/rsHzGbrfTunVr7r///ma9j8FgwG63o9frfRSZEKK5HKrqTiDgbEcy+8Vn6ZHUyf21aZPGMvjW3sx6++/uNihZO7JxqCo6RQl4zE0R9AmkOVz7RJQg/iHo9XoefPBBrcMQQvhBzpFciopL0CkKUx+4l+mPTMJkvPJjt0dSJxb++VX+tnApiz75gqLiEnKO5NL7Zm2O6/ZU0E+ix8fHA3DmzJkmj3WtTnK9hxBCBFLm9q9IbBvPX3//Pzz35EMNJg8Xk9HAc08+xNx3fkPHdteTtSP4V2MFfQJJTk5GURQOHjxIRUWFx+PKy8s5ePAgiqKQnJzsxwiFEKJhsdEWFn/wOgP69PR4TJ+ePfjoL7OJsUT5MTLfCPoE0qpVK/r27YvNZmPZsmUej1u6dCnV1dX069cvqFdgCSHC17RJY4m2RDZ5XLQlkmmTxvohIt8K+gQCMGXKFPR6Penp6WRlZTV6fWZmJqtXr0av1zN16tQARCiEEC1PSEyiJyUlkZqayvz585kzZw65ublMmjTpimW95eXlLF26lNWrV6OqKqmpqXTp0kWjqBsW7MfoCiGEp0IigcClnlZpaWmkp6eTkZFB7969SUxMBODs2bMcOHCA6upq9Ho9jzzyCPfee6+WIdezZMkSzZKHnIcuhH8NHPuI1iFoImQSCDiTSM+ePVm8eDHZ2dns2bOn3n9XFIX+/fszderUoKs8QD7IhQg3u1Yt1Cx57Fq1UJP71hVSCQSga9euzJw5k5KSEg4dOuTeaNi6dWuSk5NlwlwIEVDB8EGulZBLIC5xcXFB3Z5ECCHCXUiswhJCCBF8JIEIIYTwiiQQIYQQXpEEIoQQwitBNYnuzT6JuktjZZOeEEIETlAkENlkJwJB/o4J4VuK6jo0Q4gwpnV1KklEhKOgqECECJRAf5BrnbiE8CeZRBdCCOEVSSBCCCG8IglECCGEV0JyDqTvnuc1ue++W9/V5L5CWwUFBQAkJCRoHIkQwSXkKhCtkofW9xbaWb58OcuXL9c6DCGCTkhWIBD4akCSR8tUUFBAZmYmACkpKU2uQmT5rghnIVeBCBFIy5cvx263Y7fbpQoR4jKSQIS4Clf1odfr0ev1ZGZmuudDhBCSQIS4Klf1MWzYMIYNG+ZVFTJ58mTZTCjCVotKIN/ZCvnOVqh1GCIEuKoPnU7HhAkTSElJQa/Xs2nTJvLz87UOT4ig0KISyNyz65h7dp3WYYgQ4Ko+hg8fTrt27UhISGDYsGE4HA5WrFihdXhCBIUWk0C+sxWysnA3Kwt3SxUiruny6sNFqhAh6msxCWTu2XXUqnZqVbtUIeKaLq8+XKQKEaK+FpFAXNWHQdFjUPRShYirulr14SJViBCXtIgE4qo+xsUPYFz8AKlCxFVdrfpwkSpEiEvCPoG4qg+douOJxLt4KnEUBkXPZ4W7OGk7p3V4Iog0Vn24SBUihFPItjLxlKv6mNBmEJ3NbQEYFz+AFed38OHZ9bza5UGNIwwe+a/coMl92736jSb3vZyr+hg5cmSD1YeLqwrZsGEDK1asYPr06QGMUojgEdYVyOXVh4tUIVfSKnlofW8XT6sPF6lChAjzCqSh6gOgozleqpCr8KYaUG0VAChmS5PHBkPyAM+rDxepQoQI4wRyterD5anEUaws3M1nhbt4IvGueglGNI318FpQILLvA1qH4pW6HXcNBgOffvqpR+MMBuc/n8zMTK869QoR6sI2gVyt+nCRKsR3qg58BooSsgnEVX0AZGRkNHm8q0eWVCGipQnLBNJY9eEiVUjzOSovYMvb6n6ti7pO44iaxm6307p1a+6///5mvY/BYMBut6PX630UmRDBLywTSGPVh4tUIc1nzVkF9tqLr1cTNXCqxhE1jV6v58EH5efuK1p1Hq57cJcceR04YbcKy9Pqw0VWZDVP1YHPG3wtWh4t29a77i1HXgdW2FUgnlYfLlKFeM9eepbqk3tQjBEAVJ/cjb30LPrYRI0jE1oK9DG+DSUuOfI6MMIqgbiqDwCjomfe2fUejTMqzufWKwt381TiKDqa4/0WYzixHvgcVAfmm+4GVcWaswrrwZVY7nhS69CEEAEQVgnEVX0A/Pfc1iaPd/XIkirEM65HVpG9x7sTSNWBzyWBCNFChE0CqVXtXG+M5XEP5j2uxaDoqVXtGJSWu5qm9nwuanUlak0lqr3G+UV7DWp1pfO1qmIvPUtNfg5KRAzm7sMAUCJiqDlzkIqtHzofYymK8+umKNAbna/1RhRjFIopCkObbgH/3uR4WSF8J2wSiEHR87P2Y7QOI2wUr3iJ2oIjjV4X0fMeFIPZ/bpq7zJK17xxzTGGhJu4bvIcn8TpqSVLlgTFCiERvFxHPMgjbM+FTQIRvmNo0402Ty2jNP13VO5d6vyiomDuMQLFGAmKgi4iBoCoWy497rMMfBjlYqXhsJaBqqLWVGE7thFU1Xl9/0nE3vc75/sEmHyQB5/i4mJycnK4cOECiqLQqlUrevXqRVxcXMBjcR3xII+wPScJJIgEUzdcxRhJ3IS3MHUdTEn6LNTqSuwXTnHd5DkYru/R4PsYO/QhrkMf959rC/Mo/s8MUFUUg5nYMbOIGvCQ374PETry8vJYtGgR+/fvR734y4WLoij07duXKVOmkJSUFJB46i7AkYU0npMEEiSCtRtuZL8HMHbozYUlM6j9/hjn56YQ96M3nBPn12A9vJbiFS+hWsswxCfR6sE5GBNu9nXoIoh4WuGtWrWKtLQ0HA4HZrOZ3r17k5joXPp99uxZDhw4QHZ2NgcOHCA1NZUxY/z/aLruAhxZSOM5SSBBJhi74RradqfNk8so+fw3VB34nOKlv6D65G5i7/2t+5GVOxZ7DaVfvEblzn8BzhVaceNf9yo2EX5WrVrFggULUBSF8ePHk5KSgsVS/+9GRUUFy5YtIz09nfnz5wP4NYnUPfIaZDl/U4RsAmmpG3caEohuuIrZQqtJf8KQcDNl696mKns5saNfvvJC1UFV9nIAYka9SPTQZ/0WkwgteXl5pKWloSgKM2bMYOjQoQ1eZ7FYSE1NJSkpiTlz5pCWlkbPnj3p2rWrX+Kqu/kYYMX5HVKFeCjkWplo2W8mWHvdVB34LGBtRHSRzslNc7ch7tVXdSkGM+ZuQ+pdK1qGyZMnX3wuKtIAABqXSURBVHOl26JFi3A4HIwbN+6qyaOuoUOHMnbsWOx2O4sXL/ZlqG5y5HXzhGQFEqwf5FoIdDdc69fOlSrmm0c572ktpTT9d6i1NuLGv4Yu6jrMN92N9esMrEe+JGrAFL/GI0JDcXEx+/fvx2w2k5KS4vG4SZMmkZGRQXZ2NiUlJT5fnSVHXjdPyFUgoj53N1x7Ldac1X69l1pdSfW320HREdFjBLbjmZybM5qq/Z9iPfQF5z4Yi+14JhE3jgRFR3XetkubD0WLlpOTg6qq9O7d+4o5j2uxWCz06tULVVU5dOiQT2OSI6+bLyQrEH8YOPYRTe67a9XCZo2/vBuuP9up23K3otZYMSb2pGzT+1Tu+hhUFVOX2wCoPrGTon89TtTAn2BMuImas4ex5W4l4mK1IlquoqIiAI+OC75c+/bt+eqrrzh//rxPY5Ijr5tPKhC0Sx7NvXfdbriKMcLdDddfbEe+BKDm7GEqd/4LRW8k9p5fE//Yx8Q/9jGx9/waRW+kcue/qDl7uN4YIbzl2ieiXGyN4wueHHktVUjjpAKpw5tqoLLKCkBUZESTxzY3cQW0G67qwHr0UndjQ8JNtJr4br29HZYhT2HqPpTiZc+726BYj64nTnWAIr+rtGTx8c4lsWfOnGny2Pz8/Hrv4Qty5LVvyL/qZtqwdQ8bt+3R5N51u+G6Nvb5azVWzel9OMrPg6LDcseTtHl6RYMbA40JN9Pm6RXOJKbocJSfp+b0Pr/EJEJHcnIyiqJw8OBBKioqPB5XXl7OwYMHURSF5ORkn8TSlCOvpQq5NqlAmmnNxm0oisLYu4b47D2DsRuu9esv0ce1p9UDb2NKGnzNaxWDidjRM4lIHk3x8l9hPbIeY8f+Tfy/IMJJq1at6Nu3L9nZ2SxbtozU1FSPxi1dupTq6mr69+/vsxVYcuS170gCaYbi0jJ27Tvkft0qNsZ37x1k3XB1kXG0/ekqlAjPv0dTp1to+8xnVO75d5PuJcLTlClTOHDgAOnp6SQlJTW6FyQzM5PVq1ej1+uZOtU3i0O8OfJ6ZeFuPivcxROJd3l0ymlLIgmkGdZl7aK21tk/58vNu5g4tnlnkbgEYzdcy5CnvPpelIgYr8eK8JKUlERqairz589nzpw55ObmMmnSpCuW9ZaXl7N06VJWr16NqqqkpqbSpUsXn8QgR177liSQZli7abv79ZqN232WQEC64Yrw5OpplZaWRnp6OhkZGQ02U6yurkav1/PII49w7733+uTecuS170kC8dL354vYl3MUs8kEwL6co3x/vojr27T26X2kG64IN2PGjKFnz54sXryY7Oxs9uypvwhFURT69+/P1KlTfVZ5gBx57Q+SQLy0dtMOHKrK0EH9AFiXtZO1mTt4OMX3XUMD2Q1Xy7byouXo2rUrM2fOpKSkhEOHDrk3GrZu3Zrk5GSftyyRI6/9QxKIl9ZcfHw1esRgUC8mkI3b/ZJAwP/dcNu9+k1QHWglWoa4uDhuv/12v99Hjrz2D0kglznxXT6VVhtWq42amloAamprqbLa3NcUnC/i6+PfEm2J5I5bnXMO0ZZIDh//lo8/+YKEOo+xIiPMGA3O/81Go4GICDNREWa6dGx6SwfwvBuu9euMJnfDlQ9yIURTSAJpwOx353L82+8avW7EHQMwmYzu1yszsvjT3Gu3ne7etSNvvjzD69ikG64QIlhIArlMl47tmP/eK/zhgzQ+z8gCnJN6Qwb2IcLs/I0/JjoKgAmjR7jH/fi+uzEanM9Fy8qdG/6sNhtbdl0683n8D4fy0k9TiTCbvIqtoW64xSv+B0fZ9wBUn/qKVhPeIuLGkZTU6YarmKK8up8QQlyLJJAGRJhNzPrlk9zapydv/XUhVVYbp/PP8ebLM+jWpUODY5JvTCL5xiT3n0+ePsuv35iDqqqYTEZeeOZhHhgzollxSTdcIUQwkQRyDffdPYTkG5P49RtzyD1xmseen83LP3/MOXF+DRu37uHV9+ZSXlFF5w6JvPnyDHokdWp2PHW74dacPYxiMBFz1/NY7ngCgIqtH1K2/l33CizXGEkgIpCudSphoMiR14EhzRQbkdSpPfPfncXoEYOprLLy2z/8jbc+SKOmtvaKa2tqa3nrgzRefO0vlFdUMXrEYD76y6s+SR4NdcONf/oT5y5vRedscjjkKeKf/gRDwk3u66xH14PqaP79hWjEkiVLNL+3HHkdWFKBeCAqMoLXXppO966d+OuC/5K+bjO/fPLKyWnVoZK+bjMAP3v0xzw6eZzPYqjXDff2x4m5+1cohivnUlzdcMu+/CMV2+a5u+FKM0MRCFomEZeW+EGuFalAmiA22rkZb1D/Xu7VV3WZTEYG9e9V71pfcXXDjX/kI2JHz2wwebi4uuHGP/Ef9K07Yz3iWcsGIYRoCkkgTZC5Yy8AwwY7f5svq6jkf9/+O//z+vsUl5YBuHemZ+3c69N7u7rhNtZKvS5XN1xdRKxPYxFCCJBHWB6rstrYve8wuotLerftOcDs9/7J+aJiAPYfPs6sXz7Jnbf1Raco7Mo+TJXVRmTElZv9vCHdcIUQwcbjBKLVueHeHDPrDzuzc7BVV9OjW2fmLvqUZenrUVWV/r2cE9Z7Dx7huVl/ZOJ9d3FDUieO5Z5kZ3YOwwffonHkQgjhHx4lEK2Sh+vewZBEsnZkA3As9yTHck9iMhp4dtpEfjLR2V/n42Wr+ftHy1i68st6YySBCCHCVZMeYQX6g1zLxFWXQ1XdCQSc7Uhmv/hsveW50yaNZfCtvZn19t/dbVCydmTjUFV0F4+W9YR0wxVChAqZRPdAzpFciopL0CkKD6eMYeGfG97b0SOpEwv//CoPp4xBpygUFZeQcyTXo3to2chQmigKIbwhk+geyNz+FYlt43nlV08xoE/Pa15rMhp47smHGDnkVl555x9k7dhL75s9qyrkg1wIEUokgXggNtrC4g9eJ9ri+TnifXr24KO/zOaT1Rv8GJl/yLkgQghP+P0R1umz5zh99py/b+NX0yaNbVLycIm2RDJt0lg/ROQ/Ws7ByPyPEKHF7xXIvH9/BsD//uIJf99K+FCgqwFJHkKEHr9WIKfPnmPV+i2sWr8l5KsQIYQQ9fm1Apn378+orbW7Xwd7FRIsy4aFECIU+K0CcVUfBoMeg0Ef1FWIlhsVg2GTpBBCeMNvFYir+vjRPcMA+GxtZlBXIfJBLoQQTeOXBOKqPnQ6HY9OHodOp2PV+i2sXLeZRyePo1P7BH/cVmjEUX4OW94OHGUFoCjooq/HnDQYXXQbrUMTQviRXxJI3erDlSzG3jWEz9ZmsmDJyqCtQkTT1OTnUJbxNrbcLVeeeqjoMN9wJzGjXsTYLlmbAIUQfuXzOZDLqw+Xxx/6EQaDnpXrNnPqTIGvbysCrGL7As7/4wFs32ShGMxE3DQKyx1PYLnjCSJuGoViMGM7nsn5f0ygYrs8HhQiHPm8Ammo+gDokNhWqpAwUbF9AaWr/w8UBcsdTxI9/GdXHFrlsJZSvmkOFdvmUbp6NgCWwbLKTYhw4tMK5GrVh4tUIaGvJj+H0jVvgKLQKuWPxI6e2eCJh7qIWGJHv0yrB94BRaF0zevUnD2kQcRCCH/xaQJxVR/jRt3Z4ES5qwpxOBwsWLLSl7cWAVK27h1w2LHc/gSRfe5v9PrIvhOwDH4MHHbnWCFE2PBZAmms+nCRKiR0OcrPYftmM4oxkujhP/N4XPTwGSjGCGzHs3CUn/djhEKIQPJZAmms+nCRKiR02fJ2gOrA3G1Ig4+trkYXGYcp6XZQHVR/u8OPEQohAsknCcTT6sNFqpDQ5CjNB0DfJqnJYw1tugFgv/geQojQ55ME4mn14SJVSIhyHc2rqk0f6x7j+fG+Qojg1uxlvK7qA8BoMLDwv+kejTManLdetX4Ljz/0Izoktm1uKMLPdLHtALAX5jV5bO3FMfrYRJ/GJITQTrMTSN2Ou8tWrW/y+Npae1D3yBKXmLveBooOW+5WHNZSj+dBHFXFVOdtA0WHKWmwn6MUQgRKsxJIba2dtq1b8ciP72teEHo9tbV2DAZ9s95H+Jcuui3mG+7EdjyT8k1ziB39skfjyje+j1pjxdxjBDpLvJ+jFEIESrMSiMGg59nUib6KRYSAmFEvYsvdQsW2eRgTk4nsO+Ga11ft+4SKHQtBpydm1AsBilIIEQh+PxNdhBdju2RiR/8GVJXiT16g9IvXcVSVXHGdo6qY0tX/R/EnL4KqEnvvbzEm9tQgYiGEv/j9THQRfiyDH3G2J/niNSq2zaNy9yJMSXdgiO8KQG3ht1TnbUWtsYJOT+yY32IZlKpt0EIIn5MEIrxiGZSKqcsAyta9g+14Fraj67HVvUDRYe4xgphRL0jlIUSYkgQivGZMTKb1w/NwVBRSnbcde5lzU6g+JgFT0mCZMA9CkydPvuJrS5YsueZ/94W69xDho0kJZOBYacctrqSzxBPRq3kr8YT/+Ss5eHpvSSLhx6MEsmvVQs2Sh5xVLoRvXeuD/Gr/raqqCoDIyMgm30/LxCX8y+MKRD7IhWi5du7ciaIoDBs2TOtQRBCROZAm0uq3KSn/hZa2bNkiCURcQfaBNIHWz5CF0EJZWRkHDhxg//79lJWVaR2OCCJSgXgh0NWAFskj/5UbAn5PEZy2bduG3e7sd7d9+3Z++MMfahyRCBZSgYh62r36TYu8t7i6LVu2uF9v3rxZw0hEsJEKRFxBPsiFS2FhIV9//TUmkwmAr7/+msLCQuLjZY+PkApECHENW7duRVVVbr31Vm699VZUVWXr1q1ahyWChCSQACkoKKCgQI7vFaHF9cjqzjvvZMiQIUD9R1qiZZNHWAGyfPlyAKZPn65xJELAmTNnsFqt2Gw2amtrAaitrcVqtbqvKSwsJC8vj6ioKPr16wdAVFQUubm5rFy5st5jrIiICAwXTxk1GAyYzWYiIiJo3759AL8rEWiSQAKgoKCAzMxMAFJSUkhIaPzceCH87YMPPuDkyZONXnfbbbdhNBrdrzdu3EhaWto1x3Tu3Jnnn3/eJ3GK4CUJJACWL1/uXga5fPlyqUKE5tq3b8/rr7/OvHnz2LBhAwCKotC/f3/MZjMAFosFgLvvvts9bvTo0e5Ko6KiAgCbzcbevXtRVRWAkSNH8vjjj7vfR1wpXDYkSwLxM1f1odc7j+vNzMyUKkQEBbPZzPTp00lOTuaf//wnNpuNgoICnn/+eTp16tTgmBtuuIEbbri0Ryg/P593330XVVUxGo089thjjBo1KlDfQkjSekOyL5OIJBA/c1UfI0eOBGDDhg1ShYigMnz4cLp37867777LqVOn+M1vfsMzzzzjnjS/mp07d/LBBx9QWVlJu3bteP755+nSpUuAog594bAhWVZh+ZGr+tDpdEyYMIGUlBT0ej2bNm0iPz9f6/CEcOvQoQOvvfYaQ4YMwWq18uc//5kPP/zQPcFeV21tLR9++CHvvPMOlZWVDBkyhDfffFOSRwskFUgTNPU3hrrVR7t27QAYNmwYGzZsYMWKFVKFtBBN/c3PVwc8NfXva2RkJM899xxdunRh0aJFbNy4kdTUK48iVlWVjRs3AjB16lQmTJjgdYwitEkF4ieXVx8uUoW0LFo/7/aGa/K8T58+7tVXdRmNRvr06VPvWtEySQXiJw1VHwAJCQlShbRA3j7v9nZccxLX7t27ARgwYADgXG01b948qqurefrpp4mJiWHAgAHs2rWLPXv2SHPFFkwSSBO4/lE29o/6atWHS0pKCpmZmWzatIkJEybUSzBCaMlms5GTk4OiKNxyyy1kZ2fzt7/9jQsXLgBw9OhRpk+fzi233IKiKBw8eBCbzSZLdv2suLiYnJwcLly4gKIotGrVil69ehEXF6dpXJJA/OBq1YeLVCEiWO3fv5/q6mq6dOnC0qVLWbt2Laqq0rNnTwAOHz7M73//e+655x46d+7MiRMn2L9/PwMHDtQ48vCUl5fHokWL2L9/v3ufjYuiKPTt25cpU6aQlJSkSXySQHysserDRaqQwJIDuTyzZ88eAE6cOMGJEycwGo08+OCDjB8/HoDPP/+c//znP6xZs6beGEkgvrdq1SrS0tJwOByYzWZ69+5NYmIiAGfPnuXAgQNkZ2dz4MABUlNTGTNmTMBjlATiY41VHy5ShQROqCYPV/PNQG06VVXVnUDA2Y7k5z//eb3luT/60Y/o27cv77//vrsNyp49e1BVFUVRAhJnS7Bq1SoWLFiAoiiMHz+elJSUKxYsVFRUsGzZMtLT05k/fz5AwJOIJBAf8rT6cJEqJLBCbeNWoBtwHj9+nJKSEhRFYdy4cTz00EMNrsLq0qULv//97/n3v//NypUrKSkp4fjx4/To0SMgcfrCwLGPaHLfXasWNnpNXl4eaWlpKIrCjBkzGDp0aIPXWSwWUlNTSUpKYs6cOaSlpdGzZ0+6du3a4PX++Psvy3h9yFV9DB8+3KNk4KpCHA4HK1asCECEIlS4fhnJzMwM2DEAu3fvpk2bNsyaNYtp06Y1mDxcjEYj06ZNY/bs2SQkJLhXboUCrZKHp/detGgRDoeDcePGXTV51DV06FDGjh2L3W5n8eLFvgjTY1KB+EjdjrsGg4FPP/3Uo3GuxnTSI0vUpUUDTovFwjvvvENUVJTHY2666Sbeeust1q1b58fI/MOTauBylVXOdvdRkRFNHutJ8iguLmb//v2YzWZSUlI8fu9JkyaRkZFBdnY2JSUlAVudJQnER+r+g8/IyGjyeLvdLj2yBKBdA84f/ehHXo2Lioryemyo2bB1D4oCY++6dp8wb+Xk5KCqKr17927SJk2LxUKvXr346quvOHToELfffvsV13i6DaEpJIH4gN1up3Xr1tx///3Neh+DwYDdbnd/cAjtBXoiG6QBZzBbs3EbiqL4LYEUFRUBeDUf2r59e7766ivOnz/v67CuShKID+j1eh588EGtwxB+EOiJ7MsXYuh0OlloESSKS8vYte+Q+3Wr2BiNI6rPtU8kkKvhJIEIcRVanCQZiAacobqsWWvrsnZRW+t8TP3l5l1MHHuXz+/hOib4zJkzTR7r6q1X96hhf5NVWEJchevD3DU/5W/+bsAZ6GXMwXJvX1m7abv79ZqN269xpfeSk5PdLWJcJz56ory8nIMHD6IoCsnJyX6JrSFSgQjRAC0msgPRgDMcPsi18P35IvblHMVsMgGwL+co358v4vo2rX16n1atWtG3b1+ys7NZtmxZg+30G7J06VKqq6vp379/QPtjSQUiRANcH+bDhg1j2LBhfq9CPGnAKccAaGftph04VJWhg/oxdFA/HKrK2swdfrnXlClT0Ov1pKenk5WV1ej1mZmZrF69Gr1ez9SpU/0S09VIBeIFeYYc3rSYyJYGnMFtzcXHV6NHDAYV1mXtZO3G7Tyc4vvWIUlJSaSmpjJ//nzmzJlDbm4ukyZNumJZb3l5OUuXLmX16tWoqkpqamrAT4WUBNIES5Ys0Sx5yKOHwAn0SZLSgFM7J77Lp9Jqw2q1UVPjPL63praWKqvNfU3B+SK+Pv4t0ZZI7rjVeZBWtCWSw8e/5eNPviChzmOsyAgzxoubg41GAxERZqIizHTp2LSflaunVVpaGunp6WRkZDTYTLG6uhq9Xs8jjzzCvffe6/3/CC9JAmki+SAPb9eayPbXh7c04NTW7Hfncvzb7xq9bsQdAzCZjO7XKzOy+NPca7cO6d61I2++PMOruMaMGUPPnj1ZvHgx2dnZ9RpdgnO5bv/+/Zk6dapm59FLAhGijkCfJCkNOLXVpWM75r/3Cn/4II3PM5zzDYqiMGRgHyIuHpIVE+1s7TJh9Aj3uB/fdzdGg3OBRVl5JQBWm40tuy6d2zH+h0N56aepRJhNXsfXtWtXZs6cSUlJCYcOHXJvNGzdujXJyclyoJQQwUKLkyQ9rT5cpArxvQiziVm/fJJb+/Tkrb8upMpq43T+Od58eQbdunRocEzyjUkk33jpEKeTp8/y6zfmoKoqJpORF555mAfGjPBZjHFxcQ22J9GaJBAhLgr0RLY04Awu9909hOQbk/j1G3PIPXGax56fzcs/f8w5cX4NG7fu4dX35lJeUUXnDom8+fIMeiR1ClDU2pIEIgTaTGRLA87gk9SpPfPfncUb789nzcbt/PYPfyP70FGef3qqe3Lcpaa2lnf/sYilK78EnCu0Xv75Y1516g1VkkCEIPAT2dKAM3hFRUbw2kvT6d61E39d8F/S123ml09OueI61aGSvm4zAD979Mc8OnlcoEPVnCQQ0eJpMZEtDTiDX2y0c9/FoP693Kuv6jKZjAzq34uN2/a4r21pJIGIFk8mskVDMnfsBWDY4P4AlFVU8ocP0qiurmHmzx+lVWwMQwf1Y+O2PWTt3EvK2JFNev9w2JAsCUS0aDKRLRpSZbWxe99hdBeX9G7bc4DZ7/2T80XFAOw/fJxZv3ySO2/ri05R2JV9mCqrjcgIc6PvHU4bkiWBiBZNJrJFQ3Zm52CrrqZHt87MXfQpy9LXo6oq/XvdBMDeg0d4btYfmXjfXdyQ1IljuSfZmZ3D8MG3ePT+4bIhWRKIaLFkIltcTdaObACO5Z7kWO5JTEYDz06byE8mOluMfLxsNX//aJl7BZZrjKcJJFxIAhEtViAnssPheXdL4VBVdwIBZzuS2S8+W29vx7RJYxl8a29mvf13dxuUrB3ZOFQVXQBPBNSatHMXIkyFy2OSQMs5kktRcQk6ReHhlDEs/POrDW4M7JHUiYV/fpWHU8agUxSKikvIOZKrQcTakQpECD+TD/LQkrn9KxLbxvPKr55iQJ+e17zWZDTw3JMPMXLIrbzyzj/I2rGX3jffEKBItScViBBC1BEbbWHxB683mjzq6tOzBx/9ZTYxlig/RhZ8pAIRQog6pk0a69W4aEuk12NDlSQQ0WJcbSK77iMmmewWwnPyCEuEPS3nIGT+Q4QzRXWdfiKEEC3AwLGPaHr/XasWanp/X5IKRAjRomj5AR5OyQOkAhFCCOElqUCEEEJ4RRKIEEIIr0gCEUII4RVJIEIIIbwiCUQIIYRXJIEIIYTwyv8HQGNGvyBJA50AAAAASUVORK5CYII=</v>
+      </c>
+      <c r="E427" t="str">
+        <v>24-08-2026 02:18:02 pm</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="str">
+        <v>6a8c05752969f40a94886f78</v>
+      </c>
+      <c r="B428" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C428" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D428" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E428" t="str">
+        <v>24-08-2026 02:18:53 pm</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="str">
+        <v>6a8c05762969f40a94886f7f</v>
+      </c>
+      <c r="B429" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C429" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D429" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E429" t="str">
+        <v>24-08-2026 02:18:54 pm</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="str">
+        <v>6a8c05912969f40a94887069</v>
+      </c>
+      <c r="B430" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C430" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D430" t="str">
+        <v>Started Playing game and Debited "10" and Balance "540"</v>
+      </c>
+      <c r="E430" t="str">
+        <v>24-08-2026 02:19:21 pm</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="str">
+        <v>6a8c05912969f40a9488706f</v>
+      </c>
+      <c r="B431" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C431" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D431" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E431" t="str">
+        <v>24-08-2026 02:19:21 pm</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="str">
+        <v>6a8c05d0a4ac9b7880f2f056</v>
+      </c>
+      <c r="B432" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C432" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D432" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E432" t="str">
+        <v>24-08-2026 02:20:24 pm</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="str">
+        <v>6a8c05d1a4ac9b7880f2f05f</v>
+      </c>
+      <c r="B433" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C433" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D433" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E433" t="str">
+        <v>24-08-2026 02:20:25 pm</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="str">
+        <v>6a8c05dba4ac9b7880f2f149</v>
+      </c>
+      <c r="B434" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C434" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D434" t="str">
+        <v>Started Playing game and Debited "10" and Balance "530"</v>
+      </c>
+      <c r="E434" t="str">
+        <v>24-08-2026 02:20:35 pm</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="str">
+        <v>6a8c05dba4ac9b7880f2f14f</v>
+      </c>
+      <c r="B435" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C435" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D435" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E435" t="str">
+        <v>24-08-2026 02:20:35 pm</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="str">
+        <v>6a8c05e6a4ac9b7880f2f179</v>
+      </c>
+      <c r="B436" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C436" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D436" t="str">
+        <v>Answerd Correctly to Qst ID : 6a8c05dda4ac9b7880f2f159, Reward : 10, Qst No : 2 ,Question : What is the alphabetical arrangement of these random letters: "agn"?</v>
+      </c>
+      <c r="E436" t="str">
+        <v>24-08-2026 02:20:46 pm</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="str">
+        <v>6a8c05e9a4ac9b7880f2f190</v>
+      </c>
+      <c r="B437" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C437" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D437" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6a8c05e8a4ac9b7880f2f188 , Question : How many words are scrambled?, Type : scramble_words </v>
+      </c>
+      <c r="E437" t="str">
+        <v>24-08-2026 02:20:49 pm</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="str">
+        <v>6a8c05f3a4ac9b7880f2f1a5</v>
+      </c>
+      <c r="B438" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C438" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D438" t="str">
+        <v>Answerd Correctly to Qst ID : 6a8c05e8a4ac9b7880f2f188, Reward : 40, Qst No : 3 ,Question : How many words are scrambled?</v>
+      </c>
+      <c r="E438" t="str">
+        <v>24-08-2026 02:20:59 pm</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="str">
+        <v>6a8c05f6a4ac9b7880f2f1bc</v>
+      </c>
+      <c r="B439" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C439" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D439" t="str">
+        <v xml:space="preserve">Created Question Number : 2, Rupees : 30, Qst ID : 6a8c05f6a4ac9b7880f2f1b4 , Question : How many letters are misaligned?, Type : letters_missalign </v>
+      </c>
+      <c r="E439" t="str">
+        <v>24-08-2026 02:21:02 pm</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="str">
+        <v>6a8c060ba4ac9b7880f2f1d0</v>
+      </c>
+      <c r="B440" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C440" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D440" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E440" t="str">
+        <v>24-08-2026 02:21:23 pm</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="str">
+        <v>6a8c060ca4ac9b7880f2f1d7</v>
+      </c>
+      <c r="B441" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C441" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D441" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E441" t="str">
+        <v>24-08-2026 02:21:24 pm</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="str">
+        <v>6a8c062fa4ac9b7880f2f2c3</v>
+      </c>
+      <c r="B442" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C442" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D442" t="str">
+        <v>Started Playing game and Debited "10" and Balance "520"</v>
+      </c>
+      <c r="E442" t="str">
+        <v>24-08-2026 02:21:59 pm</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="str">
+        <v>6a8c062fa4ac9b7880f2f2c9</v>
+      </c>
+      <c r="B443" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C443" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D443" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E443" t="str">
+        <v>24-08-2026 02:21:59 pm</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="str">
+        <v>6a8c0646a4ac9b7880f2f2f3</v>
+      </c>
+      <c r="B444" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C444" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D444" t="str">
+        <v>Answerd Correctly to Qst ID : 6a8c0630a4ac9b7880f2f2d3, Reward : 10, Qst No : 2 ,Question : How many times do the letters R, F, J, V, M appear in the paragraph?</v>
+      </c>
+      <c r="E444" t="str">
+        <v>24-08-2026 02:22:22 pm</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="str">
+        <v>6a8c0a3bf8bcde8f653c9b1d</v>
+      </c>
+      <c r="B445" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C445" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D445" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E445" t="str">
+        <v>24-08-2026 02:39:15 pm</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="str">
+        <v>6a8c0a3bf8bcde8f653c9b28</v>
+      </c>
+      <c r="B446" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C446" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D446" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E446" t="str">
+        <v>24-08-2026 02:39:15 pm</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="str">
+        <v>6a8c0a43f8bcde8f653c9c15</v>
+      </c>
+      <c r="B447" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C447" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D447" t="str">
+        <v>Started Playing game and Debited "10" and Balance "510"</v>
+      </c>
+      <c r="E447" t="str">
+        <v>24-08-2026 02:39:23 pm</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="str">
+        <v>6a8c0a43f8bcde8f653c9c1b</v>
+      </c>
+      <c r="B448" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C448" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D448" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E448" t="str">
+        <v>24-08-2026 02:39:23 pm</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="str">
+        <v>6a8c0a50f8bcde8f653c9c45</v>
+      </c>
+      <c r="B449" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C449" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D449" t="str">
+        <v>Answerd Correctly to Qst ID : 6a8c0a45f8bcde8f653c9c25, Reward : 10, Qst No : 2 ,Question : How many words are scrambled?</v>
+      </c>
+      <c r="E449" t="str">
+        <v>24-08-2026 02:39:36 pm</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="str">
+        <v>6a8c0a53f8bcde8f653c9c5c</v>
+      </c>
+      <c r="B450" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C450" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D450" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6a8c0a53f8bcde8f653c9c54 , Question : How many letters are misaligned?, Type : letters_missalign </v>
+      </c>
+      <c r="E450" t="str">
+        <v>24-08-2026 02:39:39 pm</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="str">
+        <v>6a8c0a66f8bcde8f653c9c71</v>
+      </c>
+      <c r="B451" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C451" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D451" t="str">
+        <v>Answerd Correctly to Qst ID : 6a8c0a53f8bcde8f653c9c54, Reward : 40, Qst No : 3 ,Question : How many letters are misaligned?</v>
+      </c>
+      <c r="E451" t="str">
+        <v>24-08-2026 02:39:58 pm</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="str">
+        <v>6a8c0a6df8bcde8f653c9c88</v>
+      </c>
+      <c r="B452" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C452" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D452" t="str">
+        <v xml:space="preserve">Created Question Number : 2, Rupees : 30, Qst ID : 6a8c0a6cf8bcde8f653c9c80 , Question : Decode "R" using cipher key, Type : encode_decode </v>
+      </c>
+      <c r="E452" t="str">
+        <v>24-08-2026 02:40:05 pm</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="str">
+        <v>6a8c0a75f8bcde8f653c9c9d</v>
+      </c>
+      <c r="B453" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C453" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D453" t="str">
+        <v>Answerd Correctly to Qst ID : 6a8c0a6cf8bcde8f653c9c80, Reward : 30, Qst No : 4 ,Question : Decode "R" using cipher key</v>
+      </c>
+      <c r="E453" t="str">
+        <v>24-08-2026 02:40:13 pm</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="str">
+        <v>6a8c0a78f8bcde8f653c9cb4</v>
+      </c>
+      <c r="B454" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C454" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D454" t="str">
+        <v xml:space="preserve">Created Question Number : 3, Rupees : 40, Qst ID : 6a8c0a78f8bcde8f653c9cac , Question : How many colour names match their text colour out of 8?, Type : [Colours &amp; Name Match] </v>
+      </c>
+      <c r="E454" t="str">
+        <v>24-08-2026 02:40:16 pm</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="str">
+        <v>6a8c0a85f8bcde8f653c9cc9</v>
+      </c>
+      <c r="B455" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C455" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D455" t="str">
+        <v>Answerd Correctly to Qst ID : 6a8c0a78f8bcde8f653c9cac, Reward : 40, Qst No : 5 ,Question : How many colour names match their text colour out of 8?</v>
+      </c>
+      <c r="E455" t="str">
+        <v>24-08-2026 02:40:29 pm</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="str">
+        <v>6a8c0a95f8bcde8f653c9ce0</v>
+      </c>
+      <c r="B456" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C456" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D456" t="str">
+        <v xml:space="preserve">Created Question Number : 4, Rupees : 50, Qst ID : 6a8c0a95f8bcde8f653c9cd8 , Question : What is the alphabetical arrangement of these random letters: "exa"?, Type : re_arrange_letters </v>
+      </c>
+      <c r="E456" t="str">
+        <v>24-08-2026 02:40:45 pm</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="str">
+        <v>6a8c0a9ef8bcde8f653c9cf5</v>
+      </c>
+      <c r="B457" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C457" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D457" t="str">
+        <v>Answerd Correctly to Qst ID : 6a8c0a95f8bcde8f653c9cd8, Reward : 50, Qst No : 6 ,Question : What is the alphabetical arrangement of these random letters: "exa"?</v>
+      </c>
+      <c r="E457" t="str">
+        <v>24-08-2026 02:40:54 pm</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="str">
+        <v>6a8c0b39f8bcde8f653c9d10</v>
+      </c>
+      <c r="B458" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C458" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D458" t="str">
+        <v xml:space="preserve">Created Question Number : 5, Rupees : 80, Qst ID : 6a8c0b38f8bcde8f653c9d08 , Question : How many boxes are unbroken in total?, Type : Total Boxes [Comp] </v>
+      </c>
+      <c r="E458" t="str">
+        <v>24-08-2026 02:43:29 pm</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="str">
+        <v>6a8c0b47f8bcde8f653c9d25</v>
+      </c>
+      <c r="B459" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C459" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D459" t="str">
+        <v>Answerd Correctly to Qst ID : 6a8c0b38f8bcde8f653c9d08, Reward : 80, Qst No : 7 ,Question : How many boxes are unbroken in total?</v>
+      </c>
+      <c r="E459" t="str">
+        <v>24-08-2026 02:43:43 pm</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="str">
+        <v>6a8c0b53f8bcde8f653c9d40</v>
+      </c>
+      <c r="B460" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C460" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D460" t="str">
+        <v xml:space="preserve">Created Question Number : 6, Rupees : 110, Qst ID : 6a8c0b52f8bcde8f653c9d38 , Question : How many broken boxes are there?, Type : Total Boxes [Broken] </v>
+      </c>
+      <c r="E460" t="str">
+        <v>24-08-2026 02:43:55 pm</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="str">
+        <v>6a8c0b61f8bcde8f653c9d55</v>
+      </c>
+      <c r="B461" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C461" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D461" t="str">
+        <v>Answerd Correctly to Qst ID : 6a8c0b52f8bcde8f653c9d38, Reward : 110, Qst No : 8 ,Question : How many broken boxes are there?</v>
+      </c>
+      <c r="E461" t="str">
+        <v>24-08-2026 02:44:09 pm</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="str">
+        <v>6a8c0b6ff8bcde8f653c9d70</v>
+      </c>
+      <c r="B462" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C462" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D462" t="str">
+        <v xml:space="preserve">Created Question Number : 7, Rupees : 140, Qst ID : 6a8c0b6ef8bcde8f653c9d68 , Question : How many times does the letter sequence 'fly' appear in the given words?, Type : count_word_exist </v>
+      </c>
+      <c r="E462" t="str">
+        <v>24-08-2026 02:44:23 pm</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="str">
+        <v>6a8c0b7ff8bcde8f653c9d85</v>
+      </c>
+      <c r="B463" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C463" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D463" t="str">
+        <v>Answerd Correctly to Qst ID : 6a8c0b6ef8bcde8f653c9d68, Reward : 140, Qst No : 9 ,Question : How many times does the letter sequence 'fly' appear in the given words?</v>
+      </c>
+      <c r="E463" t="str">
+        <v>24-08-2026 02:44:39 pm</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="str">
+        <v>6a8c0b86f8bcde8f653c9da0</v>
+      </c>
+      <c r="B464" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C464" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D464" t="str">
+        <v xml:space="preserve">Created Question Number : 8, Rupees : 170, Qst ID : 6a8c0b85f8bcde8f653c9d98 , Question : How many puzzle pieces contain 2 or more MALE connectors (outward tabs)?, Type : puzle_peace_male_female </v>
+      </c>
+      <c r="E464" t="str">
+        <v>24-08-2026 02:44:46 pm</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="str">
+        <v>6a8c0bb6f8bcde8f653c9dc7</v>
+      </c>
+      <c r="B465" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C465" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D465" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E465" t="str">
+        <v>24-08-2026 02:45:34 pm</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="str">
+        <v>6a8c0bb7f8bcde8f653c9dce</v>
+      </c>
+      <c r="B466" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C466" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D466" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E466" t="str">
+        <v>24-08-2026 02:45:35 pm</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="str">
+        <v>6a8c0bcdf8bcde8f653c9ebc</v>
+      </c>
+      <c r="B467" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C467" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D467" t="str">
+        <v>Started Playing game and Debited "10" and Balance "500"</v>
+      </c>
+      <c r="E467" t="str">
+        <v>24-08-2026 02:45:57 pm</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="str">
+        <v>6a8c0bcef8bcde8f653c9ec2</v>
+      </c>
+      <c r="B468" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C468" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D468" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E468" t="str">
+        <v>24-08-2026 02:45:58 pm</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="str">
+        <v>6a8c0c09f8bcde8f653c9eec</v>
+      </c>
+      <c r="B469" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C469" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D469" t="str">
+        <v>Answerd Correctly to Qst ID : 6a8c0bcff8bcde8f653c9ecc, Reward : 10, Qst No : 2 ,Question : Decode "P" using cipher key</v>
+      </c>
+      <c r="E469" t="str">
+        <v>24-08-2026 02:46:57 pm</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="str">
+        <v>6a8c0c0cf8bcde8f653c9f03</v>
+      </c>
+      <c r="B470" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C470" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D470" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6a8c0c0bf8bcde8f653c9efb , Question : How many words are scrambled?, Type : scramble_words </v>
+      </c>
+      <c r="E470" t="str">
+        <v>24-08-2026 02:47:00 pm</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="str">
+        <v>6a8c0c17f8bcde8f653c9f18</v>
+      </c>
+      <c r="B471" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C471" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D471" t="str">
+        <v>Answerd Correctly to Qst ID : 6a8c0c0bf8bcde8f653c9efb, Reward : 40, Qst No : 3 ,Question : How many words are scrambled?</v>
+      </c>
+      <c r="E471" t="str">
+        <v>24-08-2026 02:47:11 pm</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="str">
+        <v>6a8c0c1af8bcde8f653c9f2f</v>
+      </c>
+      <c r="B472" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C472" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D472" t="str">
+        <v xml:space="preserve">Created Question Number : 2, Rupees : 30, Qst ID : 6a8c0c1af8bcde8f653c9f27 , Question : How many times does the letter sequence 'avi' appear in the given words?, Type : count_word_exist </v>
+      </c>
+      <c r="E472" t="str">
+        <v>24-08-2026 02:47:14 pm</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="str">
+        <v>6a8c0c2cf8bcde8f653c9f44</v>
+      </c>
+      <c r="B473" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C473" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D473" t="str">
+        <v>Answerd Correctly to Qst ID : 6a8c0c1af8bcde8f653c9f27, Reward : 30, Qst No : 4 ,Question : How many times does the letter sequence 'avi' appear in the given words?</v>
+      </c>
+      <c r="E473" t="str">
+        <v>24-08-2026 02:47:32 pm</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="str">
+        <v>6a8c0c30f8bcde8f653c9f5b</v>
+      </c>
+      <c r="B474" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C474" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D474" t="str">
+        <v xml:space="preserve">Created Question Number : 3, Rupees : 40, Qst ID : 6a8c0c2ff8bcde8f653c9f53 , Question : How many boxes are unbroken in total?, Type : Total Boxes [Comp] </v>
+      </c>
+      <c r="E474" t="str">
+        <v>24-08-2026 02:47:36 pm</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="str">
+        <v>6a8c0c42f8bcde8f653c9f70</v>
+      </c>
+      <c r="B475" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C475" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D475" t="str">
+        <v>Answerd Correctly to Qst ID : 6a8c0c2ff8bcde8f653c9f53, Reward : 40, Qst No : 5 ,Question : How many boxes are unbroken in total?</v>
+      </c>
+      <c r="E475" t="str">
+        <v>24-08-2026 02:47:54 pm</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="str">
+        <v>6a8c0c45f8bcde8f653c9f87</v>
+      </c>
+      <c r="B476" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C476" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D476" t="str">
+        <v xml:space="preserve">Created Question Number : 4, Rupees : 50, Qst ID : 6a8c0c44f8bcde8f653c9f7f , Question : How many words are colored with the WRONG color?, Type : word_colour_find </v>
+      </c>
+      <c r="E476" t="str">
+        <v>24-08-2026 02:47:57 pm</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="str">
+        <v>6a8c0c4ff8bcde8f653c9f9c</v>
+      </c>
+      <c r="B477" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C477" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D477" t="str">
+        <v>Answerd Correctly to Qst ID : 6a8c0c44f8bcde8f653c9f7f, Reward : 50, Qst No : 6 ,Question : How many words are colored with the WRONG color?</v>
+      </c>
+      <c r="E477" t="str">
+        <v>24-08-2026 02:48:07 pm</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="str">
+        <v>6a8c0c56f8bcde8f653c9fb7</v>
+      </c>
+      <c r="B478" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C478" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D478" t="str">
+        <v xml:space="preserve">Created Question Number : 5, Rupees : 80, Qst ID : 6a8c0c55f8bcde8f653c9faf , Question : How many broken boxes are there?, Type : Total Boxes [Broken] </v>
+      </c>
+      <c r="E478" t="str">
+        <v>24-08-2026 02:48:14 pm</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="str">
+        <v>6a8c0c65f8bcde8f653c9fc9</v>
+      </c>
+      <c r="B479" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C479" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D479" t="str">
+        <v>Answered incorrectly for Qst ID: 6a8c0c55f8bcde8f653c9faf, Qst: How many broken boxes are there?, Submitted Answer: 22, image : iVBORw0KGgoAAAANSUhEUgAAAZAAAAD6CAYAAACPpxFEAAAABmJLR0QA/wD/AP+gvaeTAAAgAElEQVR4nO3de1RU55rg/++mqiguMXrUtAGPIK1pG7zgBT2dH17ajtFchHg4tkY64okzyzSTZDnDmpn1s/1N5qysJOgs2zUubZ3JRI1Mt0YHGZMIjpoJSEQ9XCIBUY5NS4hHCCdB5ShKkSr27w+yK6AIRVFVe++q5/MXLvdb+92G7Kee/T7vsxVVVVWEEEKIIQrTewJCCCHMSQKIEEIIr0gAEUII4RUJIEIIIbxi1XsCQgjR26pVq/zyuUeOHBnwHL3/XnhGAogwPX/dcAYjNxzf0+u/pXZu+W86NBJAhKmFwg0nFAOkv8/94Ofr+XtkZhJARFAI9M0uUDecUAiQwrwkgAhhAsEaIIW5SRWWEEIIr0gAEUII4RV5hCU85uvHGoOVVfZ3nC+1trYCMG7cOL98vgiM27dvU1dXx61bt1AUhVGjRjFt2jRGjhyp99SCngQQ4RGjLuYOJ7gUFBQAkJ2d7fVnGFmwB8jGxkYOHjxITU0ND/aEVRSF5ORk1qxZQ0JCgk4zDH4SQMSQ+CsbeNTn+itwtba2UlpaCkBGRkZQ3mSDOUAWFRWRl5dHd3c3drud6dOn8+STTwLw7bffUltbS3V1NbW1tWRlZfH888/rPOPgJAFEhKSCggJcLpf752C7yQZzgCwqKuLDDz9EURTS0tLIyMggOjq6zzEdHR0cPXqUwsJC9u/fDyBBxA9kEV2Y2qpVq4acpWg3V4vFgsViobS01P24J1hoAdLlcrkzkWDQ2NhIXl4eiqLwxhtvsHbt2oeCB0B0dDRZWVm88cYbKIpCXl4eX3/9deAnHOQkgIiQo91cFy5cyMKFC4PuJhvMAfLgwYN0d3ezfPlyFixYMOjxCxYs4IUXXsDlcnHo0KEAzDC0SAARIUW7uYaFhbFixQoyMjKwWCycOXOGlpYWvafnE8EaIG/fvk1NTQ12u52MjAyPx61cuZLw8HCqq6tpb2/34wxDjwQQ4Te3b9+mrKyM48ePU1hYSFlZme7/A2s310WLFhETE8O4ceNYuHAh3d3dHDt2TNe5+UIwB8i6ujpUVWX69On9PrZ6lOjoaKZNm4aqqly+fNmPMww9sogufM6o5ZUP3lw1GRkZlJaWcubMGVasWEFMTExA5+VLWoBcvHix+zoWLlxIcXExx44dM3WxwM2bNwG8+u8TGxvLl19+yffff+/raYU0yUCETxUVFbFp0ya++uorwsPDSUlJYfny5SxfvpyUlBT3o4S/+7u/48SJEwGd24PZhyZYspCBAmSwZCHe0r7IKIqi80yCi2QgwmeMXF75qJurJhiykP6yD/gpQJo9CxkzZgwAzc3NQx6rBU7tM4RvSAYifMLo5ZWPyj40Zs9CPAmQZs9CkpKSUBSFS5cu0dHR4fG4u3fvcunSJRRFISkpyY8zDD0SQIRPGLm8crCbq8bMN9lgD5AAo0aNIjk5GYfDwdGjRz0el5+fT1dXFzNnzpT+WD4mAUQMm9HLKwe7uWrMepP1R4A8cuSIIV8mtWbNGiwWC4WFhXzxxReDHl9aWsqJEyewWCxkZmYGYIahJeBrIHNfWBfoUwJQUXQACM3Xg/rbcMsrv/zySy5fvszTTz/t87l5enPVmHEt5FFrHw8KhrWQhIQEsrKy2L9/P7t27eLatWusXLnyod+7u3fvkp+fz4kTJ1BVlaysLOLj43WadfAKaADRK3ho50547L5u5w/m14MaubzS05urxmw32VAIkA/Sii7y8vIoLCzk9OnT/TZT7OrqwmKxsG7dOp577jk9pxy0dKnC0rKBQHkwcMnrQY3Dn+WVvRsKWq1WPv74Y4/GWa09/1uUlpYavhGhvwKk9jtr1C89zz//PImJiRw6dIjq6mqqqqr6/L2iKMyaNYvMzEzJPPxIynjFsBm1vLJ3x93Tp08PebzWAsSoWUgoBMiBTJw4kU2bNtHe3s7ly5fdmfDo0aNJSkqSBfMAkAAihu3B8kpP10H8WV7pcrkYPXo0L7300rA+x2q14nK5sFgsPpqZ7wR7gPTUyJEj/bJ+JgYnAUQMm1ZeWV1dzdGjR8nKyvJonFZeOWvWLJ9/W7RYLKxevdqnn2kkoRAghfGZJoDc+PY7AMY/+YTXnzGc57nB/nrQ4VqzZg21tbUUFhaSkJAw6F4QKa8cnmAPkMIcTLMPZN9Hn7Dvo090O39BQUFQtMT2F628UlVVdu3axYEDB/rdLXz37l0+/PBD/uEf/kHKK4UwOVNkIDe+/Y6iz8sAWP9y+rCyEG8E8+tBfUnKK4UILaYIIPs++gSn0+X++T/923/l1ed4W5oY7O/P9iUprxS+IKXv5mD4AKJlH1ZrzyJf0edlAc1Cer8eFMxf+hgIepRXyg0nOBw5ckS6RZiI4QOIln2kL10IwCenSoeVhQxV741aAMXFxZKFeCgQ5ZWhcsMJpQApN3LzMHQA0bKPsLAwfr1qOWFhYRR9Xsbxz87y61XLmRDr3yzgwTYRYWFhpm8DEYyC+YYTKgFSmJOhA0jv7EMLFi/8VSqfnCrlwyPH/Z6FBPPrQUVfRr5Jy41cGJVhy3gfzD40619Ox2q1cPyzs1xvbvXb+eX1oKFDz8dDofRoSgQfw2Yg/WUf0LORMBBZSLC/HlQ8TJpsCjE0hgwgj8o+NOtfTvfrWkgovD/bW3LTE0JoDPkIS8s+li+Z329w0LKQ7u5uPjxy3OfnD4XXgw6Vns/hZQ1ACGMyXAYyWPah8VcWMpTXg4ZaFiI3ciFEb4bLQAbLPjT+ykKC/f3ZwrdaW1vdjTaFCDWGCiCeZh8aX1dkefN6UKnICm3SZFOEMkMFEE+zD42vsxBPsw+NZCGhTfvCUVpaKlmICEmGWQPp3XHXZrVy4H8VejTO9uPrOYfbIyvUXw8qhk6abIpQZ5gA0rvj7tGiz4c83ul0DatHlrweVAyFNNkUwiABxOl08cToUaz76xeH9TlWiwWn0+Xu3OspeT2oGCppsimEQQKI1Wrhb7N+pdv55fWgYiiM3mTTyH29fCHYr89MDLWILoQZPFhsYaRiimDv6xXs12c2hshAhDCLgZpsGikL8ebb8v379wGIjIwc8thA31yD/frMQjIQIYbgUaXeRspCvFVeXk5FRYXe0/CbYL8+PUgAEcJDnjTZHMrG0iNHjhjquXpZWRllZWV6T8Nvgv369KDLI6y5L6zT47Ruko4Kbzyqxb/GzK3+79y5Q21trfvnESNG6Dwj3wr269NLQDOQiqIDgTzdQ+eWjrLCW0NpsmnG9jbnz5/H5XLhcrm4cOGC3tPxuWC/Pr0EPAPRM4iA3MiFdwbLPjRDyUK0TNgIv5O9H+2cPXuWZ599VsfZ+F6wX59eZA1EiEEEe5PNtrY26uvrCQ8PJzw8nPr6etra2vSels8E+/XpSQKIEIMI9iab586dQ1VV5syZw5w5c1BVlXPnzuk9LZ8J9uvTk+wDEWIAodBk8+zZswDMnz8fVVU5f/48ZWVlpKWl6Twz3wj269OTBBAhBmDmJpvNzc10dnbicDhwOp0AOJ1OOjs73ce0tbXR2NhIVFQUM2fOBCAqKopr165x/PhxxowZ4z42IiLCHRitVit2u52IiAhiY2MDeFU/CfbrMwMJIEI8QjA02dy9ezfffPPNoMfNmzcPm83m/rmkpIS8vLwBx8TFxZGTk+OTeXor2K/P6CSACPEIZm+yGRsby7vvvsu+ffsoLi4GQFEUZs2ahd1uByA6OhqAZ555xj1u2bJl7m/iHR0dADgcDi5evIiqqgAsXryY9evXuz9HD8F+fWYgAUSIIGa328nOziYpKYkPPvgAh8NBa2srOTk5TJgwod8xkyZNYtKkSe4/t7S0sH37dlRVxWaz8eqrr7JkyZJAXcKAgv36jE6qsIQIAYsWLWLLli1MmDCBGzdusHnzZo/aepSXl7Np0yaampqIiYnhvffeM+TNNdivz6gkgAgRIsaPH88777xDamoqnZ2d7Nixg71797oXoHtzOp3s3buXbdu2ce/ePVJTU9myZQvx8fE6zNwzwX59RiQBRIgQEhkZycaNG8nMzASgpKTE/dy/N1VVKSkpASAzM5ONGzd61QY90IL9+oxG1kCE+FEoNdnUFpdnzJjhrk7qzWazMWPGDCoqKtzHmkmwX59RSAYiQl4oNtmsrKwEICUlBeipRtq5cyd///d/z507d/r8XVVVlS5zHI5gvz6jkAxECIzR0DBQHA4HdXV1KIrC7Nmzqa6uZs+ePdy6dQuAq1evkp2dzezZs1EUhUuXLuFwOExT0hrs12ckEkCECDE1NTV0dXURHx9Pfn4+p06dQlVVEhMTAbhy5Qq5ubksXbqUuLg4mpqaqKmpYe7cuTrP3DPBfn1GIgFEiBCjPbJpamqiqakJm83G6tWr3b2hPv30Uw4fPszJkyf7jDHLDTbYr89IJIAIEUJUVe3zzD8uLo4333yzT/lqeno6ycnJ7Ny5090mpKqqClVVURQl4HPubbBHjWa/PrORRXQhQkhDQwPt7e0oikJaWhq5ubn97n2Ij48nNzeXtLQ0FEWhvb2dhoYGHWY8NMF+fUYjGYgQIaSyspKxY8fy+uuvM3Xq1AGPtdlsrF27lnnz5rFr1y4qKyt56qmnAjRT7wT79RmNZCBChJDo6Gi2bds26M21tylTprB161ZD7JdYtWrVgPt1zH59ZiMZiBAhJD093atxUVFRXo8NpGC/PqORDEQIIYRXJIAIIYTwijzCEiIIDaWvV+/SWLP0AzPLPIOdZCBCBJFg7+sV7NdnNoraX69jIYQQYhCSgQghhPCKBBAhhBBekQAihBDCKxJAhBBCeEUCiBBCCK/IPhAfm/vf9enoWfHaZF3OK4TwLb32uHhTpiwZiA/pFTz0PrcQwjf03CDpzbklA/EDb7KBez90AxBlG3pMl+AhRHDxJhu4f/8+AJGRkUMe623gkgzEIIobOyhp7NB7GkIIkyovL6eioiKg55QAYhAnG+5wsuGO3tMQQphUWVkZZWVlAT2nPMIygNudLipu3Hf/PCrCovOMhBBmcufOHWpra90/jxgxIiDnlQzEAD67dhdnt4qzW+X/Xrur93SEECZz/vx5XC4XLpeLCxcuBOy8EkAM4FTDT0HjZIMEECHE0PR+dHX27NmAnVcCiM7+0OHkq2/vY7cq2K0KX317nz90OPWelhDCJNra2qivryc8PJzw8HDq6+tpa2sLyLklgOjsVMNdulVYEB/NgrhoulU49S+ShQghPHPu3DlUVWXOnDnMmTMHVVU5d+5cQM4tAURnWuXVsskjWDa5Z+HrlFRjCSE8pD2ymj9/PqmpqQABq8aSKiw/abrdxb0fVDqd3fzQ3fPOrh9ccN/Zs2EQFVo7nNR/7+Cx8DD+nwlRADwWHsaV7xz8U81txkVbQek5PNIahu3H4ixbmEKENYwom0L8qPBAX5oQIgCam5vp7OzE4XDgdPY81nY6nXR2drqPaWtro7GxkaioKGbOnAlAVFQU165d4/jx44wZM8Z9bEREBFZrzy3farVit9uJiIggNjbW67ctSgDxo7dLWmm42TXocX+Z8BjhFsX98/Hf/ZH/ev77AcdMHh3Olmef9Mk8hRDGtHv3br755ptBj5s3bx42m839c0lJCXl5eQOOiYuLIycnZ1jzkwDiJ/Gjwtn/ywn8l7Pf8env/gj0JBOpcdFEWBVQYER4zxPEFYkj3eP+eupItG4md7q6QYVOp0rZNx1o7x5Om/I4/3H+Ez2fI4QISrGxsbz77rvs27eP4uJiABRFYdasWdjtdgCio6MBeOaZZ9zjli1b5s40Ojp6uls4HA4uXryI9gbzxYsXs379evfneEsCiB9FWBXe+ss/YU5sJFu/+I77zm5u3PmBLc8+yZ/+rP9HT0lP2El64k/cf/6m/Qf+39MtqEC4ReHfpz7BLxMfD9AVCCH0ZLfbyc7OJikpiQ8++ACHw0Frays5OTlMmDCh3zGTJk1i0qRJ7j+3tLSwfft2VFXFZrPx6quvsmTJkj5jtF5YQ32UJYvoAfDin43gQMbP+dOfhdN4q4tX//fvPWpbUtLYwbqC6/xzWxdxI218+MsJEjyECEGLFi1iy5YtTJgwgRs3brB582aPFsrLy8vZtGkTTU1NxMTE8N577z0UPIZDAkiAJPwsnP2//DnLJo/g3g/d/H//t5WtZ79zL7D39kO3ytaz3/EfTrVwt6ubZZNH8D9/NYGnxsiCuRChavz48bzzzjukpqbS2dnJjh072Lt3r3uBvTen08nevXvZtm0b9+7dIzU1lS1bthAfH+/TOQXkEZaZXpDiT1G2MN55ZhyTx4TzD79to/B3d/h3T4996DhVhcLf9WQor/9iDL+e+bNAT1UIYUCRkZFs3LiR+Ph4Dh48SElJCVlZWQ8dp6oqJSUlAGRmZrJixQq/zMfvGYjZXpASCI//uHj+i59Huquvegu3KPzi55F9jhVCCI22eD5jxgx39VVvNpuNGTNm9DnWHwK2iB7obMCowQOgtKmnMmLhxJ7/sHe6uvkvZ7+jy6WyacETjIqwsCA+mpKvO/ii6R4ZSSMH+jghRIiprKwEICUlBeipttq3bx9dXV1s2LCBESNGkJKSQkVFBVVVVTz77LN+mYdUYQXYfWc3lc33CVN6SnrPX7/H2yV/4Pt7Pc8xa77t5K2//BPmx0cTpkBF8z3uO7uJtEomIoToKcmtq6tDURRmz55NdXU1e/bs4datWwBcvXqV7OxsZs+ejaIoXLp0CYfDMeyS3f5IAAmw8t/fx+FUeWqMnf9RdZOjde2owKyYnkdWF1vus7GomV9NHcmk0Xb+uc1B+e/vs2ii/9JQIYR51NTU0NXVRXx8PPn5+Zw6dQpVVUlMTATgypUr5ObmsnTpUuLi4mhqaqKmpoa5c+f6fC4SQALsix8fX/1zm4N/bnMQblH427mj+ZsZPQvl/1Rzi/9WcZP8uvY+YySACCEAqqqqAGhqaqKpqQmbzcbq1atJS0sD4NNPP+Xw4cOcPHmyzxgJICbXrf4UQKCnHcnbf/Vkn/Lctck/4y9+Hs1bn3/rboPyRVMH3SqEycZzIUKaqqruAAI97UjefPPNPuW56enpJCcns3PnTncblKqqKlRVRVF8exMxZAC5ffs2dXV13Lp1C0VRGDVqFNOmTWPkSHMvJtf9oZOb912EKZA5fRTZ88b0W4X11JhwDmRMYE95Gwdrb3Pzvou6P3QyfVyEDrMWQhhFQ0MD7e3tKIrC8uXLefnll/utwoqPjyc3N5ePPvqI48eP097eTkNDA0899ZRP52OoANLY2MjBgwepqalx92zRKIpCcnIya9asISEhQacZDk9pUwdPPmblPy8eR0ps5IDHhlsUNj49lsV/+hj/+fNWvmjqkAAiRIirrKxk7NixvP7660ydOnXAY202G2vXrmXevHns2rWLysrK4A0gRUVF5OXl0d3djd1uZ/r06Tz5ZE+32W+//Zba2lqqq6upra0lKyuL559/XucZD93j9jAO/XUcjw1hb8eMcRH8z19N4H9faR/8YCFEUIuOjmbbtm1ERUV5PGbKlCls3bqVzz77zOfzMUQAKSoq4sMPP0RRFNLS0sjIyHho80tHRwdHjx6lsLCQ/fv3A5guiKxN9m5H+WPhYV6PFUIEj/T0dK/GRUVFeT12ILoHkMbGRvLy8lAUhTfeeIMFCxb0e1x0dDRZWVkkJCSwa9cu8vLySExMZOLEiYGdsBAC8M1m3d4bjD39PKO1KApluu9OO3jwIN3d3SxfvvyRwaO3BQsW8MILL+ByuTh06FAAZiiEeJC0KBKgcwZy+/ZtampqsNvtZGRkeDxu5cqVnD59murqatrb2w1XnTX3vzfoPQUhAsKX2YAnnxUqwcMs16lrBlJXV4eqqkyfPn1IDb+io6OZNm0aqqpy+fJlP85waCpemxyS5xZC+Iaej+e8ObeuGcjNmzcBiImJGfLY2NhYvvzyS77/fuB3hwea3MiFEMNhpjUe3ddAvKXtE/H1zkohhBCe0TWAjBkzBoDm5uYhj21paenzGUIIIQJL10dYSUlJ7nbDHR0dHq+D3L17l0uXLqEoCklJSX6epRDCF4K1RVEo0zWAjBo1iuTkZKqrqzl69Gi/r2bsT35+Pl1dXcyaNUt++UTQM/sroYO9RVEo030j4Zo1a6itraWwsJCEhIRB94KUlpZy4sQJLBYLmZmZAZqlEPrQe7/FcINIKLQoCmW6B5CEhASysrLYv38/u3bt4tq1a6xcufKhx1l3794lPz+fEydOoKoqWVlZfVoYC+EpM36j92bs/fv3AYiMHLhxZ3988W8UKi2KQpnuAQR++oXJy8ujsLCQ06dP9/tNpaurC4vFwrp163juuef0nLIwKbN/ox+K8vJyFEVh4cKFATunRloUhQZDBBDoCSKJiYkcOnSI6urqPi9NgZ5npbNmzSIzM1MyDzFsga611yNwlZWV6RZAtBZFaWlpHrcounbtGoWFhRw6dIhNmzYFYJZiuAwTQAAmTpzIpk2baG9v5/Lly+6NhqNHjyYpKUkWzIXw0J07d6itrXX/PGLEiICdO1hbFImHGSqAaEaOHMnTTz+t9zSEMK3z58/jcrkAuHDhAs8++2zAzj3cFkVffvklly9flnuACRgygASaGRdVhRhIWVmZ++ezZ88GNIAEY4si0T/TtjLxFb0XVYV5tLa20traqvc0BtXW1kZ9fT3h4eGEh4dTX19PW1ub3tPyiLQoMhfJQH5kxjJJEVgFBQUAZGdn6zyTgZ07dw5VVZkzZw7Q8zjr3LlzpKWlBeT8odKiaO4L63Q5b0XRAV3O25+Qz0CGo7y8nIqKCr2nIYbgyJEjXn1ZaG1tpbS0lNLSUsNnIWfPngVg/vz5pKamAn0fafnbgy2KPGWmFkV6BQ+9z/2ggGUg/X3j9uZ1lkaiZ5mkJ/9e/vj3DdV1m4KCAveidEFBgS5ZSHNzM52dnTgcDpxOJwBOp5POzk73MW1tbTQ2NhIVFcXMmTOBnvdhX7t2jePHj/f5Zh8REYHV2nMLsFqt2O12IiIiiI2NHdY8Q6lFUaCzASMFDwhAADly5EhQLlLrWSap97pNqAURLfuwWCxATzudjIwMxo0bF/C57N69m2+++WbQ4+bNm4fNZnP/XFJSQl5e3oBj4uLiyMnJ8ck8pUVRaAhIBuLJDcdsNyU9yyQ1Q/k3044N9XUb7RqG8m+nZR+LFy8GoLi4WJcsJDY2lnfffZd9+/ZRXFwM/LTB1m63A7jLZp955hn3uGXLlrkzDe2RksPh4OLFi+5F68WLF7N+/Xr35wyXtCgKDbKI7iU9yySHQ8/2FmakZR9hYWGsWLGCsLAwSktLOXPmDCtWrPCqVHU47HY72dnZJCUl8cEHH+BwOGhtbSUnJ4cJEyb0O2bSpElMmjTJ/eeWlha2b9+OqqrYbDZeffVVlixZ4vO5Soui4CcBxAu9yyQBd5mkGSpH9Fy3MaPe2YcWLBYuXEhxcTHHjh3TrSJr0aJFTJ48me3bt3P9+nU2b97Ma6+95l40f5Ty8nJ2797NvXv3iImJIScnx6/f+KVF0cNufPsdAOOffELnmQyfBBAv6F0m6S09123M6MHsQ5ORkaFrFqIZP34877zzDu+//z5lZWXs2LGD+vp61q1b535kpXE6nRw4cICTJ08CkJqayoYNG7x6lDlU0qKor30ffQLAf/q3/0rnmQyflPF6Qe8ySW9p6zYul4sLFy7oPR3D07KPRYsW9QkS48aNY+HChXR3d3Ps2DEdZ9izlrVx40b3wnNJSclDL22Cng16JSUlAGRmZrJx48aABI/etBZFL774Ii+++CJPP/10yAWPG99+R9HnZRR9XubORMxMMpBezFIm6S2zrtvo4VHZh8YoWYhGW5yeMWOGu/qqN5vNxowZM6ioqBhSfyrhW/s++gSn0+X+2exZiASQB5ilTHKozLxuo4f+1j5607IQvddCNJWVlQCkpKQAPdVW+/bto6uriw0bNjBixAhSUlKoqKigqqpKvjzoQMs+rNaecvCiz8tY/3K6qddCJID0YqYyyaHy17qNP0p7PdkA6c+y78GyD41RshCHw0FdXR2KojB79myqq6vZs2cPt27dAuDq1atkZ2cze/Zs9w5xh8Oh2+9iqNKyj/SlPQUsn5wqNX0WIgHkAWYqkxyK3us2qqpy/vx5ysrKhhVAgnVD42DZh8YoWUhNTQ1dXV3Ex8eTn5/PqVOnUFWVxMREAK5cuUJubi5Lly4lLi6OpqYmampqmDt3ri7zDUVa9hEWFsavVy0nLCyMos/LOP7ZWX69ajkTYgO/KdUXJIA8glnKJI2wbuPPRpT9fbY/A5en2YfGCFmIVhrb1NREU1MTNpuN1atXu78cfPrppxw+fNhdgaWN8UUACYbNpYHQO/vQgsULf5XKJ6dK+fDIcdNmIRJABmCWMkkzrtsYdUOjp9mHRu8sRFXVPnsr4uLiePPNN/t8aUlPTyc5OZmdO3e6f0+qqqpQVdXrtunB2qLIHx7MPjTrX043fRYiAWQQWplkfHw8Bw8epKSkpN/mcA+WSXry7dUXzLpuY8QNjVr2AT3Z18cff+zROO3fUY8eWQ0NDbS3t6MoCsuXL+fll1/utworPj6e3NxcPvroI44fP057ezsNDQ089dRTXp/bbDdyvfSXfUDPRkKzZyESQDxk5DJJs63bGHVDY++Ou6dPnx7yeJfLFfAeWZWVlYwdO5bXX3+dqVOnDniszWZj7dq1zJs3j127dlFZWTmsACIG96jsQ2P2LEQCiIfMUCZplnUbIzSifJDL5WL06NG89NJLw/ocq9WKy+Vyd+71t+joaLZt20ZUVJTHY6ZMmcLWrVv57LPP/DgzAY/OPjRmz0IkgHjATGWSZli3MeKGRovFwurVq/WexpClp6d7NS4qKsrrscIzg2UfGjNnIdLKxANamRY5iIoAABLaSURBVGRcXBz5+fnk5uZy69YtEhMTSUxM5NatW+Tm5pKfn09cXBxdXV3U1NToNl8jt7cw8/u6hRgKLftYvmT+gEFBy0K6u7v58MjxAM5w+CSAeKB3meTJkyexWq288sor/OY3v+E3v/kNr7zyClarlZMnT9LU1NRnjJ48Xbfpfay/9d7QOGfOHFRV5dy5cwE5txCB4mn2oVn/cjpWq4Xjn53lerOxX5ncmzzCGoReZZK+YMR1G39saAwFD5bMmv110MFusLWPB5l1LUQCyCD0LJMcjkCv2xhhQ2Mwkv0W5qNlHwA2q5UD/6vQo3G2H3/fzdQjSwLIIMxaJqlHewszbWg007f2wW7kcqM3lt4dd48WfT7k8U6nyzQ9siSADMKsZZKBbm9hlg2N8o1e+JPT6eKJ0aNY99cvDutzrBYLTqfL3bnXqCSADMKMZZJ6rduYZUOj3MiFv1itFv4261d6TyNgpAorCPVet0lLSyM3N7ffjYHauk1aWhqKorjXbYZr0aJFbNmyhQkTJnDjxg02b97s0Rsby8vL2bRpE01NTcTExPDee+/p3sVYCPFoEkCCkLZu89Zbb7F27dp+F/012rrN22+/zbhx49yVW8OlbWhMTU2ls7OTHTt2sHfvXvcCe29Op5O9e/eybds27t27R2pqKlu2bPHrbnghxPDJI6wfDfW5uJHLKI2ybmP0RpRCiOEJ+QxEz+fh/jp3enr6kIKHxl/rNkbc0CiEGD7JQBj+jVwWZQdmxA2NQvjC3BfW6T0FXUkAEX5lpkaUQniqouiAbsGjouiALuftjwQQEzPa2kt/5H3doSEU99YY6Uaul5BfAzEjM63bmLURpfCcnl9kzPAlKphJBmJSZlh3MXMjSjF0gf6dlOChP8lAhN/ovaFRCOFfkoEIvzFrI0ohhGckAxF+o21oHCx49KZtaJT9IEIYn2Qgwm/M2IhSBFZra8/b98aNM897wMVPJAMRQuimoKCAgoICvachvCQBRAihi9bWVkpLSyktLXVnIsJc5BGWGDYppxTeKCgowOVyuX/Ozs7WeUZiqCQDEV4z04ZGYSxa9mGxWLBYLF5lIUeOHJHfA51JBiKGRf4HFt7Qso/FixcDUFxcLFmICUkGIoQIKC37CAsLY8WKFWRkZGCxWDhz5gwtLS16T08MgQQQIURAadnHokWLiImJYdy4cSxcuJDu7m6OHTvm8eesWrVK1t90JgFECBEwD2YfGslCzEkCiBAiYB7MPjTeZiFCX7KIHgDeptnDfe+6LHALI3lU9qHJyMigtLSUM2fOsGLFij4BRhiTZCB+Ju9KEKLHo7IPjWQh5iMZSIB4kw3cv38fgMjIyCGPl+AhjGSw7EMjWYi5SAZiYOXl5VRUVOg9DSGGbbDsQyNZiLlIADGwsrIyysrK9J6GEMPiafahkYos85AAYlB37tyhtraWmpoa7ty5o/d0hPCap9mHRrIQ85A1EIM6f/68u9HchQsXePbZZ3WekRBDp2UfAFarlY8//tijcVZrz62ptLSUjIwMeV+IQUkAMajej67Onj0rAUSYUu+Ou6dPnx7yeJfLJT2yDEwCiAG1tbVRX19PeHg4APX19bS1tTFmzBidZyaE51wuF6NHj+all14a1udYrVZcLhcWi8VHMxO+IgHEgM6dO4eqqsyZMwfoeZx17tw50tLSdJ6ZEJ6zWCysXr1a72kIP5JFdAM6e/YsAPPnzyc1NRVAqrGEEIYjGUgANTc309nZicPhwOl0AuB0Ouns7HQf09bWRmNjI1FRUcycOROAqKgorl27xvHjx/s8xoqIiHAvNlqtVux2OxEREcTGxgbwqoQQoUoCSIDt3r2bb775ZtDj5s2bh81mc/9cUlJCXl7egGPi4uLIycnxyTyFEGIwEkACKDY2lnfffZd9+/ZRXFwMgKIozJo1C7vdDkB0dDQAzzzzjHvcsmXL3JlGR0cHAA6Hg4sXL6KqKgCLFy9m/fr17s8JFXq1bJFGlUJIAAk4u91OdnY2SUlJfPDBBzgcDlpbW8nJyWHChAn9jpk0aRKTJk1y/7mlpYXt27ejqio2m41XX32VJUuWBOoSDEPvRpUSRPqS/muhRwKIThYtWsTkyZPZvn07169fZ/Pmzbz22mvuRfNHKS8vZ/fu3dy7d4+YmBhycnKIj48P0KyNKdA3crlR9nXkyBHJBEOUBBAdjR8/nnfeeYf333+fsrIyduzYQX19PevWrXM/stI4nU4OHDjAyZMnAUhNTWXDhg1ERkbqMXUh+pAbeWiSAKKzyMhINm7cSHx8PAcPHqSkpISsrKyHjlNVlZKSEgAyMzM9ako3VPItUggxFLIPxCC0xfMZM2a4q696s9lszJgxo8+xvqT3eoIQwnwkAzGIyspKAFJSUoCeaqt9+/bR1dXFhg0bGDFiBCkpKVRUVFBVVeW33liyniCE8JQEEANwOBzU1dWhKAqzZ8+murqaPXv2cOvWLQCuXr1KdnY2s2fPRlEULl26hMPhCLmSXV+4ffs2dXV13Lp1C0VRGDVqFNOmTWPkyJF6T80U5DGn6E0CiAHU1NTQ1dVFfHw8+fn5nDp1ClVVSUxMBODKlSvk5uaydOlS4uLiaGpqoqamhrlz5+o8c/NobGzk4MGD1NTUuPfOaBRFITk5mTVr1pCQkKDTDI1P78ecEkSMRwKIAVRVVQHQ1NREU1MTNpuN1atXu5snfvrppxw+fNhdgaWNkQDimaKiIvLy8uju7sZutzN9+nSefPJJAL799ltqa2uprq6mtraWrKwsnn/+eZ1nbGze3Mjv378P4FXVoDzmNC4JIDpTVdUdQKCnHcmbb77ZZ29Heno6ycnJ7Ny5090GpaqqClVVURQl4HN+UGtrK0DAX/rjyY2sqKiIDz/8EEVRSEtLIyMj46EihI6ODo4ePUphYSH79+8HkCDiY+Xl5SiKwsKFC/WeivAhqcLSWUNDA+3t7e4bXG5ubr8bA+Pj48nNzSUtLQ1FUWhvb6ehoUGHGT+soKCAgoICvafxkMbGRvLy8lAUhTfeeIO1a9f2W8EWHR1NVlYWb7zxBoqikJeXx9dffx34CQexsrIy6SgdhCSA6KyyspKxY8fy1ltvsXbt2n5LeDU2m421a9fy9ttvM27cOHfllp60V5aWlpa6MxGjOHjwIN3d3SxfvpwFCxYMevyCBQt44YUXcLlcHDp0KAAzDA137tyhtraWmpoa7ty5o/d0hA/JIyydRUdHs23bNqKiojweM2XKFLZu3cpnn33mx5l5pvcrSwP96lHt2Xh/j7Ju375NTU0NdrudjIwMjz9z5cqVnD59murqatrb26U6ywfOnz/v/h25cOFCyL+e+YPME7qc918f9P1jWclAdJaenj6k4KGJiooiPT3dDzPynJZ9WCwWLBaLobKQuro6VFVl+vTpQ9p4GR0dzbRp01BVlcuXL/txhqGj96Mr7WVpoUqv4OGvc0sGIrymZR+LFy8GoLi4OOBZyKPcvHkTgJiYmCGPjY2N5csvv+T777/39bRCTltbG/X19YSHhwNQX19PW1tbnxejhSJ/ZAMD8VfgkgxEeEXLPsLCwlixYgUZGRlYLBbOnDlDS0uL3tMbFm2fiBEq3Mzu3LlzqKrKnDlzmDNnDqqqcu7cOb2nJXxEMpAACbZa9t7Zh/Ytf+HChRQXF3Ps2DHdsxDtG25zc/OQx2oBMNS/JfuC9shq/vz5qKrK+fPnKSsrc+9xEuYmAcTPgvFdCQ9mH5qMjAxKS0s5c+YMK1as8Orxka8kJSW52750dHR4vA5y9+5dLl26hKIoJCUl+XmW5tXc3ExnZycOhwOn0wn0vHKgs7PTfUxbWxuNjY1ERUUxc+ZMoGft7tq1axw/frxPgI6IiHC/wsBqtWK324mIiCA2NjaAVyWGSgJIAJihBcNQ5thf9gE9GwmNkoWMGjWK5ORkqqurOXr0aL8t8vuTn59PV1cXs2bNkgqsQezevdu9sXUg8+bNc5enz5s3j5KSEvLy8gYcExcXR05Ojk/mKfxHAogYkkdlHxojZSFr1qyhtraWwsJCEhISBt0LUlpayokTJ7BYLGRmZgZoluYUGxvLu+++y759+yguLgZ61oxmzZrlbvKpZX3PPPOMe9yyZcvcmUZHRwfQ00z04sWL7rWnxYsXs379emkW+qP7tx00X7nJvVudKChE/sxObNJoIkfq/+8jAUQMyaOyD42RspCEhASysrLYv38/u3bt4tq1a6xcufKhx1l3794lPz+fEydOoKoqWVlZIf+aYE/Y7Xays7NJSkrigw8+wOFw0NraSk5ODhMmTOh3zKRJk5g0aZL7zy0tLWzfvh1VVbHZbLz66qssWbIkUJdgaN83/pGKw7+jubat3wag42eMZe7qP2PMxMd1mqEEEPGjgTblaQbLPjRGykK0nlZ5eXkUFhZy+vTpfpspdnV1YbFYWLduHc8995xu8zWyR/1uLFq0iMmTJ7N9+3auX7/O5s2bee2110hNTR3w88rLy9m9ezf37t0jJiaGnJwcCdw/uvR/vua3/1iP2q1itVsYP20Mj4/r+eLzx9YOblxq4/dffUfzpe/5xd8kMvU5ff7dJIAIjw2WfWiMlIVATxBJTEzk0KFDVFdX92leCT89esnMzJQbmJfGjx/PO++8w/vvv09ZWRk7duygvr6edevWuR9ZaZxOJwcOHHB3l05NTWXDhg1edeoNRpf+z9dcyLsCCkx/MYFZv5xEeFTfFkdd937gYsG/UHuikfN5PRte9QgiEkCERzzNPjRGykIAJk6cyKZNm2hvb+fy5cvujYajR48mKSlJFsx9IDIyko0bNxIfH8/BgwcpKSnpt3hBVVVKSkoAyMzM9Oj3KVR83/hHfvuP9aDAX/6bZCan9l+FFh5l4xev/DljJj5OyZ6v+O0/XeHJxJ8xJj6wj7NkI6HwiJZ9LFq0yKNgoGUh3d3dHDt2LAAz9MzIkSN5+umnefHFF3nxxRd5+umnJXh4aNWqVR6VpGtrTDNmzOi3OajNZmPGjBl9jhU9Kg//DrVbZfoLCY8MHr1Nnh/LtOcn0u1SqTx8NQAz7EsyEDEoLfuAnhr9jz/+2KNx2qOL0tJSMjIyAv6+EKEPrUt0SkoK0FNttW/fPrq6utiwYQMjRowgJSWFiooKqqqqQr65oub+bQc3atuw2i3M+uWkwQf8aNYvJ1P/2XV+/9X33G93BLQ6SwKIGFTvjrunT58e8niXy2WYHlnCvxwOB3V1dSiKwuzZs6murmbPnj3cunULgKtXr5Kdnc3s2bPdGz0dDoeU7ALNV26iqirjp415aM1jIPZoGzFTR3P94ne0XLnJn/5F4B4XSwARA3K5XIwePZqXXnppWJ9jtVpxuVxYLBYfzUwYUU1NDV1dXcTHx5Ofn8+pU6dQVZXExEQArly5Qm5uLkuXLiUuLo6mpiZqamrk9czAvbaeXfyPxwz9sd6omMe4fvE7Oto6Bz/YhySAiAFZLBZWr16t9zSESWgVbk1NTTQ1NWGz2Vi9erW799Wnn37K4cOH3RVY2hgJIIDWu1Md8Kh+qdqgAPf/lAAiTC/YGlWalaqqfUqk4+LiePPNN/uURqenp5OcnMzOnTvdbVCqqqpQVTXkux9Hj44AoL2lY8hjtTHaZwSKVGEJ09Kzx5gZ+psFWkNDA+3t7SiKQlpaGrm5uf3uq4mPjyc3N5e0tDQURaG9vZ2GhgYdZmwsMYmjURSF5ro2uu794PE4x90faKm7iaIoxCQFtoO0ZCDC1ORGbhyVlZWMHTuW119/nalTpw54rM1mY+3atcybN49du3ZRWVnJU089FaCZGlPkKDvjZ4zl9199x8WCf+EXr/y5R+MuFjTg7HIxYeYTRD4e7udZ9iUZiBDCJ6Kjo9m2bdugwaO3KVOmsHXrVtkP8qO5q/+MMItC7YlGGs4O/i6bhi9ucOnk14RZFOaunhKAGfYlGYjoQ9YThLfS09O9GhcVFeX12GAzZuLj/OJvEjmfd5mSPV/x/dftzPrlZOzRfct6HXd/4GJBA5dOfg0q/OKVREbHjwj4fCWACCA4X3wlhBlNfS4eFPjtP17hUtHX1H92ndipY3g8JgqAP7bco7muDWeXizCLwl+sTSRpqTRTFDqTG7kQxjB1WTxP/vnPqDx8ld9/9T3fXPwDXPzp7xVFYcLMJ5i7eooumYdGAogQYkjkMWdgjIl/nGX/MYX7f+yi5XIb9246AIgabScmaUzAF8z7IwFECOERecypj8jHwwPanmQoJIAIITwWyjdy8TAp4xVCCOEVCSBCCCG8IgFECCGEV2QNRAghAuyDzBN6T8EnJAMRQogA+dcHnw+qcyuqqnrRfV4IIUSokwxECCGEVySACCGE8IoEECGEEF6RACKEEMIrEkCEEEJ4RQKIEEIIr0gAEUII4RUJIEIIIbwiAUQIIYRX/n+2McKhnGvoAgAAAABJRU5ErkJggg==</v>
+      </c>
+      <c r="E479" t="str">
+        <v>24-08-2026 02:48:29 pm</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="str">
+        <v>6a8c0c83f8bcde8f653c9fdc</v>
+      </c>
+      <c r="B480" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C480" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D480" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E480" t="str">
+        <v>24-08-2026 02:48:59 pm</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="str">
+        <v>6a8c0c84f8bcde8f653c9fe5</v>
+      </c>
+      <c r="B481" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C481" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D481" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E481" t="str">
+        <v>24-08-2026 02:49:00 pm</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="str">
+        <v>6a8c113cf8bcde8f653ca0d4</v>
+      </c>
+      <c r="B482" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C482" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D482" t="str">
+        <v>Started Playing game and Debited "10" and Balance "490"</v>
+      </c>
+      <c r="E482" t="str">
+        <v>24-08-2026 03:09:08 pm</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="str">
+        <v>6a8c113cf8bcde8f653ca0da</v>
+      </c>
+      <c r="B483" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C483" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D483" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E483" t="str">
+        <v>24-08-2026 03:09:08 pm</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="str">
+        <v>6a8c1159f8bcde8f653ca104</v>
+      </c>
+      <c r="B484" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C484" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D484" t="str">
+        <v>Answerd Correctly to Qst ID : 6a8c113df8bcde8f653ca0e4, Reward : 10, Qst No : 2 ,Question : How many words are scrambled?</v>
+      </c>
+      <c r="E484" t="str">
+        <v>24-08-2026 03:09:37 pm</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="str">
+        <v>6a8c115df8bcde8f653ca11b</v>
+      </c>
+      <c r="B485" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C485" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D485" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6a8c115cf8bcde8f653ca113 , Question : How many times do the letters W, Z, J, L, V appear in the paragraph?, Type : count_leters_exist </v>
+      </c>
+      <c r="E485" t="str">
+        <v>24-08-2026 03:09:41 pm</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="str">
+        <v>6a8c1170f8bcde8f653ca130</v>
+      </c>
+      <c r="B486" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C486" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D486" t="str">
+        <v>Answerd Correctly to Qst ID : 6a8c115cf8bcde8f653ca113, Reward : 40, Qst No : 3 ,Question : How many times do the letters W, Z, J, L, V appear in the paragraph?</v>
+      </c>
+      <c r="E486" t="str">
+        <v>24-08-2026 03:10:00 pm</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="str">
+        <v>6a8c1173f8bcde8f653ca147</v>
+      </c>
+      <c r="B487" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C487" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D487" t="str">
+        <v xml:space="preserve">Created Question Number : 2, Rupees : 30, Qst ID : 6a8c1173f8bcde8f653ca13f , Question : How many words are colored with the WRONG color?, Type : word_colour_find </v>
+      </c>
+      <c r="E487" t="str">
+        <v>24-08-2026 03:10:03 pm</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="str">
+        <v>6a8c117ef8bcde8f653ca15c</v>
+      </c>
+      <c r="B488" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C488" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D488" t="str">
+        <v>Answerd Correctly to Qst ID : 6a8c1173f8bcde8f653ca13f, Reward : 30, Qst No : 4 ,Question : How many words are colored with the WRONG color?</v>
+      </c>
+      <c r="E488" t="str">
+        <v>24-08-2026 03:10:14 pm</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="str">
+        <v>6a8c186ef8bcde8f653ca178</v>
+      </c>
+      <c r="B489" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C489" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D489" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E489" t="str">
+        <v>24-08-2026 03:39:50 pm</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="str">
+        <v>6a8c186ef8bcde8f653ca182</v>
+      </c>
+      <c r="B490" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C490" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D490" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E490" t="str">
+        <v>24-08-2026 03:39:50 pm</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="str">
+        <v>6a8c1873f8bcde8f653ca271</v>
+      </c>
+      <c r="B491" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C491" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D491" t="str">
+        <v>Started Playing game and Debited "10" and Balance "480"</v>
+      </c>
+      <c r="E491" t="str">
+        <v>24-08-2026 03:39:55 pm</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="str">
+        <v>6a8c1874f8bcde8f653ca277</v>
+      </c>
+      <c r="B492" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C492" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D492" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E492" t="str">
+        <v>24-08-2026 03:39:56 pm</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="str">
+        <v>6a8c1890f8bcde8f653ca2b3</v>
+      </c>
+      <c r="B493" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C493" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D493" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E493" t="str">
+        <v>24-08-2026 03:40:24 pm</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="str">
+        <v>6a8c1891f8bcde8f653ca2ba</v>
+      </c>
+      <c r="B494" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C494" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D494" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E494" t="str">
+        <v>24-08-2026 03:40:25 pm</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="str">
+        <v>6a8c18e6f8bcde8f653ca3ab</v>
+      </c>
+      <c r="B495" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C495" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D495" t="str">
+        <v>Started Playing game and Debited "10" and Balance "470"</v>
+      </c>
+      <c r="E495" t="str">
+        <v>24-08-2026 03:41:50 pm</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="str">
+        <v>6a8c18e7f8bcde8f653ca3b1</v>
+      </c>
+      <c r="B496" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C496" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D496" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E496" t="str">
+        <v>24-08-2026 03:41:51 pm</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="str">
+        <v>6a8c18f8f8bcde8f653ca3db</v>
+      </c>
+      <c r="B497" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C497" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D497" t="str">
+        <v>Answerd Correctly to Qst ID : 6a8c18e8f8bcde8f653ca3bb, Reward : 10, Qst No : 2 ,Question : How many times does the letter sequence 'fly' appear in the given words?</v>
+      </c>
+      <c r="E497" t="str">
+        <v>24-08-2026 03:42:08 pm</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="str">
+        <v>6a8c18fcf8bcde8f653ca3f2</v>
+      </c>
+      <c r="B498" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C498" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D498" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6a8c18fbf8bcde8f653ca3ea , Question : How many times do the letters L, P, D, G, C appear in the paragraph?, Type : count_leters_exist </v>
+      </c>
+      <c r="E498" t="str">
+        <v>24-08-2026 03:42:12 pm</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="str">
+        <v>6a8c190ff8bcde8f653ca407</v>
+      </c>
+      <c r="B499" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C499" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D499" t="str">
+        <v>Answerd Correctly to Qst ID : 6a8c18fbf8bcde8f653ca3ea, Reward : 40, Qst No : 3 ,Question : How many times do the letters L, P, D, G, C appear in the paragraph?</v>
+      </c>
+      <c r="E499" t="str">
+        <v>24-08-2026 03:42:31 pm</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="str">
+        <v>6a8c1912f8bcde8f653ca41e</v>
+      </c>
+      <c r="B500" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C500" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D500" t="str">
+        <v xml:space="preserve">Created Question Number : 2, Rupees : 30, Qst ID : 6a8c1912f8bcde8f653ca416 , Question : How many colour names match their text colour out of 8?, Type : [Colours &amp; Name Match] </v>
+      </c>
+      <c r="E500" t="str">
+        <v>24-08-2026 03:42:34 pm</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="str">
+        <v>6a8c20c5da9813f97099993d</v>
+      </c>
+      <c r="B501" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C501" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D501" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E501" t="str">
+        <v>24-08-2026 04:15:25 pm</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="str">
+        <v>6a8c217e9f26e6fd288c7128</v>
+      </c>
+      <c r="B502" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C502" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D502" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E502" t="str">
+        <v>24-08-2026 04:18:30 pm</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="str">
+        <v>6a8c217e9f26e6fd288c7132</v>
+      </c>
+      <c r="B503" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C503" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D503" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E503" t="str">
+        <v>24-08-2026 04:18:30 pm</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="str">
+        <v>6a8c21849f26e6fd288c7225</v>
+      </c>
+      <c r="B504" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C504" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D504" t="str">
+        <v>Started Playing game and Debited "10" and Balance "450"</v>
+      </c>
+      <c r="E504" t="str">
+        <v>24-08-2026 04:18:36 pm</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="str">
+        <v>6a8c21849f26e6fd288c722b</v>
+      </c>
+      <c r="B505" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C505" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D505" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E505" t="str">
+        <v>24-08-2026 04:18:36 pm</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="str">
+        <v>6a8c21af9f26e6fd288c7262</v>
+      </c>
+      <c r="B506" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C506" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D506" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E506" t="str">
+        <v>24-08-2026 04:19:19 pm</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="str">
+        <v>6a8c21af9f26e6fd288c726b</v>
+      </c>
+      <c r="B507" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C507" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D507" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E507" t="str">
+        <v>24-08-2026 04:19:19 pm</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="str">
+        <v>6a8c21b09f26e6fd288c727a</v>
+      </c>
+      <c r="B508" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C508" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D508" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E508" t="str">
+        <v>24-08-2026 04:19:20 pm</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="str">
+        <v>6a8c21b09f26e6fd288c7283</v>
+      </c>
+      <c r="B509" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C509" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D509" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E509" t="str">
+        <v>24-08-2026 04:19:20 pm</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="str">
+        <v>6a8c21cc9f26e6fd288c7377</v>
+      </c>
+      <c r="B510" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C510" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D510" t="str">
+        <v>Started Playing game and Debited "10" and Balance "440"</v>
+      </c>
+      <c r="E510" t="str">
+        <v>24-08-2026 04:19:48 pm</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="str">
+        <v>6a8c21cc9f26e6fd288c737d</v>
+      </c>
+      <c r="B511" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C511" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D511" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E511" t="str">
+        <v>24-08-2026 04:19:48 pm</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="str">
+        <v>6a8c21d99f26e6fd288c73a6</v>
+      </c>
+      <c r="B512" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C512" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D512" t="str">
+        <v>Answered incorrectly for Qst ID: 6a8c21cd9f26e6fd288c7387, Qst: How many letters are colored with the WRONG color?, Submitted Answer: 2, image : iVBORw0KGgoAAAANSUhEUgAAAZAAAAD6CAYAAACPpxFEAAAABmJLR0QA/wD/AP+gvaeTAAAgAElEQVR4nO19d5zcxPn+o11tu2Jfs33nfrbv3LFxoZliaiimp0F6yDeBb4AkP0K+qaQ3kpCEkEBII4QQCCEQaiBAMJhm3O07l3P3uZ3v7OvbtKvfH1tu9yStRtLMSNrb5/Oxb6V9531HZeed5xnNSIhEYzJ0IGf/y/tgCorSmu4Kxyn4LXEVZTPmBr82VcjgWZY1N61drWFuZTreZM0N1R3kvojdKL8kikpYNVnlkxmfZOHIbiAqv9r8P1SR37ywiDAsDvkO6zGIXZPHpnm/FjLWc+GhWgejvgjPdDweRzwep1wnusnDQhW4hLIKWslDJwoda47XStvMxvNFNXnkO2F6VIxPGYNcoR+DQ0nrMJc8AEA05p/H6VEmj/DgYGqjrAw+n49WIKrJw/wloFyCEfughcLsg3YAMgP61TCcbcx60C0oSRJkAKJI9lMv5JDV/URT4TAWlGgnw3gMXVmMR1q84F0lF9iyDJPuaEpXtEBTuqJVkRErXTEoRSEfWDQ250CSJEQi4dRGMGQiifCgHSrxbPFckq7MQPOOotkhMCtdAUgxjrKy7Gdal7k4pCv2v2w+0pUx0JSuaP22afbTTTd27uhAK/0WgXTlTljXTQp3SbhKV9rIyFZ02IczpSvjKCbpikUvRd+gqKQrFXhFEYFgCIAZCWuIfTBNHhpbzMBIunIn+7BeXPWuYnopTZ7p4d9mBtV9Pl9RSFe0auZE6Srfqe4OY8VZgoV0ZRlkN1Bm09zYB0fpijf7YFABe7vXZt3R6bRp310s2Acl7UExsC7qDKybicSxVbAsXbFo5ykmD+bJcaSzD9dLV2yi2C5dUYzn1FyueIyXx4U1CjrSlXPZh6XII126MlYD8qgs2Ifl5EHTSqc0t6Rk5107UqUrepKxqLKPCmixD7Vv8wbWidiHTBCJuErmwFi6oonSnA+jZjaeLxZklIeCxVu64qHGcihpHaa6vprGSgmLhXRFwXI4jI190E0eFC4BnRKuZh+0A5AZlKQrMofFL125Q/ejzz7oFs9KWExppUl3JemKzCdV5lia80Hfu+VTWhzSlWo8W1CSrkxjmAtP3j76/jlrD+oxikO6Yn++SnM+jPph2BDpWbijA630WwTSlTtBV7rKwKP80hnKHh324UzpyjiKSbpi0UvRNygq6Yq6ryH2YdSPJEmQJIk0guoWMzCSrtzJPqgXBwCITC+lyTNd7NIVrZo5UbrKd6q7w1hxlmAhXVkG2Q1kl3QlSRJi0Uh6K6g/54Q3+2BQAWd0r426Y9dpE/O/pHd67v7lL9C2o428JgXQ1NyMW279nOU6WTe0DsvS1bDNX9/zK+xsUzvPRiKknM6Y0YTP3nyLRV90QLOXR6NO9/7mHuzauZOKrxkzZuAzN33WXGHXS1eFo9x/373YtWsnlbjTp8/A/3zmJiq+dEHx5NmgaZiGSHUAJAdtO9qwcdsGeBu8lvwkDieGNoqAfViKrCJd7Wxrw7q2nRic2mwpUtneHZbK59ZJuaG6gwFMJg8Co107d2J3yzY0h8YarlUudoQ7CC3Jzpdd7APIzHIP5nzWjKC6pYZdu3Zi75bNaPZaazd2JBLD9oxU6YqtZGx2jefC/tM7vA1eVH6m0pLvvt/2maqNreyDsXQ1HINTm7HjW/db8tH8rU8DGP6jowVK0hXHa6Vm1hwai/tnXm8p3Ke3P4y4rhUP6SrfiVlfREulGHTe7PXi/kpr7can+/oQs+QhH46RrijEppl/PCZcGvFPDwYC0UweFC4BnRIq7MNJKMw+aAcgM3DieTIN6gcjq3xiEIGRwmEM7tD9SFwlJAmJhP5DC1ZiGIFo7+AObRSLdKXt04mNIk3pytzxmTwrBtgHPzhfujIdzxYUj3SVkCTEolEAgD8AeL2F2B9b6SoD3VfaGvLvgOShVoW/PvI4bv78V/Ct7/0MK1e9hTu+fSc6OjoVdl3HT+CO79yJl199HQBw3+/+jLt/8/vs9319fejsOqFXBdLdBeDENAEcPHQY3/reT/H2O2uJ7B/4y6O46+77AAD/efk1fPt7P0Vvr7YkSVO6ovXbdkTyyNm98vW38N0f3oXjJwrch9Yj0vHrzNuYKxKShATBY850wV66yoA4gbB5LzldqNVpz579+Pb370L7wcOoq63B1m078cg//oXunl6F7WA4jOdefAVtu/ZCBvDiS6/i+RdeAQCs37AZF634IHbu2s32IBwsXR0/3o2/P/4UduwcOge5dZLicUjS0D3y6mtv4Kln/wMA2NKyFX//59MIZ96QRwpHSFd2n/kh7Nq9Fy++vBKDgxF9Y1UMsQ+myUNjy22wwj4SkoRoLIpoLFowiZAOnHu9IvyBAPyBgA77MBnDBIhqEY/HMZhePr1M673kNrOPWCyGt9esx0D/IMaOrcPJC+YhEoni7dWp3vLyc5bh6isvwdPP/SddRMbadZsQjkawdNFCBAJ+jBtThwfu/yXGjKnN8x6NxrBy1ds4fqIbe/cewMzmGaiuGj28Cho1o3WEzsKOHbtw6MhRLFwwH6NHV0KKxxEJh7H/wEEcOtqBhfPnaZaVEgls37ETXq8Hs5qbsHvPPnhFETXVVVi/cTOqq6swb86srP2+fQfQtnsvfF4Ri06ej8rKCgDAzt174BEETGucAiDVuALAtGlTC1feJeyjbdde7Nu7H/X1Y7PnY8VlF+HUUxdj3JhaDAyGsW//AUyeNBHt7YfQdfw4Fp+8AF6PgLXrN8Pj9WDp4oUQBAEAkEwmsGnzVpw40Y2mGY2YMGF8XrxNm1vRPzCARQtPwr4DBzC6chTq68di5849CJUFEQ5H0XHsGGprqyF6RUxPn+dIJIrde/dhVGUFevv6UVtTjbFjxgAAjhzpwInubjRNb4So1m7YDFmWsaV1G06c6MacWTNRV1eT/a6vrx8bNrVg3Ng6NNSPw4GDhzFlykR4PV7s3r0PE8bX49DhozjWeQwL589D5ahKHD16DMdPnMCsmTMAAPv2tyOZTGJWcxMAYOu2NlRWlKOvfwCi14OmpukAgO07dkEQgIkTx2Pfvva8OoqeITv9xMFHusrA1FNYzpKugP7+AVxz/aewb187fD4R0WgMH77uvXjftSvwze/9FADwm98+gONdJzB+QgMA4Mvf+D527t6LSCSKkxfMwyMP3ocjRzpwzQc/ic/e+Anc+r+fyvo/dPgI7r3/AQDAN7/3U/h8Iq69eoVuvWgOnDsJjz3+FH5xz+8Qi8VQU1OFB373K0yaUI+nnn0RP/rZPfB6vSgLheDz+1XLf/+HP8djTzyDb339dsxqbsLtX/kuYvEYBgfDOH6iG7FYDJ+/5TP41Mevx6OP/Qvfv/MXGFNXh57eXvj9Pvz1j79BY+Nk3PZ/34LfJ+Kxh1My4xe/8h0IgoDHH/kDxaO15yL84Me/xKP/+BdEUYQkSbjkPefjR9/9Gh5/4hnc97s/46nHH8TRjk78z03/DwsXzMPWbTsQjcYwb+4sQAbadu1GNBrDRz/8fvy/W29E/8AgbrrldmzeshUA4PF48ImPfhA333QDAOCO7/wYTz/7Inw+P5qmT8WevftxxYr34Mu334rP3f51BPx+tB88glAogFOXLsJ/V76BF555BDXV1Xjiqedw58/uwa9/+SN8+RvfR9O0Rvz+vp8DkPGlr30Hxzq78OwTf7XlPBZCMpnEF7/8Lax8/S2UhUJIykn84DtfwzlnnY6Dhw/jUzfehs7OLvh8ImbPasaGjVvw+/t+jvJQCB/55P9i8cknYePmrZCkOOrqanD/PT/Dxk0t+PYPfoqH/vQbzJjRiBtv+T9IkoT/vvAE9uzei4988rP44uf/F5u2tOLFl17Fz+78NrpP9OC7P7wLn/jY9TjzjKW44TNfyKtnTXUVXnjm76aPk+UdTCRh+Xw+lJWVabMPWyGj6/gJnHXGqXjkL/dh/Tsv4aR5s/HflavQPGM67vn5DwAA3/r6bfjKl27Nljpr2WnYtPoVXH3FJVi/cQsOHDysGWHypAn46pdSExnvvftHuPyyi4ZXgcpxaG06LY+MrhqFt1Y+g4cfvBfHj3fjt7/7MwABd9/7R0ybOhmrXnkaD/3pN+hRkQl/+4eH8Pd/Po3bPncj3nv1Zdn9+/e34xc/+y5ee+lJjBpViRdeTEmHTz//IiaMr8d9v/oxnvnnX/CJj16H1MTH4h04X79hCx79x7/w8Y98AKtf/zc++bHr0NFxDB2dXaqlR4+qxJuvPofLL7sIW1q24ZyzT8cbrz6LMXW1ePOt1QCA3/3xL9i8ZSu+960vY/Xrz+Oqyy/BHx54GGvWbsDGTS14+tkXseLSi/D2a8/i6isvRTiSL5Ht29+On/7oDtz7qztx3fuvgSRJ+PcL/wUAPPPsi5g6ZRJOO3UJLr7wXGzYtAXHOjtx5EgHWlq349KLz4fHY2m4lQleeuU1rHz9LXznji/h1f88icWLFuDOu+5BIpHEn/78CDo7u/DH3/0SK//zJHy+dF8751INDA7ipef/gT/97m6cONGN3/3pIZx11qkQvV68+fZqtLZuw8DAIKLRGDa3bMWbb66GIAg495xl+Ortt6Khfhx+eOfd+Pnd92HunFn4zA0fxqyZzXjiHw/iycf+jFNPWQQA+PhHryM8Ir7sAzAwBuLz+eDz+QywDx4/wVSMyZMn4vzlZ+KfTz6Hi6+4Hpu2bEU0GoXX60FZWeqd0MFAEKFgMFty+dlnAACmNU4FkGIxWvB6PQiFUmXLykLw5/asGUtXTsR555wJv9+P+XNnY0JDPba37cKRjg709fXj7LNOR3lZCI1TJ2Fm8zRF2Ucf+xcEQcDSJQsBDJ2n2tpazJszCxUV5WioH4eBtGR6wbln4UD7IVz9gU/gY5+6Bd3dPairHZIZZFnIfk4mk4Urbjh58LuHc9HSuh0AcN7yM+H1evC5z/4P/vDbX2BMXa3CFgCWLlkEr9eD8Q31AIDTT1sK0evFxIkN6OlJPbTw7rvrUVdXgxWXXAif348PXXctAOCdNeuxoy01prXikgvg8Xhw8XvOV8QYN24Mzj7zdMyZ1YyTF87D9GlT8cxzL2Lnrr1o3bYDV195KQRBwJUrLkYymcRLr7yGl199HbIsY8UlFyn8OQFb0uf5xZdX4qt3fB9Hjx7DkSMdOH7iBNradmPMmNQ9Kfp8OPecMxXlzz3nTFSUl2H+3NmYOnkytm/fiarRo7HgpLl446138e7aDWioH4dJkyZgzdoNeOOt1Zgzuxnjxo1BRWUF7vhaiuEMhiP4zh1fglcU4ff7MHF8Pf719PN4Z/U6fPB9V+G6919NcDT8Bs5zYahbQPehNDqQAbz86uv4+Kc/D8Ej4Gc/+ibOOH0pPJ7CM1nLy1MvpBLFlJ0sywVrndGRSetkDO5hHwDQm5NsI7EYyspCCPpTCTZ3cDcSiSrKXnvVZaitrcaPfvqrvPW3KirKsp99/iFl9eMf+SAee/j3uOnTH0N1TRX+/NCjuPOuewAAAoTsoLwMoKfP6KTTQrDvzPvTLH9gMHVsRzuOYfWa9RgMqz+AkOkkZXr55emXrXmzvwEZgaAfsVgcUiKVZMNp36FgCKGy1LWLxVMDvWqdqVEV+RP7rrlqBbZub8Nvf/8gfD4/Vlx2ESADc2bPxIzpjXjp5ZV46eXXMHfOTDROnWzqPLCGJ/2bPuuMU3Hh+efgfz75Yfz4+99AMBiE3+/HwMBgdqHI7p4eRfnc8xSNRhEMBQCkEktLyza8/N9VWLr0ZJy2dBFeff1NbNzUgvPSiUgGsGbdRgCpjs8rr76R9fXEU8/jTw8+gnPOOgOfv+VG08fH4w62xisd8NguAGzesg2yLGPZaUshQEBL6zZEY8rGi8ybOvyB1I967bpNOHDgIFkhM3B48gCAfz75DFa9tRoPPPgojh3rxClLFqG2thozpjfi+Rdexuur3sYjjz2Jtp17FGU/e+PHcfNNN2D9hi147oWXs/vVErQsy/joDTfjq9/4Pq5YcQnu+Mpt8Pv9iKef9GoYPxZHjh7Du+s24PEnn8VxE49YmzSjBPVoS5cshOj14g9/+ivWrNuI7//4F7jx5tvR1XXcdKRzz16G3t4+/OSue/DumvW46+774PP5cd7yZVi0YD5Enw8P/uVRbNrcip+nH73ORaZxzODySy9EMBjAS6+sxLnLl6G6qip7TFeseA82bm7F5patuOySC0zXmTUyEtG+A+2YPm0qHn7kn/jHE08jGArizGWnoL9/AN/74V34++NP4W9/f1JR/ulnX8Qbb63Go489ifZDh7FkcYpVLz/nDCSSSexo24VTFp+MU5YuQlvbbkiJBM5bfiZkAJu3tOKBB/+GC84/BwtOmovf/v5BbNu+E2vXb8KdP7kb5WUhzJ3djIf+9hj+/NCjmp2HFPhLVxkQJxAnSleZSFdffjEa6sfi5i98Fbfe9jUsWngS+voG0HFMOdfDLBadNA+jRlXi7t/8AS/99/Win/NRCBecdza+/NXv4ic//zWWnbYUN3z8egiCgO9/+8sIBoO48db/w7+eeQHLTluqWv6aKy5F04xG3PXL3yIyTGvPPR2CIODmm25AOBzBJVd8EO//0P+gafpU3JJ+wOF911wOn+jFJz/9BTz7/EuYP2+2eoVdIl1ldjdOnYw7vnobtu3YiRtu/ALWrN2Ar95+KyZNnJA1M8KIAeD6D16L6z9wNZ546jl8+rNfxP72g7jzB1/H1CmTMH58Pb74+ZuwYXMLPvmZz2VZeSFUVlbgoguWAwCuufLSvMPJjHl4PB5cfNF5hurJE6efugQf+/AH8PfHn8Z7r7sBB9oP4voPXAvR68X1170X77vmCrz2xtt49vkXseLiVCLMHQOeN28WvvmdO/GTn/8apyxdhE9+5IMAgPpxYzFr5gwIgoAlixdi6aIFEL1ezJjeiEmTJmAwHMY3vv1jjKqsxJduuxnf+Mpt8HiAO771I6xfvwlSIoGBwTB+c/8DuOfeP+Cee/+A8IBWArFHukoVkyGEI1Fzc650dt5y82expWcLlbWw5o2eh7t/9eu8OMPDJxJJHD9+AnV1Nfk/LoKTQ3oJ4vE4+voHUFNdRSmBWJeuvvC5W7Eq7qGyFtYyXwI//8Xdmja5dUpISfT196Nq9Ki8b2VZRndPr/Ix5wK+Cu9MobPzOPx+EaNG5d9P8UQCgwODiv2kfpVm6sZf/H9fgG/3cTprYU2rwU9+dlehSgBISRudx0+guroKotcLKZHA9354F5586nm8+uITqNI5x2pzPmKxGHp6+1THU6LRGOKSBDmZxNkXXIkPvPdKfPn2WxV2qtWVh7baDx3GNe//BJadfgp+/pPv6NQxH/93+23wb22lsxbW7Dn40Z0/1bWNRmPo7u5BTV0NxPQiji//9zUcPtyB5cuXYWJDA+69/wH84YG/4rknH0ZPTy+u+9iNuOWmG/Ch69+H/v4+VI3WuxYpkM75IIfS2HA+sJBAzC2m6BDpKhder0cxf8O8N/W9Pp+PYvIwWicHQU6d7+HJA0j1jE0lDx2kns9XlhS9XorJgxfIbiDB48lr6L9w+zfw+qq3UVU1uvAx5zob5tPv92sOxgcCfgQCfvT19ev41q731775A6x6613IchIf/fD7jfmxCYGAH2PHjcnb5/WK+MWvfos//+VR1NePQVvbbixZtABjxtTlPV0oej3EyYMIPKgDBReZLrxuAnGWdGUwEsdWgebAuRPBPDma4MH0T5mNF4Eg9HsuWI55c2bhgvPPNvRYrNGjCgUD+PpXvoDpjY36fvMpCM5bfiamTJ6E005ZjJPmzzEY2TlYfvYZeOiBe7Fu/SYMDAziI9e/D+ctPxOCIGDsuDH46v99HvNzJruSwEZhlBmoLOfOD3RPjyn1kEoV3PXUlay5obqDdQ3IozqSfZBBrU4rLiV9HFadfZBC9Plw7VWFJ8rKGlvnn3s2zj/XXFy7oHWaZjXPwKzmGYr9o0eNwjVXXlagJHkM40amjKm6yB1AKJhArLKPxOGEifd5KH1g9FAMW9kHY+nKLMr27ki/z8OaD6SXSyCHpREfs24sBtMy0y+wI9yBT29/2GyNsj4aUa1VCcKaEMBaDjEUgzZ2JBL4tMVHsnckEphKYGf+EOz81ds7cJ4LzQRiNbc2NVt7Q14Wo4GmpuYCkYirRGBiWYgyXsIi+5jR1JT+lD+JrvCsFhU0TceMGU2K3YXZBwW4RLqaMSPVE9V/GVThOI2oxvQZM3J3UYaRlGghwjDpihamT0+dG6svg5oKYPp0ox2iHFA8LPrsg3px09B8CovW2EfBbw1mBFoJhKZ0ZSmBMJKucifoWfKjuaG6g9wXsRuTaZ4B+7CubJLdQNaunKz2hzrk/P/YxTC2w3oMYtfOk67sYB+AxjwQWsmDDopJumJ/vmglD5qgefvYkjwsh+SvffJhHwxjFNwxUuGs5AGoJBCauZUO+3CmdGUcdKUr1qDJPvQDkBnYIV3pmVFljjRKy4yTh8YWM5DpI3TcErm2k31QL24Z+k9hmc5YNHySB9+1ey/eXrMOHo8HtdXVOO/sZRDF/MOzV7pi6wdgxD6Gudy2ow2btrQCSD2lctK8wo9qcr3BrecDBjAuXe3cvQdr12+E1+uFx+PBkkULUVM1Glt3tGHpopMVrv772iqce/YyW/pB/N3TSx579u3HmnUbIHq9EL1eTJ40CQvmzy1YcvXa9Thp7mwEcxZmtVwR+sZUXRQaT81jIM6SrsgjHTvWhdfeeAfvu3IFrrv2KtTW1mD1mvWIx+MYGAyjszO1hlB3T2/e8ibxeBwHDx9FLL1uVv/AIMKRCA4fPVawMbYsXbFo5ykmDy1P7YcOY9OWVlx75WV439WXY1vbLnQc68wuKifLMvoHUp87u07gSEfqPEqShEg0iqMdx1LLhI909qFTsL9/ALOam/Deqy7HJReejxf+8wpCwSCaZ8xALB5HNBrDkaPHEEu/IfRoxzEAwGB4EDFGr0/Nl67Y/P55S1d9/QNonj4dV19xGVZc+h5sa2vLTqI80d2DE91DCyjG4nF0dh1HV9dxSFJC13cR5HIiMJkHwpt9bGrZiqWLFmaXWV90UupteLv37sO/X/ovZs9sRk11NfYdaEdV1Wis37QF5511Bh5+/EnMm9WMV1a+jqsvvxRPPfcCqkZXAUgi4Pfj/HPOIq4D8XG4WLpq3bYNixbOhze93MP7r74cAPDAQ4/iYx96P/a3H8T+A4cQiUTg9/sQjcYgil40Tp2Cl159DfPnzsbGza345Ic/qGCHmkFV9xAVs2Kma0zmx7pVJBqFVxTR2z+Ad9asw4T6cdiydTumT5uCF15+BR+7PjXbu739ENZs2ITLL76QKKYR2CJdqYK+dNXT14sjRzoQiUQQHozA7/Nh9dp1CIdTa7SVl5Vh+rSp+M8rr2L6tEbs2rMPZ51xmvVaFgH7AHISCC32Qef2kg35isfiKE8vaf3qqrfQfugwABmnL12Mmc1NOO/sZbj/gb+iaUYjZDmJLa3bMXni+FSPeXAQXq8X27a3IZFI4oLlyyAIAh59/OkCNXMW+Aycy0gkkhBVXqk5fdpU7N1/AFtat2P5macjnkjgQPtBHDrSgRNdx9E4dQpmTGvEqUsWoaOjEwODgxg9apRKDNNVM2hmY/+QkIyuWbcBbbt2o6ysDJdfnD+BcM6sZiyYPxe79uyDLMvo6enD408/h5tu+Bg8Xv2FEE2Bt3TFXo0FAHR2dkEQPGjZuhXvvfIKBIIBbG7dhjkzU4+0b27dCgjAkkULMW3qFBw9eox+xQqCwqgto+QBpCUsysNCVIobISrTp03BptZtAIDlZ56O91+1ArFoit4HfH7IAHyiiDkzmzF/zmwsP/sMCB4P6seMxfw5s7F08UJMnpxa6VQUxdQyEQINGaV42AcATJk0Cbv37c9uv7JyFXbt2YuF8+di05ZWRKJRVFZW4OnnXkR5RTmWnrwg+5InnygCcuqdFdr5bmRLV7lYsmgh3nvV5bj0ovMVa7xlGKBHECDLMoLBAC46bzlef/NtszXThHOkKzaxpzc24qzTT8UlF16AV19fBQAI+P2Y1dyMWc1NOGXxyfCLIuLpd6Ukk4Xlq5EwcJ4LdR3BJQPnGTRNn4b2Q0fw+wf/horyMvT3D2DZ6UvzvJ257FS8+MpKlIVCqKyswMJ5s7Fuwya8vXodjnQcw/uuGnq9KpMrxCh58JzzMXvmDOzasxcPP/YERFFEMBDAtKlTIAgC+gYGsGBeagAyEPBj1+49kOIJSAlSTZ7FTWfSu+VTSlPg0iktZxq8Gdi6fQcOHT6M8Q0NljwXjGcL6EtXwzFl0kS0btuBlq3bsGjBfKxc9SYEQcDECQ2YO3sm/v2fV3Dw0CEcPtphrZZFIl1lIAwOn0hoUrrStTBwds3mmmQyCUmS8l45Kw//PpGA3zeUN2OxKHw+/9AS8GTKg/HKMUggzAbOdbqEcUmCIMsQ0+9GkCQJ/3z6eVx9+SXZsY1YLEb06t9CBiaK6JjxYB9y9i12eeM8KgVpJRBWTXsxsQ+jzVoikYCM1Gq7GUiJRHa5d0MxDBtpGzpFusqAMIHwSB4pQ5pExdQloJJA+EhXTplxvnLVWxhfPw5NM6aZvH1MSleG8gEf6UqS4oimX7MbCIaGkoj2LWEC7JJHJvl58+rNjn3oyaZ2JA8zsXmwD8NngnsCMXmmaUpXtBKIfclDpYSsutcSmLAPE8mDyHqEsQ9FAmGUPKz7yockSYhFU08f+QNBeLMPTNjFPhgmD2tfGremQB2cxj6A3DEQ879+aqDJPmiBVvKgCR5zPqj5YcU+DIEP+wDSslUwNPSZ4b1a/NIVQ1CMx6PqvE8PKSzPA6HJPmiBJvuwFJmRdEULVqUryjUgj2o9HxgyJvMzZKU9x4Uu+6CNVL1TM6xT7MPOu7YkXZkGJ/YBZBIICxTgBbEAACAASURBVOmKGHSlKwtV4BLKKnjN+aBizfFaaZvZeL4YklFWR+VlzJoAPn0V8y6dlzSdKF1lUOC9mBZPpIHiNJMHhUtAp4Sr2QftAGQGbpau6BXUcSiPBOnKHbofffZBvThzeMxnLLNfmjK04I2HdKXtk2qv0yFPXZm3tlaKt3RF04GTpSvNeLagJF2ZBmf2AVmTgfCj/cUhXbE/X6X3fBj1w7Ah0rNwRwda6bcIpCt3wn3SVaaYSgIx/bMhLW7clKN0ZRzFJF3x6AUVuXRF3Rcn6UpjixkYSVfuZB/Ui3OD4aewil26olUzJ0pX+U51dxgrzhIspCvLILuBnC5dZScOqiySSRMWu6WUYrCLbd6dO6WrDETNbxjDVumKWiiqrYV6hNKcD4OwkX24TLqSJAnRaOr9LIFAEF6RzUq+tktXFOPZoGk4C8MqV+ApLN2yBr40ZWjBmzn2YSnySJeujNWAPCoL9mE5edC00inN7Way864dqdKVs9hHIiEhQbz4aQqFV3sD6bekkI35YnFPM5auaKI058OomY3niyEZZXVUXlFEQE5PHHQx+3CMdEUhNo/8o5U8YtHUm1n9AQ1JUyWe+kpvxmtE35TAkMIloFPC1eyDdgAyg5J0ReBQZnc/yen/UosmsolCljzcofvRZx/Ui9sCopGzknRF5pNqr7M054O+d8untCRdOS12SboyWky9oNcrwh8Y+kwaj/26BTnRi0O6Yn++SnM+jPph2BDpWbijA630y/gW4yFduRPOkq5yofkkXoFiuoPodNiHM6Ur4ygm6YpHL6jIpSvqvjhJVxpbzMBIunIn+6Be3FYUTCDFLl0ZrVk8Hkc8HrfspxBKcz6omlEC2Q3kGumKN/tgUAHzHigfvMulK6vx2M4eIquDCUPrMJ48YoiEw9ltn+ijWyHQTR60PNHs5RUV+3C9dMUmiu3SFcV4RZDLrYGgcpoMpNjZh6XII126MlYD8qgs2Ifl5EHTSqc0t6Rk5107UqUrF7IPAqgyEDrhZGO+WBwjJekKAHy+IcbhdPZRIAoda47XStvMxvNFVbrKd8L0qHhLVzzUWA4lrcNU1zcPCZNLzrCSrjIwLmEZqA/N5GH9Elgv4fP5XM4+aAcgMyhJV2QOi1+6cofuR599WCtONMnPJigkrJJ0ReaTpvvSnA8G3i2f0uKQrlTj2YKSdGUavKUrA8UYpLJikq7Y/+BKcz6M+mHYEOlZuKMDrfRbBNKVO0FBN5EJJvmpFmOfPIBhCYQO+3CmdGUc2kK3E38fNNmHfgAyg6KSrqj7GmIfTJOHxhYzMJKueLOP7JiDSHfBcrPFnSRbZSAjJ4EUu3RFq2ZOlK7yneruMFacJVhIV5ZBdgO5RrrizT4YVMC8B3MlE5KEWCw95oCcJFKSrhSmhpZzp1oHjq2CZemKRTtfmvNhEDayD9dLV2yi2C5dUYxXBLncGkxWTtQtWwTsw1LkkS5dGasBeVQW7MNy8qBppVOaW1Ky8651n3QFpBiHP+ezQXdGjam6YDnnYyjGEEQ64WSFY+Ia0AJj6Yom7JrzIUmpZVhElXks5n+oJmA4edjYP2RBRnkoWLylKx5qLIeSGSjGPizG5pF/eA2c56LwWTKhidEwpHAJ6JRwNfvIhyTFEQlHAADBkHoSKRyAzKAkXZE5dLN0pR6UaCfDeAxdWYznxLbDLIYfi/YYyIiTrrR90nRv95yPRCIBScp/baWatSTFs4yFoAbk4Cxd0XTgdOlKNZ4tnt0pXVl0Z9SYqgueA+e5sDiIXkzSFQft0MY5H6Log+hLvX1OikvZ5KCVPCKDEUTCEZ0kkg9av22a/XTTjZ07OtBKv0UgXbkTI0u6ykA9gbhQutJaap0MxSRdaddYFEWy58lHunRF3dcQ+2CaPDS2mIGRdOVO9kG9uKOgdSzK1sSF0lU8Hs9bal300Vns0InSVb5T3R15EEUfgqGhz5o3xTA7KmAhXVkGGftwjXTFm30wqIB5D5QPviRdEZjK1pYysVW6ohaKamuhHsFBcz4yCUGvl6edOIqcfbheumITxXbpimK8Isjl1kClciknoso+XjXQ8UbGPoD8pdaNsY/ila4KPbJLqQYae4iKWTHTNSbzQ9NKpzS3pGTnXTtSpSsXsg9DMQrDBAORiRwT18AMVHz6fNqSjJ2wY86H3iO75n+olqtGYGZj/5AFGeWhYPGWrniosRxKWoeprq8F49xi7KUrEicelX306kBgSOES0CnhavZBOwCZQUm6InPoZulKPSjRTobxGLqyGM+JbYdZkByLSGxpzNCCN3LpikVFaLq3a85HoUFwczVi29vhqxgUh3SlGs8WzyXpyjQczD60TfO/MSBhOVO6MheKg3Zo83s+WC9XQuu3TbOfbrqxc0cHWum3CKQrd6IkXWXgcbt0ZRzFJF3x6AUVuXRF3dcQ+2CaPDS2mIGRdOVO9kG9uKNg5FgIGYhzpStaNXOidJXvVHeHseIswUK6sgyyG8jJ0pWU+5Ij3uzDhAU7D5QPviRdEZiqf0MsYdkqXVELRbW1UI/goDkfun5GOvtwkXQlSRJi0QhkAAE5mF4tls0B2C5dUYxng6bhLDCSrjIgWAuLPvtQLjtijn0Yj6y+6cQbgLl0ZawG5FFZsA/LyYOmlU5pbknJzrt2pEpXLmQfhmIYhw4DkY05JjBMLTsymN4qy5sEaMSnIxt9m97zYcqaRVUNJw8bzxcLMsowh4iiCCAIyHA9+3CMdEUhNo/847SB81zoSlg0kweFS0CnhKvZB+0AZAYl6YrMIav7SQZyFsLkdNeqhnGH7keffVAv7iiYPZYCCYS+dAVklh0pS38mIkB0wSh52P2eD11fjEvxlq5oOnC6dKUazxbPJenKNBzMPrRN9Z1otOD0patcDMlWxruXPPiK4Qg2z/lQA03pitZvm2Y/3XRj544OtNIv41uMh3TlTpSkq0LQHETPFNd9zwZH6co4ikm64tELKnLpirqvIfbBNHlobDEDI+nKneyDenFHweqxqDCQIZfxeBxhIwPeKjCVPBh3Hp0oXeU71d1hrDhLsJCuLIPsBnKNdMWbfTCogHkPlA++JF0RmJI7UWUgrKQrK7AsXbFo50tzPgzCRvbheumKTRTbpSuK8Yogl1sDR+kqYyoq9uQgf8DbXvZhKfJIl66M1YA8Kgv2YTl5DFm9Kol4Oqa8b38YDMMnGKmURgxuScnOu3akSlcuZB+GYtBBTgKRVR1rJg4Wx8hYuqIJUvYhpcePzL1ml5J0xfFaaZvxT4StCS8ejPoVVt8NRWD57TE8FCze0hUPNZZDSesw1fW1YJxbjL10RcVJ2lRU2UclDoVLQKeEjexDiscRjqTe1R6CehIpzD4oYKRLV9TBPiU6R7pyh+5Hn31QL+4oWD6WHAceSi61/OvuJf3aakVoui/N+WDgneZdzQw8aIdKPFtQkq5Mw8HsQ9vUXOzssp402YdhUJOuOGiHBpKH6PMhlPOZFWhKV7R+2zT76foe+GuffNgHwxgFd4xUlKQro6aioeIcpSvjcI50lQutxEGTfegHIDMYKdKVJEmA6DVYaoh9ME0eGlvMwEi6cif7oF7cUWBB8glW47XkX3Ov3te0LpwTpat8p7o7jBVnCRbSlWXwYB8cpSve7INBBcx7oHzwJemKwNTacXtsla6ohdJmH7RQmvNhFDayD52CqZVtmbi25lfO22ITo+AOxqAYrwhyuTXYLF1lYP6XROTfHPuwFNkh0pUWmEtXxmqg2LPnMT+6typvC09AxrzPReANKMsnY0DLPSFIA7mTK1J2DefFMW6ZxlI4lpMHvfMVl4HbwyG0J5WkfKIniTuDg/BbmjuiDTXpKrC9E2Vv7lfYDpwzFbFpNbo+K5/eDrFzIG9fYlQQPdfOIa6JGbhTunIh+zAUgx3IEgiLGvBQHihhJL3nY/x5cRx41o94v7K13PU3P5o/HlXs3/1oAB1vKW+l8klJjFlaYB01S6B3A8kAbguH8EhMOWek1iPjh6Ew/ALje3OY8/ik0fDt7YYgJfP2J4OibgLxnoig7J12YNh923/+NM14NOAY6YpCbB75x60D57nQHwMhiEPhEtAp4Wr2QTsAmcHwPYFaGbNujKiWbn/Oj57t+YPPPTu82P+MsuEVfMDcz4XhUX6lW1dW0pUW7owEVZPHKEHGo+X9aPIkuEtXyTIfonPGKuwD2zrhGSyclIMbDimSBwQB4UXjh4cZXhM24C1dWYznxLbDLCwfi44Dy4Po9klX2j5puh+Jcz7GniahYbmykZJlYNv9QSSl1HYyJqDlniDkpMIUTR+NoGJKwmpVNEBP4PprzI+fRQKK/SHIeKh8ACd5NI6BOpS1DZ8yQbFPkJIIbDla0FNwwxHFvujMWiSqgsSxjaIkXRktxp59aJvSayELJxBHS1cctMMR/J6PmZ+Komy8MjP07/dg35Op3nrbgwGEDytvodqFEia+J2a8Qjp1Kmhh4vhfjou4PRxS7PcLwB/LB3GaKJl1TYR89qFErLEa0rhyxf7Q+sOaZXz7uiF2Dir2Dy6ZkBO0hJEsXSUSEhIJiUo87QTCUboyjmKSrnj0gvSlq+HwBmXMuTkCQWW6xN5/BtD+bz/aX1TOcfFXyZhzcxjQGnBmIV2Z8LUp4cWnBssgDTP0Avh12QDO98UBmXHy0NjKRXiJkoX49veoJgkACK07pNiXrPQjOrOOmXTlTvZBvbijoHUsiYSEeDSGeDRWOIkQtv+mJSya0hWtC+dE6Srfqe4OY8VZQgZGNyXQ+F7loHkyDmz/Q0BZIQGYfVMYvtF8ml2t3XrRDyUFfHSgDANyfpYTANxZNogr08mDOQhihE8eD9mn/JmqyVSClESwpUOxf3DJRMCjltEZJg+GJa27K0lXtKCeQDi2VJalKxbtfGnORxZTr42hai7ZOMCkS2OoXWSuV2P6PJkoeN1AOQ6pPK779WAEH/EPSW98pKvCUeSQiOi8cYr9agPlgZYOCOFh518QEF7SwL97TTGeQ3K5faAkXQGA1yvCF/DDF/DD6y34RnOiKpliIDTZh6XII126MlYD8qg5RoIAzL0lDF954ZLlk5KYfr3601t6gcnOBD2rvQn12z47a4LhpSGVrnIxqDKY7j0RgX9vd96+0HqlfBVtqkGiSjnOM3KlKxeyD0Mx9OH1itrJw2AM5S+JxTEylq5oYiTN+SD1GayVMesz2snBo/fILotKqey2ejp+HQlgfzq5ML0LDDqPT66CNK5CsT+4bmgw3dMbhX/XCYVNeMkENizdhpLWYarra8E4txh76YqKE4Px8hOIAepiKSqNEq5mH7QDkBlYqUbtogR8leoexJAM/2iVZ3kJAvOUrvQQhYBvR0KOkK6GI7xUyUKCLUchxFPnPbT+MJDM95ms8CMys06rJmzAW7qyGM+JbYdZWD4WE+2/IQnLPulK2ydN9yNxzgdpsbYHAoj3qT9aFesVsPXXIfXyPO5qk2GqVVaCezruw5sJaiv8aMB4bcMnN0D25z8SJ0QTCOzoBAAENykH1cOLJwDe4T/xknRlGg5mH9qmbFPk0N3laOmKg3Y4gud86Bl0bRBx8OXC7zPp2iDi4IvGNCz9w2CnfS72JvBGZR8meJTM6euDIdCePpjPPkyUD4qIzFcOpgdaOuDtHIR4pD//C0HA4JLx5gMWFUrSFQ1TNRNiwZeWdGUcxSRd8egF0ZWuYr0CWn8dJHLS9ucg+g/k9HhZSFcUfM3zJvC3igHUCTJuDyrHdlqSXvxVZWkTs5ALbBlBeOlExb7AtmMIbVSyj9i0aiSqhw+ej1T2Qb24o2CHdJUBkYRFU7qideGcKF3lO9XdYaw4SxQItu03QcS6ldJVsE7Zc0/Gga33hLJLnTCplHZ/ghgPVwyiSpAByPiAP4a5KsuV/CgSQo9McfldChc0PmkUpIbKvH1CNIGyVfsUtoOKZMMweTAsad1dSbpiCQ/PlsqydMWinS/N+dDEwRd9OLZWOR5QMTWBJT8eQKBWmUT6dnux9+8qkwxp1InSCR4tDDnyAvhuKKyw6ZIF3BXVWjuKHPnSlfUDGFQZTBdi+QkwWeZHdLba4DkjUPxd2qBpOAsuka4y0GUgNNmHMZSkKws1II+qYTR4xIO2h5SLDApeYM7/RuAfJWPWp9Uf7d33ZADdLeoD0TSHxK2dVTn750xRwoWicvHI38cC2J4w+upbRQTVLbOInNwAOVC4TuHF4yHnDZ6PVOnKhezDUAz20ItB9ZW2hSI6stEvzflQ350AWu8OIhFWSjhT3xtFRWOqx1u7SMK4s9RX7W29J4j4gBkJiJ10peVTBvDNUAS+YdWVZOAbEbVJeMZj0ILs9yJyUr22gQDqg+eOka4oxOaRf4pp4FwPBRMIhUtAp4Sr2QftAGQGVqqx5/EAetqUvdyKKQlMuSp/bazmT0Tgr1JGi3R50PZAvgRkt3Sl5jDzqcmTwId8ynW/VkoiXo4XfgJNMwJF6SoXg6cqB9MziE2rQaK2bHhN2IC3dGUxnhPbDrOwfCwWpasMNBOIfdKVtk8191I8Dilu/K13pTkf6rv7dnmx7wmVF0R5gdn/G4FnmDLlq5TR/El1KevISh863jDS+PKQrrSdfCkYwShB+cXXIiHEnZP9IDVUIj5hlOp3g4tzx0hK0pVpOJh9aJvyT5H0JCxq0hV5CSkeRzgSRjgSNpRESnM+1HcnogK23B1UfYpq6jVRVE5Tnx0x9vQ4xp6mfv63/T6ISCfJsxr8tc/hrmsFGbcGlMlwT9KDP8aU40EF/TK+xdRmpidDPkTnjmEb2PEoSVc0TEm9Cf0DYcJ+szn2YakPTsA+wpHUEzShYAiij6y36xr2wUq6IqyabNzYQjgeYx9Dgx6s2vd81YpdFtGXTUvsw1RxUwUyxVzAPigmDwBQPCpjX/Iw7B6iz4dQzmciX6U5HzTNKIFv8mAOxjFMszmqMdjFNu+uJF3xBrNFfyxLV4QOSBMHQDd5sE6OzNiHIfBiHzQL2uc6n3SwiWKxr8KgAo5wZWsM03CxdJWx9uRvmnDJ4iToSFd2g6Z0RaEG5FFZsA9W0pUpK53S3JKSnXdtSboyDd7sw1AM9jATw9ogOmPpiiZKcz6Mmtl4vqhKV/lOmB4Vb+mKhxrLoaR1mOr6mjJOJKS8d4kX08C5mdhi/qb1qDSlK0cmIs0NFgHIDErSFZnD4peu3KH70Wcf1IurIpGQEIum5gr5A7D0Vj8jsHwsDKSrDDzahXlIV9o+abp3zVNXjErxlq5oOnC6dKUazxaUpCvT4C1dUSEOzuhem0uh1KQrDtphac6HQT8MGyI9C3d0oJV+i0C6cif4SVdAinH409OBPF6Ta6Q5ULqy0vUVaUlXxlFM0hWPXlCRS1fUfQ2xD6bJQ2OLGRhJV25kH5mxiFwpifVVyMRyxcA59eShhAoDMSdd0TqdTpSu8p3q7jBWnCVYSFeWQXYDuUa64s0+GFTAvAfKB28oecStj0eUpCuDUMamMgpkWbpi0c6X5nwYhI3sw0XSlSSle72imOOcXpREjn/bpSuK8Yogl1tDkUlXGYgkRiYjkjkZ6dKVsRqQR2XBPiwnD5pWOqUZXBpJkhCLRiADCCCY7vXSTR7RaGotrgCC8Ih6/buRKV0Bct54hCvYh6EY7EErBvmZZyxd0URpzodRMxvPF0MyyvSoeEtXPNRYDiWtYyi26bEPB0tXVJxQvzzaDkUSI+NuCUu4mn3QDkBmUJKuCBzKbC6XKIoAgoCclrAoR/GKIgIIQkbGfxqqYdyh+9FnH9SLOwqWj4WTdJWBSOSSceNJtddZmvNB3zuPu9pyGHbSVS6Gxj7YBFId+1Bg5EpXluFg9qFt6twUqb+UCTXpioN2WJrzYdAPw4ZIz8IdHWil3yKQrtwJ9RNRkq6MmVLt+sqAxxb929XSFY9eUJFLV9R9sZWuciKobjEDI+nKneyDenFHwXnSFZmzwgyEcefRidJVvlPdHcaKswQL6coyyG4gN0hXPGLYKl1xiG3eXUm64g+y2IZX47UsXbFo50tzPgzCRvbheumKTRTbpSuK8Yogl1vDCJCuMtBOICxOwkiXrozVgDwqC/ZhOXmkrCRJyk6+s1wnrdLckpLze4SmPDhaunIh+zAUgz1YSFcZqM8DYSxd0URpzodRM37nS5IkRNPvrEcwBHHYhC/njKHY6ZxPX8Ux0hWF2DzyTzENnDOLDQMSFk3pypGJSHODRQAyg5J0ReBQJnOtx4Q0IzhCunKH7keffVAv7ihYPhYbpasMlAyEceNJtddZmvNB3zvFu1oURSAYSn2myj6MSVeZJUhSCKYnBJqIZwtK0pVpOJh9aJu6K0US/aotsw8GKM35MOqHYUNUwELMW3SQPli5zmcfDGMU3DFSUZKuaJiyZh8ApdV4C0ZytXTFoxdU5NIVdV/GpCsgZwmS7GeiCKpbzMBIunIn+6Be3FFwnnRl3pnuamS0KuJE6Srfqe4OY8VZgoV0ZRlkNxBP6SoXhmUr3uyDQQXMe6B88CXpisDUfTKpDJ1BdMvSFYt2vjTnwyBsZB+ul67YRLFduqIYj0fVHc0+Rqh0ldntMRGRLNJIl66M1YA8Kgv2YTl50LTSKc0tKbmvR0jkwdHSlQvZh6EY7MFLusrAw1q6oonSnA+jZjaeLxZklH0O4S9d8VBjOZS0DvXYPPIPC+kqkZCy72w37cSCKUuHuaVUhWGa0pUjE5HmBosAZAYl6YrMYfFLV+7Q/eizD+rFbUMiISne1275WBwmXWVgeC0sXTBKHqU5Hwy887irLYfhQTtU4tmCknRlGg5iH+Smbk2RQ1AwEMvsgwFKcz6M+mHYEOlZuKMDrfRbBNKVO1Fc0hUAxfvaLR+hQ9kHYHkeSDFJVzx6QUUuXVH3NcQ+mCYPjS1mYCRduZN9UC/uCGTe1+486YquszwJi1ZFnChd5TvV3WGsOEuwkK4sg6yL4hrpijf7YFAB8x4oH3xJuiIwdZ9MqlXKo2dA7JJFO1+a82EQNrIP10tXbKLYLl1RjFcEudwaqFSuOKSrDEwOopekKws1II/Kgn1YTh40rXRKc0tK7usREnlwtHTlQvZhKAZ72CldZeChXhFKKM35MGpm4/liQUZ5KFi8pSseaiyHktahHptH/immxRKZxTZQykNTunJkItLcYBGAzKAkXZE5dLN0pR6UaCfDeAxdWYznxLbDLCwfiwukqwyszQNhlDxKcz4YeOdxV1sOw4N2qMSzxXNJujINB7MPbdNiSpFDMJhAOGiHpTkfBv0wbIj0LNzRgVb6LQLpyp0oSVc0TJ3CPgBDCaSYpCsevaAil66o+xpiH0yTh8YWMzCSrtzJPqgXdxScJ12xd2Z5KRMnSlf5TnV3GCvOEiykK8sg66K4RrrizT4YVMC8B8oHX5KuCEztTJHshXfCBEK1tVCPUJrzYRA2sg/XS1dsotguXVGMVwS53BpK0hURCBJISbqyUAPyqCzYh+XkQdNKpzS3pOS+HiGRB0dLVy5kH4ZisIfTpKsM6K/GawKlOR9GzWw8XyzIKA8Fi7d0xUON5VDSOtRj88g/xTRwziy2xVI6CaSY2AftAGQGJemKzKGbpSv1oEQ7GcZj6MpiPCe2HWZh+VhcKl1lQM5AGCWP0pwPBt553NWWw/CgHSrxbPFckq5Mw8HsQ9u0mFJkYRRIIBy0w9KcD4N+GDZEehbu6EAr/RaBdOVOlKQrGqZOZh+AZgIpJumKRy+oyKUr6r6G2AfT5KGxxQyMpCt3sg/qxR0F50lXPJ0NwdAguhOlq3ynujuMFWcJFtKVZZB1UVwjXfFmHwwqYN4D5YMvSVcEpnamSK7CexYqCYRqa6GK0pwPo7CRfbheumITxXbpimK8Isjl1lCSrkxjWAIpSVcWakAelQX7sJw8aFrplOaWlNzXIyTy4GjpyoXsw1AM9nCDdJUB93kgpTkfRs1sPF8syCgPBYu3dMVDjeVQ0jrUY/PIP8U0cM4stuVSSi+e3A2tCO5jH7QDkBmUpCsyh26WrtSDEu1kGI+hK4vxnNh2mIXlYyki6SrjRZ2BMEoepTkfDLzzuKsth+FBO1Ti2eK5JF2ZhoPZh7ZpMaVI40gnEA7aYWnOh0E/DBsiPQt3dKCVfotAunInStIVDVO3sQ8A8BSXdMWjF1Tk0hV1X0Psg2ny0NhiBkbSlTvZB/XijoLzpCuezgo71xxEd6J0le9Ud4ex4izBQrqyDLIuimukK97sg0EFzHugfPAl6YrA1M4UyVV4L4j8BMKinS/N+TAIG9mH66UrNlFsl64oxiuCXG4NJenKApRePGrfOfEGYC5dGasBeVQW7MNy8qBppVOaW1JyX4+QyIOjpSsXsg9DMdjDPdKVejym80BKcz6Mmtl4vqhKV/lOOEqy7N3zUGM5lLQO9dg88k8xDZybjZ1IJJBIJDhWQ92LOPw797EP2gHIDErSFZnD4peu3KH70Wcf1Is7CpaPhaF0lUgkEI9FUxv+ALxeL3fpKrPLwyp5lOZ8MPDO4662HIYH7VCJZwtK0pVpOJh9aJsWU4q0gJzTIDLxX5rzYdAPw4ZIz8IdHWil3yKQrtyJknRFw9RK19fr9QL+wNBn3uwjB9kE4sTfB032oR+AzKCopCvqvobYB9PkobHFDIykK3eyD+rFHQXnSVfq8Hq99JxpQlu6ysBDuw6lOR9UzSiBrIviGumKN/tgUAHzHigffEm6IjB1n0zKpMYq7QXVp7BKcz6Mwkb24Xrpik0U26UrivGKIJdbQ5FJV6Rf85CuMvA48QZgLl0ZqwF5VBbsw3LyoGmlU5pbUnJfj5DIg6OlKxeyD0Mx2INqDJs7NplNagykNOfDqJmN54uqdJXvhLcky9Q9DzWWQ0nrUI/NI/8U08A5s9iWSxnzkvst9xdK6aEw+6AdgMygJF2ROSx+QHLaswAAFz5JREFU6coduh999kG9uKNg+ViKXboq4JhKAinN+WDgncddbTkMD9qhEs8WlKQr03Aw+9A2LaYUaQE6aoXlBFKa82HUD8OGSM/CHR1opd8ikK7ciZJ0RcM0Y5JISEgkJGsOebMPHTCZSGgGNNmHfgAyg6KSrnIgSamb2CtaufxD7INp8tDYYgZG0pU72Qf14o4CT+kqkZAQj8VSG37A6zXx2+M9wKjDPgCLDKQ054OqGSUU7qJIkoRoJIxIJJxNJKZj8Dgw3uyDQQXMe6B88CXpisDUfTIpkxoTJA/AAgMpzfkwChvZh+ulKzZRbJeuKMYrglxuDQ6WroA04/DnfDbq0GHSVQa2S1jMpStjNSCPyoJ9WE4e+laiKEIOhrKfjYM9+7BFulLFSJWuXMg+DMVgD7UYpmQrLWcsQcg+AJMJpDTnw6iZjedL5WYwlziUPnlLskzd81BjOZS0DvXYPPJPMQ2cM4ttuZQxL3oxbJ0HUph90A5AZlCSrsgcFr905Q7djz77oF7cUbB8LAalK8vWvKUrg44NJ5DSnA8G3nnc1ZbD8KAdKvFsQUm6Mg0Hsw9t02JKkRZgQLrKwFACKc35MOqHYUOkZ+GODrTSbxFIVzyQkCQkTD9Fp4aSdEXD1NXswwRsGUSnyT70A5AZFJV0Rd3XEPtgmjw0tpiBkXTFmn0kJAnR9CtN/Sgwn6ckXWXhPOmKpzMC5ybYB2CAgZTmfFA1owSyLoprpCve7INBBcx7oHzwJemKwNR9MimTGltoL4gYSGnOh1Hoe5QkCZC1n4gyXSfXS1dsotguXVGM5xHFzJQCi6sJaMPR7KMkXVkA3SvLVcJiLl0ZqwF5VMrsQ5IkRMPh1EYwpEgiZH5oWumU5paU3NcjJPJAa3Atx7Jg4ih29mEoBnu4R7rSj2c0vK6EVZrzYdTMxvNFVbrKd1LIlyRJFpZF0XFOATz6Ko6RrijE5pF/imngnFlsy6WMeTETgxsDKcw+aAcgM7BDugIA0SsCGrPBnSNdkaVESZIQi0bSW0FDkxSdI125Q/ejyZYZFXcULB9LsUtXFBwX/LWX5nww8J42Nj8bvDikK9V4nJDIW43YXdIVJXdGjam6GLkD5w4CJbVCsxUrzfkw6odhQ6RnYWMHOpUIgzmfDfi1QbpKSBKiacYUQBBe0cu2Eo5ESbqiYepq9kEJzCUsmuxDPwCZgV3SVSEzmnWixT5I/RhlU3KBLWawKF0lNN6h4k72Qb24o+A86YqnMwLnlNgHoJFARtqcD0mKAwBE0WcoGN8fHVkXxTXSFW/2kYZXFBFAEIBM/AiskrWIBWOYrx0PdyXpij+4Cu+GnFqNofgFjbQ5H5IURyScahyCoZwkYr12xGamz5ON0pUlv3LeFpsYBXbQGvsgr4AjXNkawzRK0pUFsL+yzCQs5tKVsRqQR2XBPiwnD5pWOqW5tavu6REOsRbosw9HS1cuZB+GYrCHe6Qr/Xg0wuclkJE450MUfZknaiF6ydiHrPKJHXhIV/lOeEuyTN1TipcrdzlGuqIQm0f+KaaBc2axLZcy5oXWoTJhIIXZB+0AZAaFihgd+zBk7Arpin1KdIJ0xTI2bdf02Qf14o6C5WMpdumK0cXOzkQvzflg4J3HXW05DA/aoRLPFliPXZKujBZjzz60TYspRVoAC7UiDQ/AS7oyBprSFa3fNs1+ur4Hpl0Urq7z2QfDGAV3jFSUpCsapq5mHwxBVcKiyT70A5AZ0D+dNkpX1H0NsQ+myUNjixkYSVfuZB/UixuPp9NBFQTBvG/TJckdUD1fNGVOxXmVledSzrfNLWHlvGcgjrQ5H2aD8f3RkXVRXCNd8WYfDCpg3gPlg3eZdCXLcl5Dl/ms1ngJguAa6Uq73dRJllBvtElrrHYuNb3kbMqyrEgeha4FKagxEFqXjGYvr6jYh+ulKzZRbJeuaPYo6bniFiORSM/Q9yqbkkzyyEsimZ5wutHKa7yGVc5cw2Y8A+U2xMNj5nor3HgDeYeilmBkIDd/ZGIZSR5ZJqGRPPL2F+hwynI+WzGbRKgkEObSlbEakEdlwT4sJw+aVjqluSUl3q063djulK7Ys49EQkIsmn61bmAoiciQFclDlpOp79I+hew9KEAWhGyPmLQho8I+VBJIIU/ajffQ97k9e61YhZIUoN6Y557LZ576F44cOQwAmDR5Mi686GI89ujD6OvrAwAEgyFc/6GPZP1s29qCN95YNTwKAOB97/8gRldVacbVA+O1sChJVyzaH8PJw8b+IVXpKt8J06PiLV3xUGM5lLQOsgbRhAuCYsO6DrKMvz/yNyQTyWzDKooigqEgmmfOQlNzcyqZJAVgWBIZ3hDnNs6Wj1DrpyYX/sUPfS9j+7at2Lh+A05auBCzZs9WlP/3s8+gt7cXV1x9NYKBYOYo8hMNacJMJ4/uEyfwxqrX0NXZBUBG244dmDV7Dqqra/Dyf/4Dr1dEIBjA7DlzcPLJiyHLMtauXYu1776LeDyO6pqaVKKRgVBZCGecsQzl5eUQfampDEaTiOUEUph9UEBJuqIM9inROdKVO3Q/+uyDenFVeL0i/IGhz4qYspyiHHLq84SJE5FMJBCJRnG8qwtr330XoVAIEyZOhIB8VqJ6DIIAyIWe7aJ3lFqehpQ4Gclk+q+cTCeFfLvMv2RCRjKZKjhkkz4OmUxGyiSQDRvWoa+vD6GyMvh9PvT19mDNu6uxeMlSlJWVoaKiEl1dnWjZvBnNzbMAyNi6tRXV1TU4fuI4fD4fkskk6urGYHBwAJFY1MJTuLK1BEJTujJ3CKa7SfS9W753i0O6Uo1nC0rSlWkYcJGbOIYPnKcGboc+L166FF5vavn8DevXYVfbTrQfOICGhvHZxrPrWCf6+vtQXlGOutox2eX2jx49AtHrQ01dLQCgt7cX4fAgqqqq4ff7kUhI6OrqhN/vR1VVNQDg+PHj6O3pQXlFOWpqarOrRg/0DaB/oA/V1TXo6uxEIpnA+PET4PF40N/Xj67jnfD5/KgbMwY+39DqFLIs43hnF3r7elFbWws5nTggy0gmkxDSUtzwc5BMJnD40CFEo1HUjRmD8vJyyLKMjmMd8Hg8GDt2XPYM9nR3IxKNorq6BoFAIC92MpnEu6tXwyf6MBgeQELyIRAIoGXzZpx51lmY0tiInTvaUFk5Cm1tbejt6cGhw4fQ19uLsrIyBAJBTJo8BZ2dnQDSL7aThyTHDIywEK7vRNcCTemK1m+bZj9d3wOZdEUTfNiHMWgtma4ao+COkQrnSFfZ/XLuZzm7w+f1AZCRkBKQZRmRSARvvbEq27gBKS3/zLPPRk1NDTauX4+e7h5cfvXVEEURq99+C12dnZh30kmYNXs2Dh5ox9tvvYlZs2ejcv4orHlnNfbt25v1NWrUKJx97rkIBoLYtWsntra2YOzYcejoOAqv6MUVV16FPbv3YOOG9Vm24Pf7cebZZ6O2rg6yLGPN6tXYu2cPABmCx4OqqirIchLJpKzoxecmzzdXrUJXptH2+XDq6aejvmE8Nqxbh57uHlx48XtQVVUNQRDw+srXEImEseKKKyDL/qGzKwO7d+3EkcOH4BW98PsDiEajKK+oQGfnMWzfug0LFp6MrS0tCARr0dvTjV0727B37x4kEwmEB8Ooqa1BQ0MDNnk82frBAvsACN6JXri42obqDosByAyKSrqi7muIfTBNHhpbesgsmR6NRrKJxERQU7ENeXA0+6Be3GLwIUYCAG07tqNl8xasfvsdbN++DQAwdtxYyLKMjevXo/NYJyZNnozzL7wIJy1YiEg4jLfefAPxeAz148dDSkg4cugwYrEYujo7kUwmceTwESQSCbS3H0AymUR9QwN27dyJPXt2o76hAZesuAwLFi5ET083WjZtRjKZhJxMMYfjx7uwaPESnLxoMQYGBrB+3VoEy0K48OL34OxzlkNKSHj3nXeQSKQYxJ7du1BWUYYLLnoPzlm+HAN9/WmZSvnQQOrAU3/8gQAuuWwFFi9Zing8jnVr1kCSJEyePAWynMT+vfuQTCbReewYBgb6MXZcPQLBUNrB0BVcv24tIuEI4nEJ1dXVKCsrQzwehyRJaNmyCdOmTUNFZQXisSikRAItLVvQ2tqCUHk5ItEIZjTPhNcrwuMZavazOd1QIhk6PtMJZLivAjuMFWcJFtKVZZCxD9dIV4xjmGZzVGOwi23eHV/pKr9Y4YIZSaR1Swu2bWvFgQP74PF40DxzNqZMbUQymUT7gQPweDxYtHgJqqqqMKOpCXVjxqC/txddnV1oGD8esizj8OFD6DiaShqhUBm6OjsgxeM4cvgwysrKUF1djc6ODgAyamqq0dvdg4qKCngED44cPZJu4FON/qTJkzG1sRGTJ0/B0aNHIcsyaqtrER4YRCIpobKiEr29PYiGw+g8dgwAMGNaE0aNGoXq6hpMmjKZ4OTImDtvPkKhECZPmYLKykoMDAwg3D+ASZMnQRAEHDiwH8lkEgf274csy5gyZUpOPVP/BgcHsHnTRlRUViISCcPr9aK8vBy9vb0YPWo0du3ciWgkiuaZs9Dd3Y3ysjLs3NmGnu7u9LkKYfLkKQgFg/p1JkH6kpuSsGj9TGj28oqKfbheujIeRW3JdNUYBXfQg6qcRjFeEeRyfaQHvTM47/wLIHg98Ik+lIXKsuMbsVgMyWQSwVAw7+2WZWVlAIBIJILaMWNQXlmRknC8Hng8HsyaMwvr1qzBrl1tiEajmDRlMmRZRjgchiwDW1u3ZpOXx+NBUkoMVQ1AMKcxjabfCXTwYDsOHTqY3S+KIsKRFDOWZRn+gC/NMGQEAn6onWVBECAnh/b7/UNPOAUCQQC9iMQiqKmoRX19Aw4dOoju48fR3n4AouhD/fgGxSS/zZs2oqe7G6NGj0bAH0DH0aMp3z4f/MEAent7sGnTRsyfdxLWr1sHrygi3N8PKZFAPBrDhIkTUVdXh66uLsUlMvbgVb64bziBMJeujNWAPCoL9mE5edC00inNLSmZD0T6hkDSmpj1oPoGQkdLV05mH5m/AqpqqrMJIndGdjAYhD/gRzQSweDgYDZxnDhxAhAEVI4eDUEQMGH8ROzYvg379u5FdU0Nxo+fgPXCOmxr3QZBACZOSPXoy8rKIQjAKaeeivETJiCRSKC7uxujRo3Oq5PfH8g20MF0zOnTZ2D+ggUAgK6uTpSXlyMYDKG8ogKCIKC3ty9bpre3F5n5FJkBdMVsekFAT08PguNCkJNJ9Pf3AwAq0v6mNjbi0KGD2LJ5EwYGBjBt2nTVJ9rWrF4Nj9eL3p5exOMxJBKJ9PkHerpPIBgKYmtrK0499TRUVVUhHosjFo2ivKwckUgYM5qa4A8E4Pf7gUxd82c1FryOyEZDngxOcRCdknTFoqEznDxs7B9Sla7Y+eLrnE9fxTHSFYXYPPKPVvLImxQoCxA8AgRZgMeTYg6Q85/0kWUZTU3NaG1pwRuvv4apjY041nEMfb29GDt2LKrSE90mTJqIth3bEY/HMW5cPYKhEKqqq9F94gQCwRBqx9QBgoCp0xqxf/9ebN6yCUlZxpFDh7F/315MnDIZp512Rrqh98Dr8WbrMWnyZGzeuAF79uxGeWUl4vEYtmzahPKKClx08SWYOGkytra0YGfbDog+L6S4hPb2dgiCAI9HyE8gOedBgIC1767BzJkzcayrE+FIGOPqG9JjHMC4+nqEgiEcPXoUEARMnjIlv7wAtLcfwP79+1BeXonjxztx8uIlqK6pBuTU02kb1q9HQ8N4dHYew759+zBv3ny8/tpKVFVVIRqLo6y8HFOmNqKiogLHu7rSj0yn/xueSPQveh4MJZDC7IMCStIVZSh7DEwiWJCuiGMU3EE3tkJO4y1dWYxnu3SFnGU6BCHTTsHjSTe2w+Z5yAIw76T5AIC2HTuweeMmeDweTG1sxMLFi7ODvnV1YxAKlSESCWNcfT08Hg/q6xvQ092NCRMmwutNJYRx9fVYcPIitG7ZgnfffgcAMH7CRCxZcgo8Hg8EjyfVOHtSSU1GigWdceZZWPvuu9iwbh0AYHRVFU474wyIoojKykqcetrpWPPuarRuaUF5RTlmz56DbVu3QkgnRkFA6uQLQ4zE5/ehqbkJW7ZsRiKRwJi6MVhyyilD0prXi0lTpqBtx3ZUVFRizNixikS0Yf169PX1IZnsRlVVNZaecirGjhuLgD+A7u5u7GprQ0fHEQAC9u7bi1mz5+Ctt9/CiRPd8Ho9mDl7DqqqqlFZOSp9LgV0dh5D5ahRqTiCegLMh3r3Wuju7Td+T1vsDppjHyZ7WizYh46Jvgce7ENW+0Mdcv5/7GIY22E9BrFr50lXdrKPPBuNJ5MUS3nkPN4rJSSEw2EEgyF40nNGFLbp2HqLASaTSYQHw/D7/fD5fJprP2WOJONvYKAfHsGDYCikEj+JaCSCYCiU0+hmvWZ785l6Zgbs45KEeDyOYDCoWBJl/bq12L1zJ+bMnYe58+fn+U0mZTz+j7+j+8RxRKNR1NTU4LQzlmHSpMnwelLn55mnn8K+vXvg8XpxwYUXYXRVFZ5/9hn09/WlHlaYNQuz58zF+PETsGf3Tqx89VUMDgzA4/XgnOXnYdbsOYrzo4Ss2hHlnkBo/lBtSR46ZrSSh4HaFI5TYh/m4hC7HjLQm8dCN4E4O3lkbVUeawVyGMqwxjQ3mRQ6QkVDphlfTd5XJo/h/jW8qezLGQOBMjFm51sAuc8TQJZl7N69C0cOH8ah9nYIHg8uXbECoVAZPJ6UyJTLCI4ePYJketzDK4qoq6vLq05XVydi8RgAYNy4egBAx9GjkCFDgIDKykqUl1cAgoDw4GB6/CaFsWPHZpcyKXjcZhMIc/bBInkQG2ndksZ9knngyz6YJo/sB07sw+HJIxpLLSwY8AcUSYQH+zB8JjgkEAAFE0ju97l/tSNY/50WWgW38LIeyu+yx6HFrAAkVRdhlLF96zZs29qKUKgMc+bNSy3pkh6cyJeUZKVfjfZCfZXgwsul6DKP9B/V9GkogbBIHkRuRhb7oJU8rPvSiWI7+2CYPAx+aTmBUKAOTmMfZuJRSR6EppRar+zXag1xMqdBH74cfKHGvlACyf62CzI1dRhfcVcu2JboDqLTahq4Jg/D4MU+aBa0z7UzkgdjGIyXGngf+mzBlSnwPj2GYKByhQdxCRs/AlMD3vStNb6Woez9q605NXwsJ/+v9smj8UbBwtDvXhdMIIXlA3t+FjSlAFo9NjI/NK10SnNLSnY2W86QrnKhNvbBQ7oyDN7sw1AM9qAaw6Cz3OSg9RBAwcRAVa0ohMLSVQYm54Hwkq5MgJV0ZQk8pCt2vvg659NXMe/SeUmzGKQrak6oXx5zDklK6TOIwl6Y34kEATTXwirMPiigJF1RBlmPwXIER0hX7tD96LMP6sUdBcvHYsO4h/UYBpxzu9jk3WvVBEJTumKXv80X46sYFId0pRrPFjhPujJtWezSFRXiUEwp0gK4SVdDAUhiWF+Nt3AdDH5hwpdBnzSlK30PTLsoXF3nsw+GMQruGKkoSVc0TF3NPrjBWGxFAqHJPlQx0qUr6r44SVcaW8zASLqixT4SkqT53pKSdGUMzpOueDojcM6NfRhvS7QH0W2RrkyChXRlGWRdFCdKV1K6YRQZLWWuBtNsjmoMspJ5cz5gYhXhknRFYOqeXri1Usac8pCujCDvztcrK0nxVCGx0LR3uhpzUbEPF0hXkiQhll7KHIqlzNkcgO3SFcV4PKruaPZRkq4swBlJ00gtsglET7qSpDgi6ZeuBEP6ScQ4TCYPFuzDcvKgaaVTmts954ybm7oHE50arUmD9KUrF7IPQzHYwz3SlX48J0lXGRBwb0r5m8XRG04eNt6yLG4GBjkkJVuxWcpcDTzYBy3pKhfWX35lLjaP/FNMA+fMYlsuZcyL06SrDP4/Mf85Ivk8o88AAAAASUVORK5CYII=</v>
+      </c>
+      <c r="E512" t="str">
+        <v>24-08-2026 04:20:01 pm</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="str">
+        <v>6a8c21dc9f26e6fd288c73b9</v>
+      </c>
+      <c r="B513" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C513" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D513" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E513" t="str">
+        <v>24-08-2026 04:20:04 pm</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="str">
+        <v>6a8c21dd9f26e6fd288c73c2</v>
+      </c>
+      <c r="B514" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C514" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D514" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E514" t="str">
+        <v>24-08-2026 04:20:05 pm</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="str">
+        <v>6a8c21e19f26e6fd288c74b7</v>
+      </c>
+      <c r="B515" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C515" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D515" t="str">
+        <v>Started Playing game and Debited "10" and Balance "430"</v>
+      </c>
+      <c r="E515" t="str">
+        <v>24-08-2026 04:20:09 pm</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E344"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E515"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/live-history.xlsx
+++ b/live-history.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E515"/>
+  <dimension ref="A1:E645"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -9154,9 +9154,2219 @@
         <v>24-08-2026 04:20:09 pm</v>
       </c>
     </row>
+    <row r="516">
+      <c r="A516" t="str">
+        <v>6a8c21e29f26e6fd288c74bd</v>
+      </c>
+      <c r="B516" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C516" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D516" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E516" t="str">
+        <v>24-08-2026 04:20:10 pm</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="str">
+        <v>6a8c55dc97898c3b38e9233c</v>
+      </c>
+      <c r="B517" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C517" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D517" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E517" t="str">
+        <v>24-08-2026 08:01:56 pm</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="str">
+        <v>6a8c55dc97898c3b38e92342</v>
+      </c>
+      <c r="B518" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C518" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D518" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E518" t="str">
+        <v>24-08-2026 08:01:56 pm</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="str">
+        <v>6a8c55e297898c3b38e92438</v>
+      </c>
+      <c r="B519" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C519" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D519" t="str">
+        <v>Started Playing game and Debited "10" and Balance "420"</v>
+      </c>
+      <c r="E519" t="str">
+        <v>24-08-2026 08:02:02 pm</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="str">
+        <v>6a8c55e397898c3b38e9243e</v>
+      </c>
+      <c r="B520" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C520" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D520" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E520" t="str">
+        <v>24-08-2026 08:02:03 pm</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="str">
+        <v>6a8c5639efc2615742955af2</v>
+      </c>
+      <c r="B521" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C521" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D521" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E521" t="str">
+        <v>24-08-2026 08:03:29 pm</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="str">
+        <v>6a8c563aefc2615742955af9</v>
+      </c>
+      <c r="B522" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C522" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D522" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E522" t="str">
+        <v>24-08-2026 08:03:30 pm</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="str">
+        <v>6a8c5640efc2615742955bf0</v>
+      </c>
+      <c r="B523" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C523" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D523" t="str">
+        <v>Started Playing game and Debited "10" and Balance "410"</v>
+      </c>
+      <c r="E523" t="str">
+        <v>24-08-2026 08:03:36 pm</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="str">
+        <v>6a8c5640efc2615742955bf6</v>
+      </c>
+      <c r="B524" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C524" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D524" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E524" t="str">
+        <v>24-08-2026 08:03:36 pm</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="str">
+        <v>6a8c56c8efc2615742955c22</v>
+      </c>
+      <c r="B525" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C525" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D525" t="str">
+        <v>Answerd Correctly to Qst ID : 6a8c5642efc2615742955c00, Reward : 10, Qst No : 2 ,Question : How many letters are misaligned?</v>
+      </c>
+      <c r="E525" t="str">
+        <v>24-08-2026 08:05:52 pm</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="str">
+        <v>6a8c56cdefc2615742955c39</v>
+      </c>
+      <c r="B526" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C526" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D526" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6a8c56ccefc2615742955c31 , Question : How many colour names match their text colour out of 8?, Type : [Colours &amp; Name Match] </v>
+      </c>
+      <c r="E526" t="str">
+        <v>24-08-2026 08:05:57 pm</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="str">
+        <v>6a8c56daefc2615742955c51</v>
+      </c>
+      <c r="B527" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C527" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D527" t="str">
+        <v>💚💚 User won the competition by answering all 10 questions and received 200 rewards</v>
+      </c>
+      <c r="E527" t="str">
+        <v>24-08-2026 08:06:10 pm</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="str">
+        <v>6a8c56dbefc2615742955c67</v>
+      </c>
+      <c r="B528" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C528" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D528" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6a8c56dbefc2615742955c5f , Question : How many colour names match their text colour out of 8?, Type : [Colours &amp; Name Match] </v>
+      </c>
+      <c r="E528" t="str">
+        <v>24-08-2026 08:06:11 pm</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="str">
+        <v>6a8c5927c2fb496b6999be47</v>
+      </c>
+      <c r="B529" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C529" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D529" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E529" t="str">
+        <v>24-08-2026 08:15:59 pm</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="str">
+        <v>6a8c5928c2fb496b6999be4d</v>
+      </c>
+      <c r="B530" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C530" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D530" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E530" t="str">
+        <v>24-08-2026 08:16:00 pm</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="str">
+        <v>6a8c597cc2fb496b6999be60</v>
+      </c>
+      <c r="B531" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C531" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D531" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E531" t="str">
+        <v>24-08-2026 08:17:24 pm</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="str">
+        <v>6a8c597cc2fb496b6999be66</v>
+      </c>
+      <c r="B532" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C532" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D532" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E532" t="str">
+        <v>24-08-2026 08:17:24 pm</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="str">
+        <v>6a8c5983c2fb496b6999be79</v>
+      </c>
+      <c r="B533" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C533" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D533" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E533" t="str">
+        <v>24-08-2026 08:17:31 pm</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="str">
+        <v>6a8c5983c2fb496b6999be7f</v>
+      </c>
+      <c r="B534" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C534" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D534" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E534" t="str">
+        <v>24-08-2026 08:17:31 pm</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="str">
+        <v>6a8c5989c2fb496b6999be92</v>
+      </c>
+      <c r="B535" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C535" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D535" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E535" t="str">
+        <v>24-08-2026 08:17:37 pm</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="str">
+        <v>6a8c598ac2fb496b6999be98</v>
+      </c>
+      <c r="B536" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C536" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D536" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E536" t="str">
+        <v>24-08-2026 08:17:38 pm</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="str">
+        <v>6a8c598fc2fb496b6999beab</v>
+      </c>
+      <c r="B537" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C537" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D537" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E537" t="str">
+        <v>24-08-2026 08:17:43 pm</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="str">
+        <v>6a8c5990c2fb496b6999beb1</v>
+      </c>
+      <c r="B538" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C538" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D538" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E538" t="str">
+        <v>24-08-2026 08:17:44 pm</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="str">
+        <v>6a8c5994c2fb496b6999bec3</v>
+      </c>
+      <c r="B539" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C539" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D539" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E539" t="str">
+        <v>24-08-2026 08:17:48 pm</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="str">
+        <v>6a8c5994c2fb496b6999beca</v>
+      </c>
+      <c r="B540" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C540" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D540" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E540" t="str">
+        <v>24-08-2026 08:17:48 pm</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="str">
+        <v>6a8c59a4c2fb496b6999bedc</v>
+      </c>
+      <c r="B541" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C541" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D541" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E541" t="str">
+        <v>24-08-2026 08:18:04 pm</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="str">
+        <v>6a8c59a5c2fb496b6999bee3</v>
+      </c>
+      <c r="B542" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C542" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D542" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E542" t="str">
+        <v>24-08-2026 08:18:05 pm</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="str">
+        <v>6a8c59a8c2fb496b6999bef5</v>
+      </c>
+      <c r="B543" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C543" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D543" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E543" t="str">
+        <v>24-08-2026 08:18:08 pm</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="str">
+        <v>6a8c59a8c2fb496b6999befc</v>
+      </c>
+      <c r="B544" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C544" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D544" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E544" t="str">
+        <v>24-08-2026 08:18:08 pm</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="str">
+        <v>6a8c59b4c2fb496b6999bf0e</v>
+      </c>
+      <c r="B545" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C545" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D545" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E545" t="str">
+        <v>24-08-2026 08:18:20 pm</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="str">
+        <v>6a8c59b5c2fb496b6999bf15</v>
+      </c>
+      <c r="B546" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C546" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D546" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E546" t="str">
+        <v>24-08-2026 08:18:21 pm</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="str">
+        <v>6a8c59b7c2fb496b6999bf27</v>
+      </c>
+      <c r="B547" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C547" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D547" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E547" t="str">
+        <v>24-08-2026 08:18:23 pm</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="str">
+        <v>6a8c59b8c2fb496b6999bf2e</v>
+      </c>
+      <c r="B548" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C548" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D548" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E548" t="str">
+        <v>24-08-2026 08:18:24 pm</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="str">
+        <v>6a8c59bdc2fb496b6999bf40</v>
+      </c>
+      <c r="B549" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C549" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D549" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E549" t="str">
+        <v>24-08-2026 08:18:29 pm</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="str">
+        <v>6a8c59bec2fb496b6999bf47</v>
+      </c>
+      <c r="B550" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C550" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D550" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E550" t="str">
+        <v>24-08-2026 08:18:30 pm</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="str">
+        <v>6a8c59c8c2fb496b6999bf5a</v>
+      </c>
+      <c r="B551" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C551" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D551" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E551" t="str">
+        <v>24-08-2026 08:18:40 pm</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="str">
+        <v>6a8c59c8c2fb496b6999bf60</v>
+      </c>
+      <c r="B552" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C552" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D552" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E552" t="str">
+        <v>24-08-2026 08:18:40 pm</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="str">
+        <v>6a8c59cbc2fb496b6999bf72</v>
+      </c>
+      <c r="B553" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C553" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D553" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E553" t="str">
+        <v>24-08-2026 08:18:43 pm</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="str">
+        <v>6a8c59cbc2fb496b6999bf79</v>
+      </c>
+      <c r="B554" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C554" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D554" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E554" t="str">
+        <v>24-08-2026 08:18:43 pm</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="str">
+        <v>6a8c59cec2fb496b6999bf8c</v>
+      </c>
+      <c r="B555" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C555" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D555" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E555" t="str">
+        <v>24-08-2026 08:18:46 pm</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="str">
+        <v>6a8c59cfc2fb496b6999bf92</v>
+      </c>
+      <c r="B556" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C556" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D556" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E556" t="str">
+        <v>24-08-2026 08:18:47 pm</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="str">
+        <v>6a8c59dcc2fb496b6999bfa4</v>
+      </c>
+      <c r="B557" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C557" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D557" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E557" t="str">
+        <v>24-08-2026 08:19:00 pm</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="str">
+        <v>6a8c59ddc2fb496b6999bfab</v>
+      </c>
+      <c r="B558" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C558" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D558" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E558" t="str">
+        <v>24-08-2026 08:19:01 pm</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="str">
+        <v>6a8c59e9c2fb496b6999bfbd</v>
+      </c>
+      <c r="B559" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C559" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D559" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E559" t="str">
+        <v>24-08-2026 08:19:13 pm</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="str">
+        <v>6a8c59eac2fb496b6999bfc4</v>
+      </c>
+      <c r="B560" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C560" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D560" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E560" t="str">
+        <v>24-08-2026 08:19:14 pm</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="str">
+        <v>6a8c59f1c2fb496b6999bfd6</v>
+      </c>
+      <c r="B561" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C561" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D561" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E561" t="str">
+        <v>24-08-2026 08:19:21 pm</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="str">
+        <v>6a8c59f2c2fb496b6999bfdd</v>
+      </c>
+      <c r="B562" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C562" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D562" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E562" t="str">
+        <v>24-08-2026 08:19:22 pm</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="str">
+        <v>6a8c59f4c2fb496b6999bfef</v>
+      </c>
+      <c r="B563" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C563" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D563" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E563" t="str">
+        <v>24-08-2026 08:19:24 pm</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="str">
+        <v>6a8c59f5c2fb496b6999bff6</v>
+      </c>
+      <c r="B564" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C564" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D564" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E564" t="str">
+        <v>24-08-2026 08:19:25 pm</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="str">
+        <v>6a8c59f7c2fb496b6999c008</v>
+      </c>
+      <c r="B565" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C565" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D565" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E565" t="str">
+        <v>24-08-2026 08:19:27 pm</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="str">
+        <v>6a8c59f8c2fb496b6999c00f</v>
+      </c>
+      <c r="B566" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C566" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D566" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E566" t="str">
+        <v>24-08-2026 08:19:28 pm</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="str">
+        <v>6a8c59fac2fb496b6999c021</v>
+      </c>
+      <c r="B567" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C567" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D567" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E567" t="str">
+        <v>24-08-2026 08:19:30 pm</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="str">
+        <v>6a8c59fbc2fb496b6999c028</v>
+      </c>
+      <c r="B568" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C568" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D568" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E568" t="str">
+        <v>24-08-2026 08:19:31 pm</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="str">
+        <v>6a8c59fdc2fb496b6999c03a</v>
+      </c>
+      <c r="B569" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C569" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D569" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E569" t="str">
+        <v>24-08-2026 08:19:33 pm</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="str">
+        <v>6a8c59fec2fb496b6999c041</v>
+      </c>
+      <c r="B570" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C570" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D570" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E570" t="str">
+        <v>24-08-2026 08:19:34 pm</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="str">
+        <v>6a8c5a0ec2fb496b6999c054</v>
+      </c>
+      <c r="B571" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C571" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D571" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E571" t="str">
+        <v>24-08-2026 08:19:50 pm</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="str">
+        <v>6a8c5a0fc2fb496b6999c05a</v>
+      </c>
+      <c r="B572" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C572" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D572" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E572" t="str">
+        <v>24-08-2026 08:19:51 pm</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="str">
+        <v>6a8c5a11c2fb496b6999c06c</v>
+      </c>
+      <c r="B573" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C573" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D573" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E573" t="str">
+        <v>24-08-2026 08:19:53 pm</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="str">
+        <v>6a8c5a12c2fb496b6999c073</v>
+      </c>
+      <c r="B574" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C574" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D574" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E574" t="str">
+        <v>24-08-2026 08:19:54 pm</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="str">
+        <v>6a8c5a1dc2fb496b6999c085</v>
+      </c>
+      <c r="B575" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C575" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D575" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E575" t="str">
+        <v>24-08-2026 08:20:05 pm</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="str">
+        <v>6a8c5a1ec2fb496b6999c08c</v>
+      </c>
+      <c r="B576" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C576" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D576" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E576" t="str">
+        <v>24-08-2026 08:20:06 pm</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="str">
+        <v>6a8c5a21c2fb496b6999c09e</v>
+      </c>
+      <c r="B577" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C577" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D577" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E577" t="str">
+        <v>24-08-2026 08:20:09 pm</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="str">
+        <v>6a8c5a21c2fb496b6999c0a5</v>
+      </c>
+      <c r="B578" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C578" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D578" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E578" t="str">
+        <v>24-08-2026 08:20:09 pm</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="str">
+        <v>6a8c5a39c2fb496b6999c0b7</v>
+      </c>
+      <c r="B579" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C579" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D579" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E579" t="str">
+        <v>24-08-2026 08:20:33 pm</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="str">
+        <v>6a8c5a39c2fb496b6999c0be</v>
+      </c>
+      <c r="B580" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C580" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D580" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E580" t="str">
+        <v>24-08-2026 08:20:33 pm</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="str">
+        <v>6a8c5a4cc2fb496b6999c0d1</v>
+      </c>
+      <c r="B581" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C581" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D581" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E581" t="str">
+        <v>24-08-2026 08:20:52 pm</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="str">
+        <v>6a8c5a4cc2fb496b6999c0d7</v>
+      </c>
+      <c r="B582" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C582" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D582" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E582" t="str">
+        <v>24-08-2026 08:20:52 pm</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="str">
+        <v>6a8c5a4fc2fb496b6999c0e9</v>
+      </c>
+      <c r="B583" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C583" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D583" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E583" t="str">
+        <v>24-08-2026 08:20:55 pm</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="str">
+        <v>6a8c5a4fc2fb496b6999c0f0</v>
+      </c>
+      <c r="B584" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C584" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D584" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E584" t="str">
+        <v>24-08-2026 08:20:55 pm</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="str">
+        <v>6a8c5a52c2fb496b6999c102</v>
+      </c>
+      <c r="B585" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C585" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D585" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E585" t="str">
+        <v>24-08-2026 08:20:58 pm</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="str">
+        <v>6a8c5a52c2fb496b6999c109</v>
+      </c>
+      <c r="B586" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C586" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D586" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E586" t="str">
+        <v>24-08-2026 08:20:58 pm</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="str">
+        <v>6a8c5a54c2fb496b6999c11b</v>
+      </c>
+      <c r="B587" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C587" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D587" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E587" t="str">
+        <v>24-08-2026 08:21:00 pm</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="str">
+        <v>6a8c5a55c2fb496b6999c122</v>
+      </c>
+      <c r="B588" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C588" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D588" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E588" t="str">
+        <v>24-08-2026 08:21:01 pm</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="str">
+        <v>6a8c5a5ac2fb496b6999c135</v>
+      </c>
+      <c r="B589" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C589" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D589" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E589" t="str">
+        <v>24-08-2026 08:21:06 pm</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="str">
+        <v>6a8c5a66c2fb496b6999c155</v>
+      </c>
+      <c r="B590" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C590" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D590" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E590" t="str">
+        <v>24-08-2026 08:21:18 pm</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="str">
+        <v>6a8c5a5bc2fb496b6999c13b</v>
+      </c>
+      <c r="B591" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C591" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D591" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E591" t="str">
+        <v>24-08-2026 08:21:07 pm</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="str">
+        <v>6a8c5a6bc2fb496b6999c16f</v>
+      </c>
+      <c r="B592" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C592" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D592" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E592" t="str">
+        <v>24-08-2026 08:21:23 pm</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="str">
+        <v>6a8c5a66c2fb496b6999c157</v>
+      </c>
+      <c r="B593" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C593" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D593" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E593" t="str">
+        <v>24-08-2026 08:21:18 pm</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="str">
+        <v>6a8c5a6cc2fb496b6999c171</v>
+      </c>
+      <c r="B594" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C594" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D594" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E594" t="str">
+        <v>24-08-2026 08:21:24 pm</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="str">
+        <v>6a8c5a99c2fb496b6999c186</v>
+      </c>
+      <c r="B595" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C595" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D595" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E595" t="str">
+        <v>24-08-2026 08:22:09 pm</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="str">
+        <v>6a8c5a9ec2fb496b6999c1a1</v>
+      </c>
+      <c r="B596" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C596" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D596" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E596" t="str">
+        <v>24-08-2026 08:22:14 pm</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="str">
+        <v>6a8c5a99c2fb496b6999c18b</v>
+      </c>
+      <c r="B597" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C597" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D597" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E597" t="str">
+        <v>24-08-2026 08:22:09 pm</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="str">
+        <v>6a8c5aaac2fb496b6999c1ba</v>
+      </c>
+      <c r="B598" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C598" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D598" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E598" t="str">
+        <v>24-08-2026 08:22:26 pm</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="str">
+        <v>6a8c5a9ec2fb496b6999c1a3</v>
+      </c>
+      <c r="B599" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C599" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D599" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E599" t="str">
+        <v>24-08-2026 08:22:14 pm</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="str">
+        <v>6a8c5aaac2fb496b6999c1bc</v>
+      </c>
+      <c r="B600" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C600" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D600" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E600" t="str">
+        <v>24-08-2026 08:22:26 pm</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="str">
+        <v>6a8c5acec2fb496b6999c1d2</v>
+      </c>
+      <c r="B601" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C601" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D601" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E601" t="str">
+        <v>24-08-2026 08:23:02 pm</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="str">
+        <v>6a8c5acec2fb496b6999c1d6</v>
+      </c>
+      <c r="B602" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C602" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D602" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E602" t="str">
+        <v>24-08-2026 08:23:02 pm</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="str">
+        <v>6a8c5ad2c2fb496b6999c1e9</v>
+      </c>
+      <c r="B603" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C603" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D603" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E603" t="str">
+        <v>24-08-2026 08:23:06 pm</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="str">
+        <v>6a8c5ad7c2fb496b6999c203</v>
+      </c>
+      <c r="B604" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C604" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D604" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E604" t="str">
+        <v>24-08-2026 08:23:11 pm</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="str">
+        <v>6a8c5ad2c2fb496b6999c1ef</v>
+      </c>
+      <c r="B605" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C605" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D605" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E605" t="str">
+        <v>24-08-2026 08:23:06 pm</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="str">
+        <v>6a8c5adbc2fb496b6999c21d</v>
+      </c>
+      <c r="B606" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C606" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D606" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E606" t="str">
+        <v>24-08-2026 08:23:15 pm</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="str">
+        <v>6a8c5ad7c2fb496b6999c207</v>
+      </c>
+      <c r="B607" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C607" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D607" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E607" t="str">
+        <v>24-08-2026 08:23:11 pm</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="str">
+        <v>6a8c5aeac2fb496b6999c236</v>
+      </c>
+      <c r="B608" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C608" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D608" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E608" t="str">
+        <v>24-08-2026 08:23:30 pm</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="str">
+        <v>6a8c5adbc2fb496b6999c220</v>
+      </c>
+      <c r="B609" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C609" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D609" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E609" t="str">
+        <v>24-08-2026 08:23:15 pm</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="str">
+        <v>6a8c5af0c2fb496b6999c24e</v>
+      </c>
+      <c r="B610" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C610" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D610" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E610" t="str">
+        <v>24-08-2026 08:23:36 pm</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="str">
+        <v>6a8c5aeac2fb496b6999c239</v>
+      </c>
+      <c r="B611" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C611" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D611" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E611" t="str">
+        <v>24-08-2026 08:23:30 pm</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="str">
+        <v>6a8c5af5c2fb496b6999c267</v>
+      </c>
+      <c r="B612" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C612" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D612" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E612" t="str">
+        <v>24-08-2026 08:23:41 pm</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="str">
+        <v>6a8c5af0c2fb496b6999c252</v>
+      </c>
+      <c r="B613" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C613" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D613" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E613" t="str">
+        <v>24-08-2026 08:23:36 pm</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="str">
+        <v>6a8c5af5c2fb496b6999c26b</v>
+      </c>
+      <c r="B614" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C614" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D614" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E614" t="str">
+        <v>24-08-2026 08:23:41 pm</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="str">
+        <v>6a8c5b21c2fb496b6999c27f</v>
+      </c>
+      <c r="B615" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C615" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D615" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E615" t="str">
+        <v>24-08-2026 08:24:25 pm</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="str">
+        <v>6a8c5b22c2fb496b6999c286</v>
+      </c>
+      <c r="B616" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C616" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D616" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E616" t="str">
+        <v>24-08-2026 08:24:26 pm</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="str">
+        <v>6a8c5b33c2fb496b6999c298</v>
+      </c>
+      <c r="B617" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C617" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D617" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E617" t="str">
+        <v>24-08-2026 08:24:43 pm</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="str">
+        <v>6a8c5b33c2fb496b6999c29e</v>
+      </c>
+      <c r="B618" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C618" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D618" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E618" t="str">
+        <v>24-08-2026 08:24:43 pm</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="str">
+        <v>6a8c5b3ec2fb496b6999c2b2</v>
+      </c>
+      <c r="B619" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C619" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D619" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E619" t="str">
+        <v>24-08-2026 08:24:54 pm</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="str">
+        <v>6a8c5b3fc2fb496b6999c2b8</v>
+      </c>
+      <c r="B620" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C620" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D620" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E620" t="str">
+        <v>24-08-2026 08:24:55 pm</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="str">
+        <v>6a8c5b52c2fb496b6999c2ca</v>
+      </c>
+      <c r="B621" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C621" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D621" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E621" t="str">
+        <v>24-08-2026 08:25:14 pm</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="str">
+        <v>6a8c5b52c2fb496b6999c2d1</v>
+      </c>
+      <c r="B622" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C622" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D622" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E622" t="str">
+        <v>24-08-2026 08:25:14 pm</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="str">
+        <v>6a8c5b61c2fb496b6999c2e4</v>
+      </c>
+      <c r="B623" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C623" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D623" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E623" t="str">
+        <v>24-08-2026 08:25:29 pm</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="str">
+        <v>6a8c5b62c2fb496b6999c2ea</v>
+      </c>
+      <c r="B624" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C624" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D624" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E624" t="str">
+        <v>24-08-2026 08:25:30 pm</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="str">
+        <v>6a8c5b70c2fb496b6999c2fc</v>
+      </c>
+      <c r="B625" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C625" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D625" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E625" t="str">
+        <v>24-08-2026 08:25:44 pm</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="str">
+        <v>6a8c5b70c2fb496b6999c303</v>
+      </c>
+      <c r="B626" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C626" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D626" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E626" t="str">
+        <v>24-08-2026 08:25:44 pm</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="str">
+        <v>6a8c5b73c2fb496b6999c315</v>
+      </c>
+      <c r="B627" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C627" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D627" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E627" t="str">
+        <v>24-08-2026 08:25:47 pm</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="str">
+        <v>6a8c5b73c2fb496b6999c31c</v>
+      </c>
+      <c r="B628" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C628" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D628" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E628" t="str">
+        <v>24-08-2026 08:25:47 pm</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="str">
+        <v>6a8c5e39c2fb496b6999c32d</v>
+      </c>
+      <c r="B629" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C629" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D629" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E629" t="str">
+        <v>24-08-2026 08:37:37 pm</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="str">
+        <v>6a8c5e3ac2fb496b6999c336</v>
+      </c>
+      <c r="B630" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C630" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D630" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E630" t="str">
+        <v>24-08-2026 08:37:38 pm</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="str">
+        <v>6a8c5e40c2fb496b6999c348</v>
+      </c>
+      <c r="B631" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C631" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D631" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E631" t="str">
+        <v>24-08-2026 08:37:44 pm</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="str">
+        <v>6a8c5e40c2fb496b6999c34c</v>
+      </c>
+      <c r="B632" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C632" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D632" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E632" t="str">
+        <v>24-08-2026 08:37:44 pm</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="str">
+        <v>6a8c5e80c2fb496b6999c397</v>
+      </c>
+      <c r="B633" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C633" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D633" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E633" t="str">
+        <v>24-08-2026 08:38:48 pm</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="str">
+        <v>6a8c5e80c2fb496b6999c39b</v>
+      </c>
+      <c r="B634" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C634" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D634" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E634" t="str">
+        <v>24-08-2026 08:38:48 pm</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="str">
+        <v>6a8c5e86c2fb496b6999c3b1</v>
+      </c>
+      <c r="B635" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C635" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D635" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E635" t="str">
+        <v>24-08-2026 08:38:54 pm</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="str">
+        <v>6a8c5eddc2fb496b6999c3c9</v>
+      </c>
+      <c r="B636" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C636" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D636" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E636" t="str">
+        <v>24-08-2026 08:40:21 pm</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="str">
+        <v>6a8c5e86c2fb496b6999c3b4</v>
+      </c>
+      <c r="B637" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C637" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D637" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E637" t="str">
+        <v>24-08-2026 08:38:54 pm</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="str">
+        <v>6a8c5ee7c2fb496b6999c3e4</v>
+      </c>
+      <c r="B638" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C638" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D638" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E638" t="str">
+        <v>24-08-2026 08:40:31 pm</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="str">
+        <v>6a8c5eddc2fb496b6999c3cc</v>
+      </c>
+      <c r="B639" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C639" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D639" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E639" t="str">
+        <v>24-08-2026 08:40:21 pm</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="str">
+        <v>6a8c5ee7c2fb496b6999c3e6</v>
+      </c>
+      <c r="B640" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C640" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D640" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E640" t="str">
+        <v>24-08-2026 08:40:31 pm</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="str">
+        <v>6a8c5f08c2fb496b6999c404</v>
+      </c>
+      <c r="B641" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C641" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D641" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E641" t="str">
+        <v>24-08-2026 08:41:04 pm</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="str">
+        <v>6a8c5f06c2fb496b6999c3f3</v>
+      </c>
+      <c r="B642" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C642" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D642" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E642" t="str">
+        <v>24-08-2026 08:41:02 pm</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="str">
+        <v>6a8c5f0dc2fb496b6999c41e</v>
+      </c>
+      <c r="B643" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C643" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D643" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E643" t="str">
+        <v>24-08-2026 08:41:09 pm</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="str">
+        <v>6a8c5f08c2fb496b6999c407</v>
+      </c>
+      <c r="B644" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C644" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D644" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E644" t="str">
+        <v>24-08-2026 08:41:04 pm</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="str">
+        <v>6a8c5f0dc2fb496b6999c422</v>
+      </c>
+      <c r="B645" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C645" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D645" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E645" t="str">
+        <v>24-08-2026 08:41:09 pm</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E515"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E645"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/live-history.xlsx
+++ b/live-history.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E645"/>
+  <dimension ref="A1:E647"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -11364,9 +11364,43 @@
         <v>24-08-2026 08:41:09 pm</v>
       </c>
     </row>
+    <row r="646">
+      <c r="A646" t="str">
+        <v>6a8c5f18c2fb496b6999c42f</v>
+      </c>
+      <c r="B646" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C646" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D646" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E646" t="str">
+        <v>24-08-2026 08:41:20 pm</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="str">
+        <v>6aa02d37bc28a15fc89bd2d0</v>
+      </c>
+      <c r="B647" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C647" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D647" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E647" t="str">
+        <v>08-09-2026 09:13:51 pm</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E645"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E647"/>
   </ignoredErrors>
 </worksheet>
 </file>